--- a/extraction.xlsx
+++ b/extraction.xlsx
@@ -2,247 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Studies" sheetId="2" r:id="R2192726500594f0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reports" sheetId="3" r:id="R2474118eba0c4590"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conditions" sheetId="4" r:id="R3b8d46cc5b87460e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outcomes" sheetId="5" r:id="Rd32f6bcd12844c2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Derivations" sheetId="6" r:id="R9dadbeaf385849ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data limitations" sheetId="7" r:id="R04a389541bd6482c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Studies" sheetId="2" r:id="Ra6616189493d4f60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reports" sheetId="3" r:id="R8d3611462bf94ef6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conditions" sheetId="4" r:id="Rfbeffa0c268941d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outcomes" sheetId="5" r:id="R1f20d4ccb1cf4e0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Derivations" sheetId="6" r:id="Raade7c8bdf3d4aaf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data limitations" sheetId="7" r:id="R9e03f753410f4b97"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t xml:space="preserve">derivation_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">study_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">outcome_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">derivation_type</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">inputs</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">formula_or_method</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">assumptions</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">result</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">data_status</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">notes</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D001</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Bandin_2015</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">O0003</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">paired SE from exact paired t-test</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">condition means 102.6 and 70.0; n=10; two-sided p=0.002</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SE = |MD| / |t_(1-p/2, n-1)|</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Exact p corresponds to unadjusted paired t-test for displayed means</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SE=7.5870; SDdifference=23.9923</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">derived</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Do not use if the reported p was from a different model/test.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D002</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Bo_2015</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">O0004</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SE from 95% CI</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CI [-2564.1, -1036.0]</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SE = (upper-lower)/(2×1.96)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Normal approximation</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SE=389.8286</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Reported model contrast itself remains primary.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D003</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Gu_2020</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CI [70.3, 107.3]</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SE=9.4390</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D004</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Lopez_Minguez_2018</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">late 284.74; early 269.61; n=40; p=0.004</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Exact p corresponds to unadjusted paired t-test for displayed total-sample means</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MD=15.13; SE=4.9456; SDdifference=31.2787</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Do not transfer covariance to genotype subgroups.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D005</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Stutz_2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">early chronotype 2-h iAUC contrast CI [2,77]</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SE=19.1330</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Use reported multilevel-model contrast.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D006</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">late chronotype 2-h iAUC contrast CI [-55,48]</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SE=26.2760</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D007</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Garaulet_2022</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">manual graph digitization</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Figure 1B/D bars and SEM caps</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Axis-calibrated visual read; rounded to graph resolution</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No subpixel precision claimed</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">glucose ~276 vs 299; insulin ~98 vs 91.5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">graph_digitized</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Prefer author data or supplement for final model.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D008</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Nakamura_2021</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Figure 3A/B bars and SD caps</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Figure states mean±SD</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">meal-specific iAUC and period mean values</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Dinner contrast direction robust; exact values approximate.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D009</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sulaimani_2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Figures 3B/C and 4B/C bars and SD caps</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Figures state mean±SD</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">glucose/insulin iAUC and peaks</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Individual dots offer a future cross-check; author data preferred.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D010</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Enomoto_2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">O0261</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Author-provided Day-2 MD=598.84615 and SE=738.32932 mg/dL×min</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Divide glucose concentration-time values by 18</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1 mmol/L glucose = 18 mg/dL; time unit unchanged</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MD=33.2692; SE=41.0183 mmol/L×min</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Original author-provided units and values remain unchanged in Outcomes.</x:t>
-  </x:si>
-</x:sst>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -831,7 +602,7 @@
         <x:v>mixed_meal</x:v>
       </x:c>
       <x:c r="K2" s="1" t="n">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L2" s="1" t="n">
         <x:v>10</x:v>
@@ -846,23 +617,23 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="P2" s="1" t="str">
-        <x:v>24 ± 4 y</x:v>
+        <x:v>26 ± 4 y (SD)</x:v>
       </x:c>
       <x:c r="Q2" s="1" t="str">
-        <x:v>22.9 ± 2.6 kg/m²</x:v>
+        <x:v>22.54 ± 2.05 kg/m² (SD)</x:v>
       </x:c>
       <x:c r="R2" s="1"/>
       <x:c r="S2" s="1" t="str">
         <x:v>two 1-week timing conditions</x:v>
       </x:c>
       <x:c r="T2" s="1" t="str">
-        <x:v>crossover weeks; NR</x:v>
+        <x:v>1 wk</x:v>
       </x:c>
       <x:c r="U2" s="1" t="str">
-        <x:v>Only Protocol 1 (n=10) contributes mixed-meal glucose outcomes.</x:v>
+        <x:v>Glucose protocol 1: 10 women, all completed; broader study also enrolled 22 women in protocol 2 without glucose outcomes.</x:v>
       </x:c>
       <x:c r="V2" s="1" t="str">
-        <x:v>Bandin_2015; PDF pp2–4; Methods/Table 1</x:v>
+        <x:v>Bandin_2015_primary; PDF pp7–9,24; Methods and Table 1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -984,19 +755,19 @@
         <x:v>27.9 ± 4.1 kg/m²</x:v>
       </x:c>
       <x:c r="R4" s="1" t="str">
-        <x:v>7.4 ± 1.0%</x:v>
+        <x:v>7.4 ± 1.0% (SD)</x:v>
       </x:c>
       <x:c r="S4" s="1" t="str">
         <x:v>three 8-day periods</x:v>
       </x:c>
       <x:c r="T4" s="1" t="str">
-        <x:v>NR</x:v>
+        <x:v>6 d</x:v>
       </x:c>
       <x:c r="U4" s="1" t="str">
         <x:v>Primary nonexercise adherent analysis n=11; exercise secondary analysis n=10.</x:v>
       </x:c>
       <x:c r="V4" s="1" t="str">
-        <x:v>Bravo_Garcia_2024; PDF pp2–5</x:v>
+        <x:v>Bravo_Garcia_2024_primary; PDF pp3–4; Methods and Table 1</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
@@ -1031,10 +802,10 @@
         <x:v>mixed_meal</x:v>
       </x:c>
       <x:c r="K5" s="1" t="n">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L5" s="1" t="n">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="M5" s="1" t="n">
         <x:v>13</x:v>
@@ -1056,13 +827,13 @@
         <x:v>four monitored days per condition</x:v>
       </x:c>
       <x:c r="T5" s="1" t="str">
-        <x:v>NR</x:v>
+        <x:v>≥1 wk</x:v>
       </x:c>
       <x:c r="U5" s="1" t="str">
         <x:v>Dinner 1 h versus 5 h before bedtime.</x:v>
       </x:c>
       <x:c r="V5" s="1" t="str">
-        <x:v>Enomoto_2026; PDF pp3–6; Tables 1–2</x:v>
+        <x:v>Enomoto_2026_primary; PDF pp2–3,5; Methods, Results and Table 1</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
@@ -1122,7 +893,7 @@
         <x:v>two OGTT sessions</x:v>
       </x:c>
       <x:c r="T6" s="1" t="str">
-        <x:v>NR</x:v>
+        <x:v>1 wk</x:v>
       </x:c>
       <x:c r="U6" s="1" t="str">
         <x:v>Early evening 4 h before habitual bedtime versus late evening 1 h before bedtime.</x:v>
@@ -1188,7 +959,7 @@
         <x:v>four test visits</x:v>
       </x:c>
       <x:c r="T7" s="1" t="str">
-        <x:v>NR</x:v>
+        <x:v>≥2 d</x:v>
       </x:c>
       <x:c r="U7" s="1" t="str">
         <x:v>Low/high-GI meals at 08:00 or 20:00; fasting duration differed by daypart.</x:v>
@@ -1244,10 +1015,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="P8" s="1" t="str">
-        <x:v>26.0 ± 0.6 y</x:v>
+        <x:v>26.0 ± 0.6 y (SEM)</x:v>
       </x:c>
       <x:c r="Q8" s="1" t="str">
-        <x:v>23.2 ± 0.7 kg/m²</x:v>
+        <x:v>23.2 ± 0.7 kg/m² (SEM)</x:v>
       </x:c>
       <x:c r="R8" s="1"/>
       <x:c r="S8" s="1" t="str">
@@ -1369,10 +1140,14 @@
       <x:c r="M10" s="1" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="N10" s="1"/>
-      <x:c r="O10" s="1"/>
+      <x:c r="N10" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O10" s="1" t="n">
+        <x:v>23</x:v>
+      </x:c>
       <x:c r="P10" s="1" t="str">
-        <x:v>broad adult range</x:v>
+        <x:v>19–91 y (range)</x:v>
       </x:c>
       <x:c r="Q10" s="1"/>
       <x:c r="R10" s="1"/>
@@ -1386,7 +1161,7 @@
         <x:v>50-g oral glucose at 09:00, 15:00, and 20:00.</x:v>
       </x:c>
       <x:c r="V10" s="1" t="str">
-        <x:v>Jarrett_1972; PDF pp1–3; Tables I–III</x:v>
+        <x:v>Jarrett_1972_primary; PDF p1; Table I</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
@@ -1436,10 +1211,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="P11" s="1" t="str">
-        <x:v>NR</x:v>
+        <x:v>42 ± 10 y (SD)</x:v>
       </x:c>
       <x:c r="Q11" s="1" t="str">
-        <x:v>BMI &gt;25 kg/m²</x:v>
+        <x:v>28.42 ± 4.04 kg/m² (SD)</x:v>
       </x:c>
       <x:c r="R11" s="1"/>
       <x:c r="S11" s="1" t="str">
@@ -1452,10 +1227,10 @@
         <x:v>20 GG and 20 CC participants; early 4 h vs late 1 h before bedtime.</x:v>
       </x:c>
       <x:c r="V11" s="1" t="str">
-        <x:v>Lopez_Minguez_2018; PDF pp3–6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
+        <x:v>Lopez_Minguez_2018_primary; PDF pp3–6,15; Methods and Table 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="55" customHeight="1">
       <x:c r="A12" s="1" t="str">
         <x:v>Lu_2022</x:v>
       </x:c>
@@ -1578,7 +1353,7 @@
         <x:v>two 3-day trials</x:v>
       </x:c>
       <x:c r="T13" s="1" t="str">
-        <x:v>NR</x:v>
+        <x:v>≥3 d; mean 5 ± 2 d (SD)</x:v>
       </x:c>
       <x:c r="U13" s="1" t="str">
         <x:v>14 randomized; one illness dropout and one scheduling withdrawal; 12 analyzed. Dinner at 18:00 versus 21:00 with CGM.</x:v>
@@ -1693,26 +1468,30 @@
       <x:c r="M15" s="1" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="N15" s="1"/>
-      <x:c r="O15" s="1"/>
+      <x:c r="N15" s="1" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O15" s="1" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="P15" s="1" t="str">
-        <x:v>NR</x:v>
+        <x:v>26 ± 2 y (SEM)</x:v>
       </x:c>
       <x:c r="Q15" s="1" t="str">
-        <x:v>NR</x:v>
+        <x:v>20.5 ± 1.7 kg/m² (SEM)</x:v>
       </x:c>
       <x:c r="R15" s="1"/>
       <x:c r="S15" s="1" t="str">
         <x:v>two 24-h chamber trials</x:v>
       </x:c>
       <x:c r="T15" s="1" t="str">
-        <x:v>NR</x:v>
+        <x:v>2 wk men; 1 month women</x:v>
       </x:c>
       <x:c r="U15" s="1" t="str">
         <x:v>Dinner at 19:00 versus 22:30; CGM.</x:v>
       </x:c>
       <x:c r="V15" s="1" t="str">
-        <x:v>Sato_2011; PDF pp2–5</x:v>
+        <x:v>Sato_2011_primary; PDF pp2–4; Methods and Statistical analysis</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
@@ -1762,17 +1541,17 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="P16" s="1" t="str">
-        <x:v>39 ± 4 y</x:v>
+        <x:v>39 ± 4 y (SEM)</x:v>
       </x:c>
       <x:c r="Q16" s="1" t="str">
-        <x:v>96.5 ± 3.1% ideal body weight</x:v>
+        <x:v>NR; 96.5 ± 3.1% ideal body weight (SEM)</x:v>
       </x:c>
       <x:c r="R16" s="1"/>
       <x:c r="S16" s="1" t="str">
         <x:v>three experimental days</x:v>
       </x:c>
       <x:c r="T16" s="1" t="str">
-        <x:v>NR</x:v>
+        <x:v>≥2 wk</x:v>
       </x:c>
       <x:c r="U16" s="1" t="str">
         <x:v>Small/medium/large identical meal types rotated across 08:00, 13:00, 18:00.</x:v>
@@ -1817,13 +1596,17 @@
       <x:c r="M17" s="1" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="N17" s="1"/>
-      <x:c r="O17" s="1"/>
+      <x:c r="N17" s="1" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="O17" s="1" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="P17" s="1" t="str">
-        <x:v>~22 y</x:v>
+        <x:v>22 (IQR 21–23) y</x:v>
       </x:c>
       <x:c r="Q17" s="1" t="str">
-        <x:v>NR</x:v>
+        <x:v>22.4 ± 2.2 kg/m² (SD)</x:v>
       </x:c>
       <x:c r="R17" s="1"/>
       <x:c r="S17" s="1" t="str">
@@ -1875,13 +1658,17 @@
       <x:c r="M18" s="1" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="N18" s="1"/>
-      <x:c r="O18" s="1"/>
+      <x:c r="N18" s="1" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="O18" s="1" t="n">
+        <x:v>11</x:v>
+      </x:c>
       <x:c r="P18" s="1" t="str">
-        <x:v>~22 y</x:v>
+        <x:v>22 (IQR 21–24) y</x:v>
       </x:c>
       <x:c r="Q18" s="1" t="str">
-        <x:v>NR</x:v>
+        <x:v>22.5 ± 2.6 kg/m² (SD)</x:v>
       </x:c>
       <x:c r="R18" s="1"/>
       <x:c r="S18" s="1" t="str">
@@ -1937,8 +1724,12 @@
       <x:c r="M19" s="1" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="N19" s="1"/>
-      <x:c r="O19" s="1"/>
+      <x:c r="N19" s="1" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="O19" s="1" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="P19" s="1" t="str">
         <x:v>19.5 y, median (IQR 2.25)</x:v>
       </x:c>
@@ -1950,19 +1741,19 @@
         <x:v>four test sessions</x:v>
       </x:c>
       <x:c r="T19" s="1" t="str">
-        <x:v>NR</x:v>
+        <x:v>≥1 wk</x:v>
       </x:c>
       <x:c r="U19" s="1" t="str">
         <x:v>White rice control or green-tea-extract rice in morning/evening.</x:v>
       </x:c>
       <x:c r="V19" s="1" t="str">
-        <x:v>Sulaimani_2025; PDF pp2–7</x:v>
+        <x:v>Sulaimani_2025_primary; PDF pp2–3,5; Methods and Table 1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9da89b367d142e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd6ffb568add4ac4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2282,7 +2073,9 @@
       <x:c r="E12" s="1" t="str">
         <x:v>British Medical Journal</x:v>
       </x:c>
-      <x:c r="F12" s="1"/>
+      <x:c r="F12" s="1" t="str">
+        <x:v>10.1136/bmj.1.5794.199</x:v>
+      </x:c>
       <x:c r="G12" s="1" t="str">
         <x:v>primary outcomes</x:v>
       </x:c>
@@ -2437,7 +2230,7 @@
         <x:v>Diabetologia</x:v>
       </x:c>
       <x:c r="F18" s="1" t="str">
-        <x:v>10.1007/BF00252690</x:v>
+        <x:v>10.1007/BF00253193</x:v>
       </x:c>
       <x:c r="G18" s="1" t="str">
         <x:v>primary outcomes</x:v>
@@ -2501,7 +2294,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd57d28d041234092"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbed60b1872494840"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3373,7 +3166,7 @@
         <x:v>earlier</x:v>
       </x:c>
       <x:c r="F19" s="1" t="str">
-        <x:v>08:00</x:v>
+        <x:v>~09:00</x:v>
       </x:c>
       <x:c r="G19" s="1"/>
       <x:c r="H19" s="1" t="str">
@@ -3419,7 +3212,7 @@
         <x:v>later</x:v>
       </x:c>
       <x:c r="F20" s="1" t="str">
-        <x:v>20:00</x:v>
+        <x:v>~18:30</x:v>
       </x:c>
       <x:c r="G20" s="1"/>
       <x:c r="H20" s="1" t="str">
@@ -3465,7 +3258,7 @@
         <x:v>earlier</x:v>
       </x:c>
       <x:c r="F21" s="1" t="str">
-        <x:v>08:00</x:v>
+        <x:v>~09:00</x:v>
       </x:c>
       <x:c r="G21" s="1"/>
       <x:c r="H21" s="1" t="str">
@@ -3511,7 +3304,7 @@
         <x:v>later</x:v>
       </x:c>
       <x:c r="F22" s="1" t="str">
-        <x:v>20:00</x:v>
+        <x:v>~18:30</x:v>
       </x:c>
       <x:c r="G22" s="1"/>
       <x:c r="H22" s="1" t="str">
@@ -4865,7 +4658,9 @@
       <x:c r="N51" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O51" s="1"/>
+      <x:c r="O51" s="1" t="str">
+        <x:v>Meal approximately 30 min after 08:00/18:00 baseline sampling; matched ≥9-h fast.</x:v>
+      </x:c>
       <x:c r="P51" s="1" t="str">
         <x:v>Sulaimani_2025; PDF pp3–6</x:v>
       </x:c>
@@ -4911,7 +4706,9 @@
       <x:c r="N52" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O52" s="1"/>
+      <x:c r="O52" s="1" t="str">
+        <x:v>Meal approximately 30 min after 08:00/18:00 baseline sampling; matched ≥9-h fast.</x:v>
+      </x:c>
       <x:c r="P52" s="1" t="str">
         <x:v>Sulaimani_2025; PDF pp3–6</x:v>
       </x:c>
@@ -4957,7 +4754,9 @@
       <x:c r="N53" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O53" s="1"/>
+      <x:c r="O53" s="1" t="str">
+        <x:v>Meal approximately 30 min after 08:00/18:00 baseline sampling; matched ≥9-h fast.</x:v>
+      </x:c>
       <x:c r="P53" s="1" t="str">
         <x:v>Sulaimani_2025; PDF pp3–6</x:v>
       </x:c>
@@ -5003,7 +4802,9 @@
       <x:c r="N54" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O54" s="1"/>
+      <x:c r="O54" s="1" t="str">
+        <x:v>Meal approximately 30 min after 08:00/18:00 baseline sampling; matched ≥9-h fast.</x:v>
+      </x:c>
       <x:c r="P54" s="1" t="str">
         <x:v>Sulaimani_2025; PDF pp3–6</x:v>
       </x:c>
@@ -5011,7 +4812,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf60dbeec83d4942"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44a55932107e4b12"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5188,10 +4989,10 @@
       <x:c r="W2" s="1"/>
       <x:c r="X2" s="1"/>
       <x:c r="Y2" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_text</x:v>
       </x:c>
       <x:c r="Z2" s="1" t="str">
-        <x:v>Bandin_2015; PDF p4; Results/Figure 2</x:v>
+        <x:v>Bandin_2015_primary; PDF p13; Results</x:v>
       </x:c>
       <x:c r="AA2" s="1" t="str">
         <x:v>Absolute scale/unit label requires QA.</x:v>
@@ -5257,10 +5058,10 @@
       <x:c r="W3" s="1"/>
       <x:c r="X3" s="1"/>
       <x:c r="Y3" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_text</x:v>
       </x:c>
       <x:c r="Z3" s="1" t="str">
-        <x:v>Bandin_2015; PDF p4; Results/Figure 2</x:v>
+        <x:v>Bandin_2015_primary; PDF p13; Results</x:v>
       </x:c>
       <x:c r="AA3" s="1" t="str">
         <x:v>Absolute scale/unit label requires QA.</x:v>
@@ -5329,7 +5130,7 @@
         <x:v>derived</x:v>
       </x:c>
       <x:c r="Z4" s="1" t="str">
-        <x:v>Bandin_2015; PDF p4; displayed means and paired p</x:v>
+        <x:v>Bandin_2015_primary; PDF p13; Results</x:v>
       </x:c>
       <x:c r="AA4" s="1" t="str">
         <x:v>SE derived from exact two-sided paired t-test p; see Derivations.</x:v>
@@ -5400,7 +5201,7 @@
         <x:v>reported_table</x:v>
       </x:c>
       <x:c r="Z5" s="1" t="str">
-        <x:v>Bo_2015_primary; PDF p5; Table 2</x:v>
+        <x:v>Bo_2015_primary; PDF p24; Table 2</x:v>
       </x:c>
       <x:c r="AA5" s="1" t="str">
         <x:v>Condition means are figure-only; reported adjusted contrast retained.</x:v>
@@ -5471,7 +5272,7 @@
         <x:v>reported_table</x:v>
       </x:c>
       <x:c r="Z6" s="1" t="str">
-        <x:v>Bo_2015_primary; PDF p5; Table 2</x:v>
+        <x:v>Bo_2015_primary; PDF p24; Table 2</x:v>
       </x:c>
       <x:c r="AA6" s="1"/>
     </x:row>
@@ -5540,7 +5341,7 @@
         <x:v>reported_table</x:v>
       </x:c>
       <x:c r="Z7" s="1" t="str">
-        <x:v>Bo_2015_primary; PDF p5; Table 2</x:v>
+        <x:v>Bo_2015_primary; PDF p24; Table 2</x:v>
       </x:c>
       <x:c r="AA7" s="1"/>
     </x:row>
@@ -6471,7 +6272,9 @@
       <x:c r="K21" s="1" t="str">
         <x:v>incremental</x:v>
       </x:c>
-      <x:c r="L21" s="4"/>
+      <x:c r="L21" s="4" t="n">
+        <x:v>120</x:v>
+      </x:c>
       <x:c r="M21" s="4"/>
       <x:c r="N21" s="1" t="str">
         <x:v>condition_summary</x:v>
@@ -6490,7 +6293,9 @@
       </x:c>
       <x:c r="S21" s="3"/>
       <x:c r="T21" s="3"/>
-      <x:c r="U21" s="1"/>
+      <x:c r="U21" s="1" t="n">
+        <x:v>0.263</x:v>
+      </x:c>
       <x:c r="V21" s="1" t="str">
         <x:v>mg/dL×min</x:v>
       </x:c>
@@ -6500,7 +6305,7 @@
         <x:v>reported_table</x:v>
       </x:c>
       <x:c r="Z21" s="1" t="str">
-        <x:v>Enomoto_2026; PDF p8; Table 4</x:v>
+        <x:v>Enomoto_2026_primary; PDF p7; Table 4</x:v>
       </x:c>
       <x:c r="AA21" s="1" t="str">
         <x:v>Next-day supportive outcome; p=0.263.</x:v>
@@ -6540,7 +6345,9 @@
       <x:c r="K22" s="1" t="str">
         <x:v>incremental</x:v>
       </x:c>
-      <x:c r="L22" s="4"/>
+      <x:c r="L22" s="4" t="n">
+        <x:v>120</x:v>
+      </x:c>
       <x:c r="M22" s="4"/>
       <x:c r="N22" s="1" t="str">
         <x:v>condition_summary</x:v>
@@ -6559,7 +6366,9 @@
       </x:c>
       <x:c r="S22" s="3"/>
       <x:c r="T22" s="3"/>
-      <x:c r="U22" s="1"/>
+      <x:c r="U22" s="1" t="n">
+        <x:v>0.263</x:v>
+      </x:c>
       <x:c r="V22" s="1" t="str">
         <x:v>mg/dL×min</x:v>
       </x:c>
@@ -6569,7 +6378,7 @@
         <x:v>reported_table</x:v>
       </x:c>
       <x:c r="Z22" s="1" t="str">
-        <x:v>Enomoto_2026; PDF p8; Table 4</x:v>
+        <x:v>Enomoto_2026_primary; PDF p7; Table 4</x:v>
       </x:c>
       <x:c r="AA22" s="1" t="str">
         <x:v>Next-day supportive outcome; p=0.263.</x:v>
@@ -7332,17 +7141,19 @@
       </x:c>
       <x:c r="S33" s="3"/>
       <x:c r="T33" s="3"/>
-      <x:c r="U33" s="1"/>
+      <x:c r="U33" s="1" t="str">
+        <x:v>&lt;0.001</x:v>
+      </x:c>
       <x:c r="V33" s="1" t="str">
         <x:v>mmol/L·h (as printed)</x:v>
       </x:c>
       <x:c r="W33" s="1"/>
       <x:c r="X33" s="1"/>
       <x:c r="Y33" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_figure</x:v>
       </x:c>
       <x:c r="Z33" s="1" t="str">
-        <x:v>Gibbs_2014; PDF p4; Figure 2</x:v>
+        <x:v>Gibbs_2014_primary; PDF p4; Figure 2 numeric labels and Results</x:v>
       </x:c>
       <x:c r="AA33" s="1" t="str">
         <x:v>Unit label/scale requires QA.</x:v>
@@ -7542,10 +7353,10 @@
       <x:c r="W36" s="1"/>
       <x:c r="X36" s="1"/>
       <x:c r="Y36" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_figure</x:v>
       </x:c>
       <x:c r="Z36" s="1" t="str">
-        <x:v>Gibbs_2014; PDF p4; Figure 2</x:v>
+        <x:v>Gibbs_2014_primary; PDF p4; Figure 2 numeric labels and Results</x:v>
       </x:c>
       <x:c r="AA36" s="1"/>
     </x:row>
@@ -7604,17 +7415,19 @@
       </x:c>
       <x:c r="S37" s="3"/>
       <x:c r="T37" s="3"/>
-      <x:c r="U37" s="1"/>
+      <x:c r="U37" s="1" t="str">
+        <x:v>&lt;0.001</x:v>
+      </x:c>
       <x:c r="V37" s="1" t="str">
         <x:v>mmol/L·h (as printed)</x:v>
       </x:c>
       <x:c r="W37" s="1"/>
       <x:c r="X37" s="1"/>
       <x:c r="Y37" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_figure</x:v>
       </x:c>
       <x:c r="Z37" s="1" t="str">
-        <x:v>Gibbs_2014; PDF p4; Figure 2</x:v>
+        <x:v>Gibbs_2014_primary; PDF p4; Figure 2 numeric labels and Results</x:v>
       </x:c>
       <x:c r="AA37" s="1" t="str">
         <x:v>Unit label/scale requires QA.</x:v>
@@ -7814,10 +7627,10 @@
       <x:c r="W40" s="1"/>
       <x:c r="X40" s="1"/>
       <x:c r="Y40" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_figure</x:v>
       </x:c>
       <x:c r="Z40" s="1" t="str">
-        <x:v>Gibbs_2014; PDF p4; Figure 2</x:v>
+        <x:v>Gibbs_2014_primary; PDF p4; Figure 2 numeric labels and Results</x:v>
       </x:c>
       <x:c r="AA40" s="1"/>
     </x:row>
@@ -7876,17 +7689,19 @@
       </x:c>
       <x:c r="S41" s="3"/>
       <x:c r="T41" s="3"/>
-      <x:c r="U41" s="1"/>
+      <x:c r="U41" s="1" t="str">
+        <x:v>0.003</x:v>
+      </x:c>
       <x:c r="V41" s="1" t="str">
         <x:v>mmol/L·h (as printed)</x:v>
       </x:c>
       <x:c r="W41" s="1"/>
       <x:c r="X41" s="1"/>
       <x:c r="Y41" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_figure</x:v>
       </x:c>
       <x:c r="Z41" s="1" t="str">
-        <x:v>Gibbs_2014; PDF p4; Figure 2</x:v>
+        <x:v>Gibbs_2014_primary; PDF p4; Figure 2 numeric labels and Results</x:v>
       </x:c>
       <x:c r="AA41" s="1" t="str">
         <x:v>Unit label/scale requires QA.</x:v>
@@ -8086,10 +7901,10 @@
       <x:c r="W44" s="1"/>
       <x:c r="X44" s="1"/>
       <x:c r="Y44" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_figure</x:v>
       </x:c>
       <x:c r="Z44" s="1" t="str">
-        <x:v>Gibbs_2014; PDF p4; Figure 2</x:v>
+        <x:v>Gibbs_2014_primary; PDF p4; Figure 2 numeric labels and Results</x:v>
       </x:c>
       <x:c r="AA44" s="1"/>
     </x:row>
@@ -8148,17 +7963,19 @@
       </x:c>
       <x:c r="S45" s="3"/>
       <x:c r="T45" s="3"/>
-      <x:c r="U45" s="1"/>
+      <x:c r="U45" s="1" t="str">
+        <x:v>0.003</x:v>
+      </x:c>
       <x:c r="V45" s="1" t="str">
         <x:v>mmol/L·h (as printed)</x:v>
       </x:c>
       <x:c r="W45" s="1"/>
       <x:c r="X45" s="1"/>
       <x:c r="Y45" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_figure</x:v>
       </x:c>
       <x:c r="Z45" s="1" t="str">
-        <x:v>Gibbs_2014; PDF p4; Figure 2</x:v>
+        <x:v>Gibbs_2014_primary; PDF p4; Figure 2 numeric labels and Results</x:v>
       </x:c>
       <x:c r="AA45" s="1" t="str">
         <x:v>Unit label/scale requires QA.</x:v>
@@ -8358,10 +8175,10 @@
       <x:c r="W48" s="1"/>
       <x:c r="X48" s="1"/>
       <x:c r="Y48" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_figure</x:v>
       </x:c>
       <x:c r="Z48" s="1" t="str">
-        <x:v>Gibbs_2014; PDF p4; Figure 2</x:v>
+        <x:v>Gibbs_2014_primary; PDF p4; Figure 2 numeric labels and Results</x:v>
       </x:c>
       <x:c r="AA48" s="1"/>
     </x:row>
@@ -8425,10 +8242,10 @@
       <x:c r="W49" s="1"/>
       <x:c r="X49" s="1"/>
       <x:c r="Y49" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_text</x:v>
       </x:c>
       <x:c r="Z49" s="1" t="str">
-        <x:v>Gu_2020; PDF p5; Results</x:v>
+        <x:v>Gu_2020_primary; PDF p5; Results</x:v>
       </x:c>
       <x:c r="AA49" s="1"/>
     </x:row>
@@ -8492,10 +8309,10 @@
       <x:c r="W50" s="1"/>
       <x:c r="X50" s="1"/>
       <x:c r="Y50" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_text</x:v>
       </x:c>
       <x:c r="Z50" s="1" t="str">
-        <x:v>Gu_2020; PDF p5; Results</x:v>
+        <x:v>Gu_2020_primary; PDF p5; Results</x:v>
       </x:c>
       <x:c r="AA50" s="1"/>
     </x:row>
@@ -8555,10 +8372,10 @@
       <x:c r="W51" s="1"/>
       <x:c r="X51" s="1"/>
       <x:c r="Y51" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_text</x:v>
       </x:c>
       <x:c r="Z51" s="1" t="str">
-        <x:v>Gu_2020; PDF p5; Results</x:v>
+        <x:v>Gu_2020_primary; PDF p5; Results</x:v>
       </x:c>
       <x:c r="AA51" s="1"/>
     </x:row>
@@ -8618,10 +8435,10 @@
       <x:c r="W52" s="1"/>
       <x:c r="X52" s="1"/>
       <x:c r="Y52" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_text</x:v>
       </x:c>
       <x:c r="Z52" s="1" t="str">
-        <x:v>Gu_2020; PDF p5; Results</x:v>
+        <x:v>Gu_2020_primary; PDF p5; Results</x:v>
       </x:c>
       <x:c r="AA52" s="1"/>
     </x:row>
@@ -8687,10 +8504,10 @@
       </x:c>
       <x:c r="X53" s="1"/>
       <x:c r="Y53" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_text</x:v>
       </x:c>
       <x:c r="Z53" s="1" t="str">
-        <x:v>Gu_2020; PDF p5; Results</x:v>
+        <x:v>Gu_2020_primary; PDF p11; Table 4</x:v>
       </x:c>
       <x:c r="AA53" s="1"/>
     </x:row>
@@ -12137,10 +11954,10 @@
       <x:c r="W105" s="1"/>
       <x:c r="X105" s="1"/>
       <x:c r="Y105" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_text</x:v>
       </x:c>
       <x:c r="Z105" s="1" t="str">
-        <x:v>Lopez_Minguez_2018; PDF p6; Results/Table</x:v>
+        <x:v>Lopez_Minguez_2018_primary; PDF p7; Results</x:v>
       </x:c>
       <x:c r="AA105" s="1"/>
     </x:row>
@@ -12206,10 +12023,10 @@
       <x:c r="W106" s="1"/>
       <x:c r="X106" s="1"/>
       <x:c r="Y106" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_text</x:v>
       </x:c>
       <x:c r="Z106" s="1" t="str">
-        <x:v>Lopez_Minguez_2018; PDF p6; Results/Table</x:v>
+        <x:v>Lopez_Minguez_2018_primary; PDF p7; Results</x:v>
       </x:c>
       <x:c r="AA106" s="1"/>
     </x:row>
@@ -12274,7 +12091,7 @@
         <x:v>derived</x:v>
       </x:c>
       <x:c r="Z107" s="1" t="str">
-        <x:v>Lopez_Minguez_2018; PDF p6; Results</x:v>
+        <x:v>Lopez_Minguez_2018_primary; PDF p7; Results</x:v>
       </x:c>
       <x:c r="AA107" s="1" t="str">
         <x:v>Paired SE derived separately from exact p; unit label requires QA.</x:v>
@@ -12342,10 +12159,10 @@
       <x:c r="W108" s="1"/>
       <x:c r="X108" s="1"/>
       <x:c r="Y108" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_text</x:v>
       </x:c>
       <x:c r="Z108" s="1" t="str">
-        <x:v>Lopez_Minguez_2018; PDF p6; Results/Table</x:v>
+        <x:v>Lopez_Minguez_2018_primary; PDF p7; Results</x:v>
       </x:c>
       <x:c r="AA108" s="1"/>
     </x:row>
@@ -12411,10 +12228,10 @@
       <x:c r="W109" s="1"/>
       <x:c r="X109" s="1"/>
       <x:c r="Y109" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_text</x:v>
       </x:c>
       <x:c r="Z109" s="1" t="str">
-        <x:v>Lopez_Minguez_2018; PDF p6; Results/Table</x:v>
+        <x:v>Lopez_Minguez_2018_primary; PDF p7; Results</x:v>
       </x:c>
       <x:c r="AA109" s="1"/>
     </x:row>
@@ -12479,7 +12296,7 @@
         <x:v>reported_text</x:v>
       </x:c>
       <x:c r="Z110" s="1" t="str">
-        <x:v>Lopez_Minguez_2018; PDF p6; Results</x:v>
+        <x:v>Lopez_Minguez_2018_primary; PDF p7; Results</x:v>
       </x:c>
       <x:c r="AA110" s="1" t="str">
         <x:v>No paired precision derived for subgroup.</x:v>
@@ -12547,10 +12364,10 @@
       <x:c r="W111" s="1"/>
       <x:c r="X111" s="1"/>
       <x:c r="Y111" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_text</x:v>
       </x:c>
       <x:c r="Z111" s="1" t="str">
-        <x:v>Lopez_Minguez_2018; PDF p6; Results/Table</x:v>
+        <x:v>Lopez_Minguez_2018_primary; PDF p7; Results</x:v>
       </x:c>
       <x:c r="AA111" s="1"/>
     </x:row>
@@ -12616,10 +12433,10 @@
       <x:c r="W112" s="1"/>
       <x:c r="X112" s="1"/>
       <x:c r="Y112" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_text</x:v>
       </x:c>
       <x:c r="Z112" s="1" t="str">
-        <x:v>Lopez_Minguez_2018; PDF p6; Results/Table</x:v>
+        <x:v>Lopez_Minguez_2018_primary; PDF p7; Results</x:v>
       </x:c>
       <x:c r="AA112" s="1"/>
     </x:row>
@@ -12684,7 +12501,7 @@
         <x:v>reported_text</x:v>
       </x:c>
       <x:c r="Z113" s="1" t="str">
-        <x:v>Lopez_Minguez_2018; PDF p6; Results</x:v>
+        <x:v>Lopez_Minguez_2018_primary; PDF p7; Results</x:v>
       </x:c>
       <x:c r="AA113" s="1" t="str">
         <x:v>No paired precision derived for subgroup.</x:v>
@@ -16275,17 +16092,19 @@
       </x:c>
       <x:c r="S166" s="3"/>
       <x:c r="T166" s="3"/>
-      <x:c r="U166" s="1"/>
+      <x:c r="U166" s="1" t="str">
+        <x:v>0.11 (meal main effect)</x:v>
+      </x:c>
       <x:c r="V166" s="1" t="str">
         <x:v>mg/dL×180 min</x:v>
       </x:c>
       <x:c r="W166" s="1"/>
       <x:c r="X166" s="1"/>
       <x:c r="Y166" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_text</x:v>
       </x:c>
       <x:c r="Z166" s="1" t="str">
-        <x:v>Pizinger_2018; PDF pp4–5; Results</x:v>
+        <x:v>Pizinger_2018_primary; PDF pp3–5; Results</x:v>
       </x:c>
       <x:c r="AA166" s="1"/>
     </x:row>
@@ -16344,17 +16163,19 @@
       </x:c>
       <x:c r="S167" s="3"/>
       <x:c r="T167" s="3"/>
-      <x:c r="U167" s="1"/>
+      <x:c r="U167" s="1" t="str">
+        <x:v>0.0088 (meal main effect)</x:v>
+      </x:c>
       <x:c r="V167" s="1" t="str">
         <x:v>µU/mL or µU/dL ×180 min (report inconsistent)</x:v>
       </x:c>
       <x:c r="W167" s="1"/>
       <x:c r="X167" s="1"/>
       <x:c r="Y167" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_text</x:v>
       </x:c>
       <x:c r="Z167" s="1" t="str">
-        <x:v>Pizinger_2018; PDF pp4–5; Results</x:v>
+        <x:v>Pizinger_2018_primary; PDF pp3–5; Results</x:v>
       </x:c>
       <x:c r="AA167" s="1" t="str">
         <x:v>Concentration denominator differs across page break; flagged.</x:v>
@@ -16415,17 +16236,19 @@
       </x:c>
       <x:c r="S168" s="3"/>
       <x:c r="T168" s="3"/>
-      <x:c r="U168" s="1"/>
+      <x:c r="U168" s="1" t="str">
+        <x:v>0.11 (meal main effect)</x:v>
+      </x:c>
       <x:c r="V168" s="1" t="str">
         <x:v>mg/dL×180 min</x:v>
       </x:c>
       <x:c r="W168" s="1"/>
       <x:c r="X168" s="1"/>
       <x:c r="Y168" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_text</x:v>
       </x:c>
       <x:c r="Z168" s="1" t="str">
-        <x:v>Pizinger_2018; PDF pp4–5; Results</x:v>
+        <x:v>Pizinger_2018_primary; PDF pp3–5; Results</x:v>
       </x:c>
       <x:c r="AA168" s="1"/>
     </x:row>
@@ -16484,17 +16307,19 @@
       </x:c>
       <x:c r="S169" s="3"/>
       <x:c r="T169" s="3"/>
-      <x:c r="U169" s="1"/>
+      <x:c r="U169" s="1" t="str">
+        <x:v>0.0088 (meal main effect)</x:v>
+      </x:c>
       <x:c r="V169" s="1" t="str">
         <x:v>µU/mL or µU/dL ×180 min (report inconsistent)</x:v>
       </x:c>
       <x:c r="W169" s="1"/>
       <x:c r="X169" s="1"/>
       <x:c r="Y169" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_text</x:v>
       </x:c>
       <x:c r="Z169" s="1" t="str">
-        <x:v>Pizinger_2018; PDF pp4–5; Results</x:v>
+        <x:v>Pizinger_2018_primary; PDF pp3–5; Results</x:v>
       </x:c>
       <x:c r="AA169" s="1" t="str">
         <x:v>Concentration denominator differs across page break; flagged.</x:v>
@@ -16555,17 +16380,19 @@
       </x:c>
       <x:c r="S170" s="3"/>
       <x:c r="T170" s="3"/>
-      <x:c r="U170" s="1"/>
+      <x:c r="U170" s="1" t="str">
+        <x:v>0.11 (meal main effect)</x:v>
+      </x:c>
       <x:c r="V170" s="1" t="str">
         <x:v>mg/dL×180 min</x:v>
       </x:c>
       <x:c r="W170" s="1"/>
       <x:c r="X170" s="1"/>
       <x:c r="Y170" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_text</x:v>
       </x:c>
       <x:c r="Z170" s="1" t="str">
-        <x:v>Pizinger_2018; PDF pp4–5; Results</x:v>
+        <x:v>Pizinger_2018_primary; PDF pp3–5; Results</x:v>
       </x:c>
       <x:c r="AA170" s="1"/>
     </x:row>
@@ -16624,17 +16451,19 @@
       </x:c>
       <x:c r="S171" s="3"/>
       <x:c r="T171" s="3"/>
-      <x:c r="U171" s="1"/>
+      <x:c r="U171" s="1" t="str">
+        <x:v>0.0088 (meal main effect)</x:v>
+      </x:c>
       <x:c r="V171" s="1" t="str">
         <x:v>µU/mL or µU/dL ×180 min (report inconsistent)</x:v>
       </x:c>
       <x:c r="W171" s="1"/>
       <x:c r="X171" s="1"/>
       <x:c r="Y171" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_text</x:v>
       </x:c>
       <x:c r="Z171" s="1" t="str">
-        <x:v>Pizinger_2018; PDF pp4–5; Results</x:v>
+        <x:v>Pizinger_2018_primary; PDF pp3–5; Results</x:v>
       </x:c>
       <x:c r="AA171" s="1" t="str">
         <x:v>Concentration denominator differs across page break; flagged.</x:v>
@@ -16695,17 +16524,19 @@
       </x:c>
       <x:c r="S172" s="3"/>
       <x:c r="T172" s="3"/>
-      <x:c r="U172" s="1"/>
+      <x:c r="U172" s="1" t="str">
+        <x:v>0.11 (meal main effect)</x:v>
+      </x:c>
       <x:c r="V172" s="1" t="str">
         <x:v>mg/dL×180 min</x:v>
       </x:c>
       <x:c r="W172" s="1"/>
       <x:c r="X172" s="1"/>
       <x:c r="Y172" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_text</x:v>
       </x:c>
       <x:c r="Z172" s="1" t="str">
-        <x:v>Pizinger_2018; PDF pp4–5; Results</x:v>
+        <x:v>Pizinger_2018_primary; PDF pp3–5; Results</x:v>
       </x:c>
       <x:c r="AA172" s="1"/>
     </x:row>
@@ -16764,17 +16595,19 @@
       </x:c>
       <x:c r="S173" s="3"/>
       <x:c r="T173" s="3"/>
-      <x:c r="U173" s="1"/>
+      <x:c r="U173" s="1" t="str">
+        <x:v>0.0088 (meal main effect)</x:v>
+      </x:c>
       <x:c r="V173" s="1" t="str">
         <x:v>µU/mL or µU/dL ×180 min (report inconsistent)</x:v>
       </x:c>
       <x:c r="W173" s="1"/>
       <x:c r="X173" s="1"/>
       <x:c r="Y173" s="1" t="str">
-        <x:v>reported_table</x:v>
+        <x:v>reported_text</x:v>
       </x:c>
       <x:c r="Z173" s="1" t="str">
-        <x:v>Pizinger_2018; PDF pp4–5; Results</x:v>
+        <x:v>Pizinger_2018_primary; PDF pp3–5; Results</x:v>
       </x:c>
       <x:c r="AA173" s="1" t="str">
         <x:v>Concentration denominator differs across page break; flagged.</x:v>
@@ -16833,7 +16666,9 @@
       </x:c>
       <x:c r="S174" s="3"/>
       <x:c r="T174" s="3"/>
-      <x:c r="U174" s="1"/>
+      <x:c r="U174" s="1" t="str">
+        <x:v>&lt;0.05</x:v>
+      </x:c>
       <x:c r="V174" s="1" t="str">
         <x:v>mg/dL×min</x:v>
       </x:c>
@@ -16843,7 +16678,7 @@
         <x:v>reported_table</x:v>
       </x:c>
       <x:c r="Z174" s="1" t="str">
-        <x:v>Sato_2011; PDF p5; Results/Figure</x:v>
+        <x:v>Sato_2011_primary; PDF pp4–5; Results and Table 1</x:v>
       </x:c>
       <x:c r="AA174" s="1"/>
     </x:row>
@@ -16896,7 +16731,9 @@
       </x:c>
       <x:c r="S175" s="3"/>
       <x:c r="T175" s="3"/>
-      <x:c r="U175" s="1"/>
+      <x:c r="U175" s="1" t="n">
+        <x:v>0.098</x:v>
+      </x:c>
       <x:c r="V175" s="1" t="str">
         <x:v>mg/dL</x:v>
       </x:c>
@@ -16906,7 +16743,7 @@
         <x:v>reported_table</x:v>
       </x:c>
       <x:c r="Z175" s="1" t="str">
-        <x:v>Sato_2011; PDF p5; Results</x:v>
+        <x:v>Sato_2011_primary; PDF pp4–5; Results and Table 1</x:v>
       </x:c>
       <x:c r="AA175" s="1"/>
     </x:row>
@@ -16959,7 +16796,9 @@
       </x:c>
       <x:c r="S176" s="3"/>
       <x:c r="T176" s="3"/>
-      <x:c r="U176" s="1"/>
+      <x:c r="U176" s="1" t="str">
+        <x:v>&lt;0.01</x:v>
+      </x:c>
       <x:c r="V176" s="1" t="str">
         <x:v>min</x:v>
       </x:c>
@@ -16969,7 +16808,7 @@
         <x:v>reported_table</x:v>
       </x:c>
       <x:c r="Z176" s="1" t="str">
-        <x:v>Sato_2011; PDF p5; Results</x:v>
+        <x:v>Sato_2011_primary; PDF pp4–5; Results and Table 1</x:v>
       </x:c>
       <x:c r="AA176" s="1"/>
     </x:row>
@@ -17022,7 +16861,9 @@
       </x:c>
       <x:c r="S177" s="3"/>
       <x:c r="T177" s="3"/>
-      <x:c r="U177" s="1"/>
+      <x:c r="U177" s="1" t="str">
+        <x:v>&lt;0.05</x:v>
+      </x:c>
       <x:c r="V177" s="1" t="str">
         <x:v>mg/dL</x:v>
       </x:c>
@@ -17032,7 +16873,7 @@
         <x:v>reported_table</x:v>
       </x:c>
       <x:c r="Z177" s="1" t="str">
-        <x:v>Sato_2011; PDF p5; Results</x:v>
+        <x:v>Sato_2011_primary; PDF pp4–5; Results and Table 1</x:v>
       </x:c>
       <x:c r="AA177" s="1"/>
     </x:row>
@@ -17089,7 +16930,9 @@
       </x:c>
       <x:c r="S178" s="3"/>
       <x:c r="T178" s="3"/>
-      <x:c r="U178" s="1"/>
+      <x:c r="U178" s="1" t="str">
+        <x:v>&lt;0.05</x:v>
+      </x:c>
       <x:c r="V178" s="1" t="str">
         <x:v>mg/dL×min</x:v>
       </x:c>
@@ -17099,7 +16942,7 @@
         <x:v>reported_table</x:v>
       </x:c>
       <x:c r="Z178" s="1" t="str">
-        <x:v>Sato_2011; PDF p5; Results/Figure</x:v>
+        <x:v>Sato_2011_primary; PDF pp4–5; Results and Table 1</x:v>
       </x:c>
       <x:c r="AA178" s="1"/>
     </x:row>
@@ -17152,7 +16995,9 @@
       </x:c>
       <x:c r="S179" s="3"/>
       <x:c r="T179" s="3"/>
-      <x:c r="U179" s="1"/>
+      <x:c r="U179" s="1" t="n">
+        <x:v>0.098</x:v>
+      </x:c>
       <x:c r="V179" s="1" t="str">
         <x:v>mg/dL</x:v>
       </x:c>
@@ -17162,7 +17007,7 @@
         <x:v>reported_table</x:v>
       </x:c>
       <x:c r="Z179" s="1" t="str">
-        <x:v>Sato_2011; PDF p5; Results</x:v>
+        <x:v>Sato_2011_primary; PDF pp4–5; Results and Table 1</x:v>
       </x:c>
       <x:c r="AA179" s="1"/>
     </x:row>
@@ -17215,7 +17060,9 @@
       </x:c>
       <x:c r="S180" s="3"/>
       <x:c r="T180" s="3"/>
-      <x:c r="U180" s="1"/>
+      <x:c r="U180" s="1" t="str">
+        <x:v>&lt;0.01</x:v>
+      </x:c>
       <x:c r="V180" s="1" t="str">
         <x:v>min</x:v>
       </x:c>
@@ -17225,7 +17072,7 @@
         <x:v>reported_table</x:v>
       </x:c>
       <x:c r="Z180" s="1" t="str">
-        <x:v>Sato_2011; PDF p5; Results</x:v>
+        <x:v>Sato_2011_primary; PDF pp4–5; Results and Table 1</x:v>
       </x:c>
       <x:c r="AA180" s="1"/>
     </x:row>
@@ -17278,7 +17125,9 @@
       </x:c>
       <x:c r="S181" s="3"/>
       <x:c r="T181" s="3"/>
-      <x:c r="U181" s="1"/>
+      <x:c r="U181" s="1" t="str">
+        <x:v>&lt;0.05</x:v>
+      </x:c>
       <x:c r="V181" s="1" t="str">
         <x:v>mg/dL</x:v>
       </x:c>
@@ -17288,7 +17137,7 @@
         <x:v>reported_table</x:v>
       </x:c>
       <x:c r="Z181" s="1" t="str">
-        <x:v>Sato_2011; PDF p5; Results</x:v>
+        <x:v>Sato_2011_primary; PDF pp4–5; Results and Table 1</x:v>
       </x:c>
       <x:c r="AA181" s="1"/>
     </x:row>
@@ -17347,7 +17196,9 @@
       </x:c>
       <x:c r="S182" s="3"/>
       <x:c r="T182" s="3"/>
-      <x:c r="U182" s="1"/>
+      <x:c r="U182" s="1" t="str">
+        <x:v>&lt;0.01</x:v>
+      </x:c>
       <x:c r="V182" s="1" t="str">
         <x:v>mg/dL×min</x:v>
       </x:c>
@@ -17357,7 +17208,7 @@
         <x:v>reported_table</x:v>
       </x:c>
       <x:c r="Z182" s="1" t="str">
-        <x:v>Sato_2011; PDF p5; Results</x:v>
+        <x:v>Sato_2011_primary; PDF pp4–5; Results and Table 1</x:v>
       </x:c>
       <x:c r="AA182" s="1"/>
     </x:row>
@@ -17416,7 +17267,9 @@
       </x:c>
       <x:c r="S183" s="3"/>
       <x:c r="T183" s="3"/>
-      <x:c r="U183" s="1"/>
+      <x:c r="U183" s="1" t="str">
+        <x:v>&lt;0.01</x:v>
+      </x:c>
       <x:c r="V183" s="1" t="str">
         <x:v>mg/dL×min</x:v>
       </x:c>
@@ -17426,7 +17279,7 @@
         <x:v>reported_table</x:v>
       </x:c>
       <x:c r="Z183" s="1" t="str">
-        <x:v>Sato_2011; PDF p5; Results</x:v>
+        <x:v>Sato_2011_primary; PDF pp4–5; Results and Table 1</x:v>
       </x:c>
       <x:c r="AA183" s="1"/>
     </x:row>
@@ -22785,30 +22638,32 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="P262" s="3" t="n">
-        <x:v>190</x:v>
+        <x:v>196.344285714286</x:v>
       </x:c>
       <x:c r="Q262" s="3" t="str">
         <x:v>SD</x:v>
       </x:c>
       <x:c r="R262" s="3" t="n">
-        <x:v>65</x:v>
+        <x:v>66.4976272236358</x:v>
       </x:c>
       <x:c r="S262" s="3"/>
       <x:c r="T262" s="3"/>
-      <x:c r="U262" s="1"/>
+      <x:c r="U262" s="1" t="str">
+        <x:v>&lt;0.01 (published timing comparison)</x:v>
+      </x:c>
       <x:c r="V262" s="1" t="str">
-        <x:v>mmol/L×min</x:v>
+        <x:v>mmol/L×min (source-inferred)</x:v>
       </x:c>
       <x:c r="W262" s="1"/>
       <x:c r="X262" s="1"/>
       <x:c r="Y262" s="1" t="str">
-        <x:v>graph_digitized</x:v>
+        <x:v>author_provided</x:v>
       </x:c>
       <x:c r="Z262" s="1" t="str">
-        <x:v>Sulaimani_2025; PDF p6; Figure 3B</x:v>
+        <x:v>Sulaimani_2025; author-provided iAUC-glucose worksheet; PDF p6, Figure 3B</x:v>
       </x:c>
       <x:c r="AA262" s="1" t="str">
-        <x:v>Approximate graph digitization; rounded to graph resolution.</x:v>
+        <x:v>Aggregate of 14 author-provided participant iAUCs; 180-min window and mmol/L×min scale inferred from Methods/Figure 3B.</x:v>
       </x:c>
     </x:row>
     <x:row r="263" ht="100" customHeight="1">
@@ -22862,7 +22717,9 @@
       </x:c>
       <x:c r="S263" s="3"/>
       <x:c r="T263" s="3"/>
-      <x:c r="U263" s="1"/>
+      <x:c r="U263" s="1" t="str">
+        <x:v>0.07 (timing main effect)</x:v>
+      </x:c>
       <x:c r="V263" s="1" t="str">
         <x:v>mmol/L</x:v>
       </x:c>
@@ -22872,7 +22729,7 @@
         <x:v>graph_digitized</x:v>
       </x:c>
       <x:c r="Z263" s="1" t="str">
-        <x:v>Sulaimani_2025; PDF p6; Figure 3C</x:v>
+        <x:v>Sulaimani_2025_primary; PDF pp6–7; Figures 3–4</x:v>
       </x:c>
       <x:c r="AA263" s="1" t="str">
         <x:v>Approximate graph digitization.</x:v>
@@ -22943,7 +22800,7 @@
         <x:v>graph_digitized</x:v>
       </x:c>
       <x:c r="Z264" s="1" t="str">
-        <x:v>Sulaimani_2025; PDF p7; Figure 4B</x:v>
+        <x:v>Sulaimani_2025_primary; PDF pp6–7; Figures 3–4</x:v>
       </x:c>
       <x:c r="AA264" s="1" t="str">
         <x:v>Approximate graph digitization.</x:v>
@@ -23000,7 +22857,9 @@
       </x:c>
       <x:c r="S265"/>
       <x:c r="T265"/>
-      <x:c r="U265"/>
+      <x:c r="U265" t="n">
+        <x:v>0.0002</x:v>
+      </x:c>
       <x:c r="V265" t="str">
         <x:v>pmol/L</x:v>
       </x:c>
@@ -23010,7 +22869,7 @@
         <x:v>graph_digitized</x:v>
       </x:c>
       <x:c r="Z265" t="str">
-        <x:v>Sulaimani_2025; PDF p7; Figure 4C</x:v>
+        <x:v>Sulaimani_2025_primary; PDF pp6–7; Figures 3–4</x:v>
       </x:c>
       <x:c r="AA265" t="str">
         <x:v>Approximate graph digitization.</x:v>
@@ -23061,30 +22920,32 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="P266" t="n">
-        <x:v>180</x:v>
+        <x:v>182.851428571429</x:v>
       </x:c>
       <x:c r="Q266" t="str">
         <x:v>SD</x:v>
       </x:c>
       <x:c r="R266" t="n">
-        <x:v>80</x:v>
+        <x:v>64.2224026162382</x:v>
       </x:c>
       <x:c r="S266"/>
       <x:c r="T266"/>
-      <x:c r="U266"/>
+      <x:c r="U266" t="str">
+        <x:v>&lt;0.01 (published timing comparison)</x:v>
+      </x:c>
       <x:c r="V266" t="str">
-        <x:v>mmol/L×min</x:v>
+        <x:v>mmol/L×min (source-inferred)</x:v>
       </x:c>
       <x:c r="W266"/>
       <x:c r="X266"/>
       <x:c r="Y266" t="str">
-        <x:v>graph_digitized</x:v>
+        <x:v>author_provided</x:v>
       </x:c>
       <x:c r="Z266" t="str">
-        <x:v>Sulaimani_2025; PDF p6; Figure 3B</x:v>
+        <x:v>Sulaimani_2025; author-provided iAUC-glucose worksheet; PDF p6, Figure 3B</x:v>
       </x:c>
       <x:c r="AA266" t="str">
-        <x:v>Approximate graph digitization; rounded to graph resolution.</x:v>
+        <x:v>Aggregate of 14 author-provided participant iAUCs; 180-min window and mmol/L×min scale inferred from Methods/Figure 3B.</x:v>
       </x:c>
     </x:row>
     <x:row r="267">
@@ -23138,7 +22999,9 @@
       </x:c>
       <x:c r="S267"/>
       <x:c r="T267"/>
-      <x:c r="U267"/>
+      <x:c r="U267" t="str">
+        <x:v>0.07 (timing main effect)</x:v>
+      </x:c>
       <x:c r="V267" t="str">
         <x:v>mmol/L</x:v>
       </x:c>
@@ -23148,7 +23011,7 @@
         <x:v>graph_digitized</x:v>
       </x:c>
       <x:c r="Z267" t="str">
-        <x:v>Sulaimani_2025; PDF p6; Figure 3C</x:v>
+        <x:v>Sulaimani_2025_primary; PDF pp6–7; Figures 3–4</x:v>
       </x:c>
       <x:c r="AA267" t="str">
         <x:v>Approximate graph digitization.</x:v>
@@ -23219,7 +23082,7 @@
         <x:v>graph_digitized</x:v>
       </x:c>
       <x:c r="Z268" t="str">
-        <x:v>Sulaimani_2025; PDF p7; Figure 4B</x:v>
+        <x:v>Sulaimani_2025_primary; PDF pp6–7; Figures 3–4</x:v>
       </x:c>
       <x:c r="AA268" t="str">
         <x:v>Approximate graph digitization.</x:v>
@@ -23266,30 +23129,32 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="P269" t="n">
-        <x:v>610</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="Q269" t="str">
         <x:v>SD</x:v>
       </x:c>
       <x:c r="R269" t="n">
-        <x:v>400</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="S269"/>
       <x:c r="T269"/>
-      <x:c r="U269"/>
+      <x:c r="U269" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
       <x:c r="V269" t="str">
         <x:v>pmol/L</x:v>
       </x:c>
       <x:c r="W269"/>
       <x:c r="X269"/>
       <x:c r="Y269" t="str">
-        <x:v>graph_digitized</x:v>
+        <x:v>reported_text</x:v>
       </x:c>
       <x:c r="Z269" t="str">
-        <x:v>Sulaimani_2025; PDF p7; Figure 4C</x:v>
+        <x:v>Sulaimani_2025_primary; PDF p1; Abstract</x:v>
       </x:c>
       <x:c r="AA269" t="str">
-        <x:v>Approximate graph digitization.</x:v>
+        <x:v>Abstract reports peak insulin at 30 min after morning GTE meal as 629 ± 313 pmol/L; replaces approximate figure read.</x:v>
       </x:c>
     </x:row>
     <x:row r="270">
@@ -23337,30 +23202,32 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="P270" t="n">
-        <x:v>355</x:v>
+        <x:v>359.952142857143</x:v>
       </x:c>
       <x:c r="Q270" t="str">
         <x:v>SD</x:v>
       </x:c>
       <x:c r="R270" t="n">
-        <x:v>145</x:v>
+        <x:v>141.379139369644</x:v>
       </x:c>
       <x:c r="S270"/>
       <x:c r="T270"/>
-      <x:c r="U270"/>
+      <x:c r="U270" t="str">
+        <x:v>&lt;0.01 (published timing comparison)</x:v>
+      </x:c>
       <x:c r="V270" t="str">
-        <x:v>mmol/L×min</x:v>
+        <x:v>mmol/L×min (source-inferred)</x:v>
       </x:c>
       <x:c r="W270"/>
       <x:c r="X270"/>
       <x:c r="Y270" t="str">
-        <x:v>graph_digitized</x:v>
+        <x:v>author_provided</x:v>
       </x:c>
       <x:c r="Z270" t="str">
-        <x:v>Sulaimani_2025; PDF p6; Figure 3B</x:v>
+        <x:v>Sulaimani_2025; author-provided iAUC-glucose worksheet; PDF p6, Figure 3B</x:v>
       </x:c>
       <x:c r="AA270" t="str">
-        <x:v>Approximate graph digitization; rounded to graph resolution.</x:v>
+        <x:v>Aggregate of 14 author-provided participant iAUCs; 180-min window and mmol/L×min scale inferred from Methods/Figure 3B.</x:v>
       </x:c>
     </x:row>
     <x:row r="271">
@@ -23414,7 +23281,9 @@
       </x:c>
       <x:c r="S271"/>
       <x:c r="T271"/>
-      <x:c r="U271"/>
+      <x:c r="U271" t="str">
+        <x:v>0.07 (timing main effect)</x:v>
+      </x:c>
       <x:c r="V271" t="str">
         <x:v>mmol/L</x:v>
       </x:c>
@@ -23424,7 +23293,7 @@
         <x:v>graph_digitized</x:v>
       </x:c>
       <x:c r="Z271" t="str">
-        <x:v>Sulaimani_2025; PDF p6; Figure 3C</x:v>
+        <x:v>Sulaimani_2025_primary; PDF pp6–7; Figures 3–4</x:v>
       </x:c>
       <x:c r="AA271" t="str">
         <x:v>Approximate graph digitization.</x:v>
@@ -23495,7 +23364,7 @@
         <x:v>graph_digitized</x:v>
       </x:c>
       <x:c r="Z272" t="str">
-        <x:v>Sulaimani_2025; PDF p7; Figure 4B</x:v>
+        <x:v>Sulaimani_2025_primary; PDF pp6–7; Figures 3–4</x:v>
       </x:c>
       <x:c r="AA272" t="str">
         <x:v>Approximate graph digitization.</x:v>
@@ -23552,7 +23421,9 @@
       </x:c>
       <x:c r="S273"/>
       <x:c r="T273"/>
-      <x:c r="U273"/>
+      <x:c r="U273" t="n">
+        <x:v>0.0002</x:v>
+      </x:c>
       <x:c r="V273" t="str">
         <x:v>pmol/L</x:v>
       </x:c>
@@ -23562,7 +23433,7 @@
         <x:v>graph_digitized</x:v>
       </x:c>
       <x:c r="Z273" t="str">
-        <x:v>Sulaimani_2025; PDF p7; Figure 4C</x:v>
+        <x:v>Sulaimani_2025_primary; PDF pp6–7; Figures 3–4</x:v>
       </x:c>
       <x:c r="AA273" t="str">
         <x:v>Approximate graph digitization.</x:v>
@@ -23613,30 +23484,32 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="P274" t="n">
-        <x:v>380</x:v>
+        <x:v>385.2</x:v>
       </x:c>
       <x:c r="Q274" t="str">
         <x:v>SD</x:v>
       </x:c>
       <x:c r="R274" t="n">
-        <x:v>150</x:v>
+        <x:v>141.575185244177</x:v>
       </x:c>
       <x:c r="S274"/>
       <x:c r="T274"/>
-      <x:c r="U274"/>
+      <x:c r="U274" t="str">
+        <x:v>&lt;0.01 (published timing comparison)</x:v>
+      </x:c>
       <x:c r="V274" t="str">
-        <x:v>mmol/L×min</x:v>
+        <x:v>mmol/L×min (source-inferred)</x:v>
       </x:c>
       <x:c r="W274"/>
       <x:c r="X274"/>
       <x:c r="Y274" t="str">
-        <x:v>graph_digitized</x:v>
+        <x:v>author_provided</x:v>
       </x:c>
       <x:c r="Z274" t="str">
-        <x:v>Sulaimani_2025; PDF p6; Figure 3B</x:v>
+        <x:v>Sulaimani_2025; author-provided iAUC-glucose worksheet; PDF p6, Figure 3B</x:v>
       </x:c>
       <x:c r="AA274" t="str">
-        <x:v>Approximate graph digitization; rounded to graph resolution.</x:v>
+        <x:v>Aggregate of 14 author-provided participant iAUCs; 180-min window and mmol/L×min scale inferred from Methods/Figure 3B.</x:v>
       </x:c>
     </x:row>
     <x:row r="275">
@@ -23690,7 +23563,9 @@
       </x:c>
       <x:c r="S275"/>
       <x:c r="T275"/>
-      <x:c r="U275"/>
+      <x:c r="U275" t="str">
+        <x:v>0.07 (timing main effect)</x:v>
+      </x:c>
       <x:c r="V275" t="str">
         <x:v>mmol/L</x:v>
       </x:c>
@@ -23700,7 +23575,7 @@
         <x:v>graph_digitized</x:v>
       </x:c>
       <x:c r="Z275" t="str">
-        <x:v>Sulaimani_2025; PDF p6; Figure 3C</x:v>
+        <x:v>Sulaimani_2025_primary; PDF pp6–7; Figures 3–4</x:v>
       </x:c>
       <x:c r="AA275" t="str">
         <x:v>Approximate graph digitization.</x:v>
@@ -23771,7 +23646,7 @@
         <x:v>graph_digitized</x:v>
       </x:c>
       <x:c r="Z276" t="str">
-        <x:v>Sulaimani_2025; PDF p7; Figure 4B</x:v>
+        <x:v>Sulaimani_2025_primary; PDF pp6–7; Figures 3–4</x:v>
       </x:c>
       <x:c r="AA276" t="str">
         <x:v>Approximate graph digitization.</x:v>
@@ -23828,7 +23703,9 @@
       </x:c>
       <x:c r="S277"/>
       <x:c r="T277"/>
-      <x:c r="U277"/>
+      <x:c r="U277" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
       <x:c r="V277" t="str">
         <x:v>pmol/L</x:v>
       </x:c>
@@ -23838,10 +23715,6438 @@
         <x:v>graph_digitized</x:v>
       </x:c>
       <x:c r="Z277" t="str">
-        <x:v>Sulaimani_2025; PDF p7; Figure 4C</x:v>
+        <x:v>Sulaimani_2025_primary; PDF pp6–7; Figures 3–4</x:v>
       </x:c>
       <x:c r="AA277" t="str">
         <x:v>Approximate graph digitization.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278">
+      <x:c r="A278" t="str">
+        <x:v>O0301</x:v>
+      </x:c>
+      <x:c r="B278" t="str">
+        <x:v>Bo_2015</x:v>
+      </x:c>
+      <x:c r="C278" t="str">
+        <x:v>Bo_2015_all</x:v>
+      </x:c>
+      <x:c r="D278" t="str">
+        <x:v>Bo_daypart</x:v>
+      </x:c>
+      <x:c r="E278" t="str">
+        <x:v>Bo_morning</x:v>
+      </x:c>
+      <x:c r="F278" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G278"/>
+      <x:c r="H278" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I278" t="str">
+        <x:v>glucose_auc</x:v>
+      </x:c>
+      <x:c r="J278" t="str">
+        <x:v>glucose AUC</x:v>
+      </x:c>
+      <x:c r="K278" t="str">
+        <x:v>reported AUC</x:v>
+      </x:c>
+      <x:c r="L278" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="M278"/>
+      <x:c r="N278" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O278" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P278" t="n">
+        <x:v>15383.2</x:v>
+      </x:c>
+      <x:c r="Q278" t="str">
+        <x:v>SD</x:v>
+      </x:c>
+      <x:c r="R278" t="n">
+        <x:v>2045.3</x:v>
+      </x:c>
+      <x:c r="S278"/>
+      <x:c r="T278"/>
+      <x:c r="U278" t="str">
+        <x:v>&lt;0.001</x:v>
+      </x:c>
+      <x:c r="V278" t="str">
+        <x:v>mg/dL×h (as printed)</x:v>
+      </x:c>
+      <x:c r="W278"/>
+      <x:c r="X278"/>
+      <x:c r="Y278" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z278" t="str">
+        <x:v>Bo_2017_secondary; PDF p4; Results</x:v>
+      </x:c>
+      <x:c r="AA278"/>
+    </x:row>
+    <x:row r="279">
+      <x:c r="A279" t="str">
+        <x:v>O0302</x:v>
+      </x:c>
+      <x:c r="B279" t="str">
+        <x:v>Bo_2015</x:v>
+      </x:c>
+      <x:c r="C279" t="str">
+        <x:v>Bo_2015_all</x:v>
+      </x:c>
+      <x:c r="D279" t="str">
+        <x:v>Bo_daypart</x:v>
+      </x:c>
+      <x:c r="E279" t="str">
+        <x:v>Bo_evening</x:v>
+      </x:c>
+      <x:c r="F279" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G279"/>
+      <x:c r="H279" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I279" t="str">
+        <x:v>glucose_auc</x:v>
+      </x:c>
+      <x:c r="J279" t="str">
+        <x:v>glucose AUC</x:v>
+      </x:c>
+      <x:c r="K279" t="str">
+        <x:v>reported AUC</x:v>
+      </x:c>
+      <x:c r="L279" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="M279"/>
+      <x:c r="N279" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O279" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P279" t="n">
+        <x:v>17183.3</x:v>
+      </x:c>
+      <x:c r="Q279" t="str">
+        <x:v>SD</x:v>
+      </x:c>
+      <x:c r="R279" t="n">
+        <x:v>2290.4</x:v>
+      </x:c>
+      <x:c r="S279"/>
+      <x:c r="T279"/>
+      <x:c r="U279" t="str">
+        <x:v>&lt;0.001</x:v>
+      </x:c>
+      <x:c r="V279" t="str">
+        <x:v>mg/dL×h (as printed)</x:v>
+      </x:c>
+      <x:c r="W279"/>
+      <x:c r="X279"/>
+      <x:c r="Y279" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z279" t="str">
+        <x:v>Bo_2017_secondary; PDF p4; Results</x:v>
+      </x:c>
+      <x:c r="AA279"/>
+    </x:row>
+    <x:row r="280">
+      <x:c r="A280" t="str">
+        <x:v>O0303</x:v>
+      </x:c>
+      <x:c r="B280" t="str">
+        <x:v>Bo_2015</x:v>
+      </x:c>
+      <x:c r="C280" t="str">
+        <x:v>Bo_2015_all</x:v>
+      </x:c>
+      <x:c r="D280" t="str">
+        <x:v>Bo_daypart</x:v>
+      </x:c>
+      <x:c r="E280" t="str">
+        <x:v>Bo_morning</x:v>
+      </x:c>
+      <x:c r="F280" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G280"/>
+      <x:c r="H280" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I280" t="str">
+        <x:v>insulin_auc</x:v>
+      </x:c>
+      <x:c r="J280" t="str">
+        <x:v>insulin AUC</x:v>
+      </x:c>
+      <x:c r="K280" t="str">
+        <x:v>reported AUC</x:v>
+      </x:c>
+      <x:c r="L280" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="M280"/>
+      <x:c r="N280" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O280" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P280" t="n">
+        <x:v>6968.9</x:v>
+      </x:c>
+      <x:c r="Q280" t="str">
+        <x:v>SD</x:v>
+      </x:c>
+      <x:c r="R280" t="n">
+        <x:v>2788.7</x:v>
+      </x:c>
+      <x:c r="S280"/>
+      <x:c r="T280"/>
+      <x:c r="U280" t="str">
+        <x:v>0.007 (log AUC)</x:v>
+      </x:c>
+      <x:c r="V280" t="str">
+        <x:v>µU/mL×h (as printed)</x:v>
+      </x:c>
+      <x:c r="W280"/>
+      <x:c r="X280"/>
+      <x:c r="Y280" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z280" t="str">
+        <x:v>Bo_2017_secondary; PDF p4; Results</x:v>
+      </x:c>
+      <x:c r="AA280"/>
+    </x:row>
+    <x:row r="281">
+      <x:c r="A281" t="str">
+        <x:v>O0304</x:v>
+      </x:c>
+      <x:c r="B281" t="str">
+        <x:v>Bo_2015</x:v>
+      </x:c>
+      <x:c r="C281" t="str">
+        <x:v>Bo_2015_all</x:v>
+      </x:c>
+      <x:c r="D281" t="str">
+        <x:v>Bo_daypart</x:v>
+      </x:c>
+      <x:c r="E281" t="str">
+        <x:v>Bo_evening</x:v>
+      </x:c>
+      <x:c r="F281" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G281"/>
+      <x:c r="H281" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I281" t="str">
+        <x:v>insulin_auc</x:v>
+      </x:c>
+      <x:c r="J281" t="str">
+        <x:v>insulin AUC</x:v>
+      </x:c>
+      <x:c r="K281" t="str">
+        <x:v>reported AUC</x:v>
+      </x:c>
+      <x:c r="L281" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="M281"/>
+      <x:c r="N281" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O281" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P281" t="n">
+        <x:v>8597.8</x:v>
+      </x:c>
+      <x:c r="Q281" t="str">
+        <x:v>SD</x:v>
+      </x:c>
+      <x:c r="R281" t="n">
+        <x:v>4231.1</x:v>
+      </x:c>
+      <x:c r="S281"/>
+      <x:c r="T281"/>
+      <x:c r="U281" t="str">
+        <x:v>0.007 (log AUC)</x:v>
+      </x:c>
+      <x:c r="V281" t="str">
+        <x:v>µU/mL×h (as printed)</x:v>
+      </x:c>
+      <x:c r="W281"/>
+      <x:c r="X281"/>
+      <x:c r="Y281" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z281" t="str">
+        <x:v>Bo_2017_secondary; PDF p4; Results</x:v>
+      </x:c>
+      <x:c r="AA281"/>
+    </x:row>
+    <x:row r="282">
+      <x:c r="A282" t="str">
+        <x:v>O0305</x:v>
+      </x:c>
+      <x:c r="B282" t="str">
+        <x:v>Gu_2020</x:v>
+      </x:c>
+      <x:c r="C282" t="str">
+        <x:v>Gu_2020_all</x:v>
+      </x:c>
+      <x:c r="D282" t="str">
+        <x:v>Gu_supportive</x:v>
+      </x:c>
+      <x:c r="E282" t="str">
+        <x:v>Gu_routine</x:v>
+      </x:c>
+      <x:c r="F282" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G282"/>
+      <x:c r="H282" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I282" t="str">
+        <x:v>timed_insulin</x:v>
+      </x:c>
+      <x:c r="J282" t="str">
+        <x:v>20-h mean insulin</x:v>
+      </x:c>
+      <x:c r="K282"/>
+      <x:c r="L282" t="n">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="M282"/>
+      <x:c r="N282" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O282" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P282" t="n">
+        <x:v>20.9</x:v>
+      </x:c>
+      <x:c r="Q282" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R282" t="n">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="S282"/>
+      <x:c r="T282"/>
+      <x:c r="U282" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="V282" t="str">
+        <x:v>µU/mL</x:v>
+      </x:c>
+      <x:c r="W282"/>
+      <x:c r="X282"/>
+      <x:c r="Y282" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z282" t="str">
+        <x:v>Gu_2020_primary; PDF p6; Results</x:v>
+      </x:c>
+      <x:c r="AA282"/>
+    </x:row>
+    <x:row r="283">
+      <x:c r="A283" t="str">
+        <x:v>O0306</x:v>
+      </x:c>
+      <x:c r="B283" t="str">
+        <x:v>Gu_2020</x:v>
+      </x:c>
+      <x:c r="C283" t="str">
+        <x:v>Gu_2020_all</x:v>
+      </x:c>
+      <x:c r="D283" t="str">
+        <x:v>Gu_supportive</x:v>
+      </x:c>
+      <x:c r="E283" t="str">
+        <x:v>Gu_late</x:v>
+      </x:c>
+      <x:c r="F283" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G283"/>
+      <x:c r="H283" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I283" t="str">
+        <x:v>timed_insulin</x:v>
+      </x:c>
+      <x:c r="J283" t="str">
+        <x:v>20-h mean insulin</x:v>
+      </x:c>
+      <x:c r="K283"/>
+      <x:c r="L283" t="n">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="M283"/>
+      <x:c r="N283" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O283" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P283" t="n">
+        <x:v>23.4</x:v>
+      </x:c>
+      <x:c r="Q283" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R283" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="S283"/>
+      <x:c r="T283"/>
+      <x:c r="U283" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="V283" t="str">
+        <x:v>µU/mL</x:v>
+      </x:c>
+      <x:c r="W283"/>
+      <x:c r="X283"/>
+      <x:c r="Y283" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z283" t="str">
+        <x:v>Gu_2020_primary; PDF p6; Results</x:v>
+      </x:c>
+      <x:c r="AA283"/>
+    </x:row>
+    <x:row r="284">
+      <x:c r="A284" t="str">
+        <x:v>O0307</x:v>
+      </x:c>
+      <x:c r="B284" t="str">
+        <x:v>Gu_2020</x:v>
+      </x:c>
+      <x:c r="C284" t="str">
+        <x:v>Gu_2020_all</x:v>
+      </x:c>
+      <x:c r="D284" t="str">
+        <x:v>Gu_supportive</x:v>
+      </x:c>
+      <x:c r="E284" t="str">
+        <x:v>Gu_routine</x:v>
+      </x:c>
+      <x:c r="F284" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G284"/>
+      <x:c r="H284" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I284" t="str">
+        <x:v>timed_glucose</x:v>
+      </x:c>
+      <x:c r="J284" t="str">
+        <x:v>20-h mean glucose</x:v>
+      </x:c>
+      <x:c r="K284"/>
+      <x:c r="L284" t="n">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="M284"/>
+      <x:c r="N284" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O284" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P284" t="n">
+        <x:v>99.8</x:v>
+      </x:c>
+      <x:c r="Q284" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R284" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S284"/>
+      <x:c r="T284"/>
+      <x:c r="U284" t="str">
+        <x:v>&lt;0.01</x:v>
+      </x:c>
+      <x:c r="V284" t="str">
+        <x:v>mg/dL</x:v>
+      </x:c>
+      <x:c r="W284"/>
+      <x:c r="X284"/>
+      <x:c r="Y284" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z284" t="str">
+        <x:v>Gu_2020_primary; PDF p6; Results</x:v>
+      </x:c>
+      <x:c r="AA284"/>
+    </x:row>
+    <x:row r="285">
+      <x:c r="A285" t="str">
+        <x:v>O0308</x:v>
+      </x:c>
+      <x:c r="B285" t="str">
+        <x:v>Gu_2020</x:v>
+      </x:c>
+      <x:c r="C285" t="str">
+        <x:v>Gu_2020_all</x:v>
+      </x:c>
+      <x:c r="D285" t="str">
+        <x:v>Gu_supportive</x:v>
+      </x:c>
+      <x:c r="E285" t="str">
+        <x:v>Gu_late</x:v>
+      </x:c>
+      <x:c r="F285" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G285"/>
+      <x:c r="H285" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I285" t="str">
+        <x:v>timed_glucose</x:v>
+      </x:c>
+      <x:c r="J285" t="str">
+        <x:v>20-h mean glucose</x:v>
+      </x:c>
+      <x:c r="K285"/>
+      <x:c r="L285" t="n">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="M285"/>
+      <x:c r="N285" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O285" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P285" t="n">
+        <x:v>105.8</x:v>
+      </x:c>
+      <x:c r="Q285" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R285" t="n">
+        <x:v>2.3</x:v>
+      </x:c>
+      <x:c r="S285"/>
+      <x:c r="T285"/>
+      <x:c r="U285" t="str">
+        <x:v>&lt;0.01</x:v>
+      </x:c>
+      <x:c r="V285" t="str">
+        <x:v>mg/dL</x:v>
+      </x:c>
+      <x:c r="W285"/>
+      <x:c r="X285"/>
+      <x:c r="Y285" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z285" t="str">
+        <x:v>Gu_2020_primary; PDF p6; Results</x:v>
+      </x:c>
+      <x:c r="AA285"/>
+    </x:row>
+    <x:row r="286">
+      <x:c r="A286" t="str">
+        <x:v>O0309</x:v>
+      </x:c>
+      <x:c r="B286" t="str">
+        <x:v>Gu_2020</x:v>
+      </x:c>
+      <x:c r="C286" t="str">
+        <x:v>Gu_2020_all</x:v>
+      </x:c>
+      <x:c r="D286" t="str">
+        <x:v>Gu_supportive</x:v>
+      </x:c>
+      <x:c r="E286" t="str">
+        <x:v>Gu_routine</x:v>
+      </x:c>
+      <x:c r="F286" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G286"/>
+      <x:c r="H286" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I286" t="str">
+        <x:v>glucose_auc</x:v>
+      </x:c>
+      <x:c r="J286" t="str">
+        <x:v>Next-breakfast glucose AUC</x:v>
+      </x:c>
+      <x:c r="K286" t="str">
+        <x:v>total</x:v>
+      </x:c>
+      <x:c r="L286" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="M286"/>
+      <x:c r="N286" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O286" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P286" t="n">
+        <x:v>391.7</x:v>
+      </x:c>
+      <x:c r="Q286" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R286" t="n">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="S286"/>
+      <x:c r="T286"/>
+      <x:c r="U286" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="V286" t="str">
+        <x:v>mg/dL×h</x:v>
+      </x:c>
+      <x:c r="W286"/>
+      <x:c r="X286"/>
+      <x:c r="Y286" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z286" t="str">
+        <x:v>Gu_2020_primary; PDF p6; Results</x:v>
+      </x:c>
+      <x:c r="AA286"/>
+    </x:row>
+    <x:row r="287">
+      <x:c r="A287" t="str">
+        <x:v>O0310</x:v>
+      </x:c>
+      <x:c r="B287" t="str">
+        <x:v>Gu_2020</x:v>
+      </x:c>
+      <x:c r="C287" t="str">
+        <x:v>Gu_2020_all</x:v>
+      </x:c>
+      <x:c r="D287" t="str">
+        <x:v>Gu_supportive</x:v>
+      </x:c>
+      <x:c r="E287" t="str">
+        <x:v>Gu_late</x:v>
+      </x:c>
+      <x:c r="F287" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G287"/>
+      <x:c r="H287" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I287" t="str">
+        <x:v>glucose_auc</x:v>
+      </x:c>
+      <x:c r="J287" t="str">
+        <x:v>Next-breakfast glucose AUC</x:v>
+      </x:c>
+      <x:c r="K287" t="str">
+        <x:v>total</x:v>
+      </x:c>
+      <x:c r="L287" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="M287"/>
+      <x:c r="N287" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O287" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P287" t="n">
+        <x:v>412.2</x:v>
+      </x:c>
+      <x:c r="Q287" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R287" t="n">
+        <x:v>10.6</x:v>
+      </x:c>
+      <x:c r="S287"/>
+      <x:c r="T287"/>
+      <x:c r="U287" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="V287" t="str">
+        <x:v>mg/dL×h</x:v>
+      </x:c>
+      <x:c r="W287"/>
+      <x:c r="X287"/>
+      <x:c r="Y287" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z287" t="str">
+        <x:v>Gu_2020_primary; PDF p6; Results</x:v>
+      </x:c>
+      <x:c r="AA287"/>
+    </x:row>
+    <x:row r="288">
+      <x:c r="A288" t="str">
+        <x:v>O0311</x:v>
+      </x:c>
+      <x:c r="B288" t="str">
+        <x:v>Gu_2020</x:v>
+      </x:c>
+      <x:c r="C288" t="str">
+        <x:v>Gu_2020_all</x:v>
+      </x:c>
+      <x:c r="D288" t="str">
+        <x:v>Gu_supportive</x:v>
+      </x:c>
+      <x:c r="E288"/>
+      <x:c r="F288"/>
+      <x:c r="G288"/>
+      <x:c r="H288" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I288" t="str">
+        <x:v>insulin_auc</x:v>
+      </x:c>
+      <x:c r="J288" t="str">
+        <x:v>Postdinner insulin AUC</x:v>
+      </x:c>
+      <x:c r="K288" t="str">
+        <x:v>total</x:v>
+      </x:c>
+      <x:c r="L288" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="M288"/>
+      <x:c r="N288" t="str">
+        <x:v>narrative_only</x:v>
+      </x:c>
+      <x:c r="O288" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P288"/>
+      <x:c r="Q288"/>
+      <x:c r="R288"/>
+      <x:c r="S288"/>
+      <x:c r="T288"/>
+      <x:c r="U288" t="str">
+        <x:v>NS</x:v>
+      </x:c>
+      <x:c r="V288"/>
+      <x:c r="W288" t="str">
+        <x:v>no significant difference</x:v>
+      </x:c>
+      <x:c r="X288"/>
+      <x:c r="Y288" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z288" t="str">
+        <x:v>Gu_2020_primary; PDF pp5–6,8; Results and Figure 3</x:v>
+      </x:c>
+      <x:c r="AA288" t="str">
+        <x:v>No significant timing difference; numerical AUC summaries and paired precision not reported.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="289">
+      <x:c r="A289" t="str">
+        <x:v>O0312</x:v>
+      </x:c>
+      <x:c r="B289" t="str">
+        <x:v>Gu_2020</x:v>
+      </x:c>
+      <x:c r="C289" t="str">
+        <x:v>Gu_2020_all</x:v>
+      </x:c>
+      <x:c r="D289" t="str">
+        <x:v>Gu_supportive</x:v>
+      </x:c>
+      <x:c r="E289"/>
+      <x:c r="F289"/>
+      <x:c r="G289"/>
+      <x:c r="H289" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I289" t="str">
+        <x:v>timed_insulin</x:v>
+      </x:c>
+      <x:c r="J289" t="str">
+        <x:v>Postdinner peak insulin</x:v>
+      </x:c>
+      <x:c r="K289"/>
+      <x:c r="L289" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="M289"/>
+      <x:c r="N289" t="str">
+        <x:v>narrative_only</x:v>
+      </x:c>
+      <x:c r="O289" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P289"/>
+      <x:c r="Q289"/>
+      <x:c r="R289"/>
+      <x:c r="S289"/>
+      <x:c r="T289"/>
+      <x:c r="U289" t="str">
+        <x:v>NS</x:v>
+      </x:c>
+      <x:c r="V289"/>
+      <x:c r="W289" t="str">
+        <x:v>no significant difference</x:v>
+      </x:c>
+      <x:c r="X289"/>
+      <x:c r="Y289" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z289" t="str">
+        <x:v>Gu_2020_primary; PDF pp5–6,8; Results and Figure 3</x:v>
+      </x:c>
+      <x:c r="AA289" t="str">
+        <x:v>No significant timing difference; peak summaries not printed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="290">
+      <x:c r="A290" t="str">
+        <x:v>O0313</x:v>
+      </x:c>
+      <x:c r="B290" t="str">
+        <x:v>Gu_2020</x:v>
+      </x:c>
+      <x:c r="C290" t="str">
+        <x:v>Gu_2020_all</x:v>
+      </x:c>
+      <x:c r="D290" t="str">
+        <x:v>Gu_supportive</x:v>
+      </x:c>
+      <x:c r="E290"/>
+      <x:c r="F290"/>
+      <x:c r="G290"/>
+      <x:c r="H290" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I290" t="str">
+        <x:v>insulin_auc</x:v>
+      </x:c>
+      <x:c r="J290" t="str">
+        <x:v>Next-breakfast insulin AUC</x:v>
+      </x:c>
+      <x:c r="K290" t="str">
+        <x:v>total</x:v>
+      </x:c>
+      <x:c r="L290" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="M290"/>
+      <x:c r="N290" t="str">
+        <x:v>narrative_only</x:v>
+      </x:c>
+      <x:c r="O290" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P290"/>
+      <x:c r="Q290"/>
+      <x:c r="R290"/>
+      <x:c r="S290"/>
+      <x:c r="T290"/>
+      <x:c r="U290" t="str">
+        <x:v>NS</x:v>
+      </x:c>
+      <x:c r="V290"/>
+      <x:c r="W290" t="str">
+        <x:v>no significant difference</x:v>
+      </x:c>
+      <x:c r="X290"/>
+      <x:c r="Y290" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z290" t="str">
+        <x:v>Gu_2020_primary; PDF pp5–6,8; Results and Figure 3</x:v>
+      </x:c>
+      <x:c r="AA290" t="str">
+        <x:v>No significant timing difference; numerical AUC summaries and paired precision not reported.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291">
+      <x:c r="A291" t="str">
+        <x:v>O0314</x:v>
+      </x:c>
+      <x:c r="B291" t="str">
+        <x:v>Gu_2020</x:v>
+      </x:c>
+      <x:c r="C291" t="str">
+        <x:v>Gu_2020_all</x:v>
+      </x:c>
+      <x:c r="D291" t="str">
+        <x:v>Gu_supportive</x:v>
+      </x:c>
+      <x:c r="E291" t="str">
+        <x:v>Gu_routine</x:v>
+      </x:c>
+      <x:c r="F291" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G291"/>
+      <x:c r="H291" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I291" t="str">
+        <x:v>timed_insulin</x:v>
+      </x:c>
+      <x:c r="J291" t="str">
+        <x:v>Postdinner insulin concentration</x:v>
+      </x:c>
+      <x:c r="K291"/>
+      <x:c r="L291"/>
+      <x:c r="M291" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N291" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O291" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P291" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="Q291" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R291" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S291"/>
+      <x:c r="T291"/>
+      <x:c r="U291" t="str">
+        <x:v>NS</x:v>
+      </x:c>
+      <x:c r="V291" t="str">
+        <x:v>µU/mL</x:v>
+      </x:c>
+      <x:c r="W291"/>
+      <x:c r="X291"/>
+      <x:c r="Y291" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z291" t="str">
+        <x:v>Gu_2020_primary; PDF p8; Figure 3D</x:v>
+      </x:c>
+      <x:c r="AA291" t="str">
+        <x:v>Approximate means and SEM read from clear plotted markers/error bars; rounded to 1 µU/mL.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292">
+      <x:c r="A292" t="str">
+        <x:v>O0315</x:v>
+      </x:c>
+      <x:c r="B292" t="str">
+        <x:v>Gu_2020</x:v>
+      </x:c>
+      <x:c r="C292" t="str">
+        <x:v>Gu_2020_all</x:v>
+      </x:c>
+      <x:c r="D292" t="str">
+        <x:v>Gu_supportive</x:v>
+      </x:c>
+      <x:c r="E292" t="str">
+        <x:v>Gu_late</x:v>
+      </x:c>
+      <x:c r="F292" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G292"/>
+      <x:c r="H292" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I292" t="str">
+        <x:v>timed_insulin</x:v>
+      </x:c>
+      <x:c r="J292" t="str">
+        <x:v>Postdinner insulin concentration</x:v>
+      </x:c>
+      <x:c r="K292"/>
+      <x:c r="L292"/>
+      <x:c r="M292" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N292" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O292" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P292" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="Q292" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R292" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S292"/>
+      <x:c r="T292"/>
+      <x:c r="U292" t="str">
+        <x:v>NS</x:v>
+      </x:c>
+      <x:c r="V292" t="str">
+        <x:v>µU/mL</x:v>
+      </x:c>
+      <x:c r="W292"/>
+      <x:c r="X292"/>
+      <x:c r="Y292" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z292" t="str">
+        <x:v>Gu_2020_primary; PDF p8; Figure 3D</x:v>
+      </x:c>
+      <x:c r="AA292" t="str">
+        <x:v>Approximate means and SEM read from clear plotted markers/error bars; rounded to 1 µU/mL.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293">
+      <x:c r="A293" t="str">
+        <x:v>O0316</x:v>
+      </x:c>
+      <x:c r="B293" t="str">
+        <x:v>Gu_2020</x:v>
+      </x:c>
+      <x:c r="C293" t="str">
+        <x:v>Gu_2020_all</x:v>
+      </x:c>
+      <x:c r="D293" t="str">
+        <x:v>Gu_supportive</x:v>
+      </x:c>
+      <x:c r="E293" t="str">
+        <x:v>Gu_routine</x:v>
+      </x:c>
+      <x:c r="F293" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G293"/>
+      <x:c r="H293" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I293" t="str">
+        <x:v>timed_insulin</x:v>
+      </x:c>
+      <x:c r="J293" t="str">
+        <x:v>Postdinner insulin concentration</x:v>
+      </x:c>
+      <x:c r="K293"/>
+      <x:c r="L293"/>
+      <x:c r="M293" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="N293" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O293" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P293" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="Q293" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R293" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="S293"/>
+      <x:c r="T293"/>
+      <x:c r="U293" t="str">
+        <x:v>NS</x:v>
+      </x:c>
+      <x:c r="V293" t="str">
+        <x:v>µU/mL</x:v>
+      </x:c>
+      <x:c r="W293"/>
+      <x:c r="X293"/>
+      <x:c r="Y293" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z293" t="str">
+        <x:v>Gu_2020_primary; PDF p8; Figure 3D</x:v>
+      </x:c>
+      <x:c r="AA293" t="str">
+        <x:v>Approximate means and SEM read from clear plotted markers/error bars; rounded to 1 µU/mL.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294">
+      <x:c r="A294" t="str">
+        <x:v>O0317</x:v>
+      </x:c>
+      <x:c r="B294" t="str">
+        <x:v>Gu_2020</x:v>
+      </x:c>
+      <x:c r="C294" t="str">
+        <x:v>Gu_2020_all</x:v>
+      </x:c>
+      <x:c r="D294" t="str">
+        <x:v>Gu_supportive</x:v>
+      </x:c>
+      <x:c r="E294" t="str">
+        <x:v>Gu_late</x:v>
+      </x:c>
+      <x:c r="F294" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G294"/>
+      <x:c r="H294" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I294" t="str">
+        <x:v>timed_insulin</x:v>
+      </x:c>
+      <x:c r="J294" t="str">
+        <x:v>Postdinner insulin concentration</x:v>
+      </x:c>
+      <x:c r="K294"/>
+      <x:c r="L294"/>
+      <x:c r="M294" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="N294" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O294" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P294" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="Q294" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R294" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="S294"/>
+      <x:c r="T294"/>
+      <x:c r="U294" t="str">
+        <x:v>NS</x:v>
+      </x:c>
+      <x:c r="V294" t="str">
+        <x:v>µU/mL</x:v>
+      </x:c>
+      <x:c r="W294"/>
+      <x:c r="X294"/>
+      <x:c r="Y294" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z294" t="str">
+        <x:v>Gu_2020_primary; PDF p8; Figure 3D</x:v>
+      </x:c>
+      <x:c r="AA294" t="str">
+        <x:v>Approximate means and SEM read from clear plotted markers/error bars; rounded to 1 µU/mL.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295">
+      <x:c r="A295" t="str">
+        <x:v>O0318</x:v>
+      </x:c>
+      <x:c r="B295" t="str">
+        <x:v>Gu_2020</x:v>
+      </x:c>
+      <x:c r="C295" t="str">
+        <x:v>Gu_2020_all</x:v>
+      </x:c>
+      <x:c r="D295" t="str">
+        <x:v>Gu_supportive</x:v>
+      </x:c>
+      <x:c r="E295" t="str">
+        <x:v>Gu_routine</x:v>
+      </x:c>
+      <x:c r="F295" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G295"/>
+      <x:c r="H295" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I295" t="str">
+        <x:v>timed_insulin</x:v>
+      </x:c>
+      <x:c r="J295" t="str">
+        <x:v>Postdinner insulin concentration</x:v>
+      </x:c>
+      <x:c r="K295"/>
+      <x:c r="L295"/>
+      <x:c r="M295" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="N295" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O295" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P295" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="Q295" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R295" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="S295"/>
+      <x:c r="T295"/>
+      <x:c r="U295" t="str">
+        <x:v>NS</x:v>
+      </x:c>
+      <x:c r="V295" t="str">
+        <x:v>µU/mL</x:v>
+      </x:c>
+      <x:c r="W295"/>
+      <x:c r="X295"/>
+      <x:c r="Y295" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z295" t="str">
+        <x:v>Gu_2020_primary; PDF p8; Figure 3D</x:v>
+      </x:c>
+      <x:c r="AA295" t="str">
+        <x:v>Approximate means and SEM read from clear plotted markers/error bars; rounded to 1 µU/mL.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296">
+      <x:c r="A296" t="str">
+        <x:v>O0319</x:v>
+      </x:c>
+      <x:c r="B296" t="str">
+        <x:v>Gu_2020</x:v>
+      </x:c>
+      <x:c r="C296" t="str">
+        <x:v>Gu_2020_all</x:v>
+      </x:c>
+      <x:c r="D296" t="str">
+        <x:v>Gu_supportive</x:v>
+      </x:c>
+      <x:c r="E296" t="str">
+        <x:v>Gu_late</x:v>
+      </x:c>
+      <x:c r="F296" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G296"/>
+      <x:c r="H296" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I296" t="str">
+        <x:v>timed_insulin</x:v>
+      </x:c>
+      <x:c r="J296" t="str">
+        <x:v>Postdinner insulin concentration</x:v>
+      </x:c>
+      <x:c r="K296"/>
+      <x:c r="L296"/>
+      <x:c r="M296" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="N296" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O296" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P296" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="Q296" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R296" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="S296"/>
+      <x:c r="T296"/>
+      <x:c r="U296" t="str">
+        <x:v>NS</x:v>
+      </x:c>
+      <x:c r="V296" t="str">
+        <x:v>µU/mL</x:v>
+      </x:c>
+      <x:c r="W296"/>
+      <x:c r="X296"/>
+      <x:c r="Y296" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z296" t="str">
+        <x:v>Gu_2020_primary; PDF p8; Figure 3D</x:v>
+      </x:c>
+      <x:c r="AA296" t="str">
+        <x:v>Approximate means and SEM read from clear plotted markers/error bars; rounded to 1 µU/mL.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="297">
+      <x:c r="A297" t="str">
+        <x:v>O0320</x:v>
+      </x:c>
+      <x:c r="B297" t="str">
+        <x:v>Gu_2020</x:v>
+      </x:c>
+      <x:c r="C297" t="str">
+        <x:v>Gu_2020_all</x:v>
+      </x:c>
+      <x:c r="D297" t="str">
+        <x:v>Gu_supportive</x:v>
+      </x:c>
+      <x:c r="E297" t="str">
+        <x:v>Gu_routine</x:v>
+      </x:c>
+      <x:c r="F297" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G297"/>
+      <x:c r="H297" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I297" t="str">
+        <x:v>timed_insulin</x:v>
+      </x:c>
+      <x:c r="J297" t="str">
+        <x:v>Postdinner insulin concentration</x:v>
+      </x:c>
+      <x:c r="K297"/>
+      <x:c r="L297"/>
+      <x:c r="M297" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="N297" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O297" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P297" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="Q297" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R297" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="S297"/>
+      <x:c r="T297"/>
+      <x:c r="U297" t="str">
+        <x:v>NS</x:v>
+      </x:c>
+      <x:c r="V297" t="str">
+        <x:v>µU/mL</x:v>
+      </x:c>
+      <x:c r="W297"/>
+      <x:c r="X297"/>
+      <x:c r="Y297" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z297" t="str">
+        <x:v>Gu_2020_primary; PDF p8; Figure 3D</x:v>
+      </x:c>
+      <x:c r="AA297" t="str">
+        <x:v>Approximate means and SEM read from clear plotted markers/error bars; rounded to 1 µU/mL.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298">
+      <x:c r="A298" t="str">
+        <x:v>O0321</x:v>
+      </x:c>
+      <x:c r="B298" t="str">
+        <x:v>Gu_2020</x:v>
+      </x:c>
+      <x:c r="C298" t="str">
+        <x:v>Gu_2020_all</x:v>
+      </x:c>
+      <x:c r="D298" t="str">
+        <x:v>Gu_supportive</x:v>
+      </x:c>
+      <x:c r="E298" t="str">
+        <x:v>Gu_late</x:v>
+      </x:c>
+      <x:c r="F298" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G298"/>
+      <x:c r="H298" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I298" t="str">
+        <x:v>timed_insulin</x:v>
+      </x:c>
+      <x:c r="J298" t="str">
+        <x:v>Postdinner insulin concentration</x:v>
+      </x:c>
+      <x:c r="K298"/>
+      <x:c r="L298"/>
+      <x:c r="M298" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="N298" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O298" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P298" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="Q298" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R298" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="S298"/>
+      <x:c r="T298"/>
+      <x:c r="U298" t="str">
+        <x:v>NS</x:v>
+      </x:c>
+      <x:c r="V298" t="str">
+        <x:v>µU/mL</x:v>
+      </x:c>
+      <x:c r="W298"/>
+      <x:c r="X298"/>
+      <x:c r="Y298" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z298" t="str">
+        <x:v>Gu_2020_primary; PDF p8; Figure 3D</x:v>
+      </x:c>
+      <x:c r="AA298" t="str">
+        <x:v>Approximate means and SEM read from clear plotted markers/error bars; rounded to 1 µU/mL.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299">
+      <x:c r="A299" t="str">
+        <x:v>O0322</x:v>
+      </x:c>
+      <x:c r="B299" t="str">
+        <x:v>Gu_2020</x:v>
+      </x:c>
+      <x:c r="C299" t="str">
+        <x:v>Gu_2020_all</x:v>
+      </x:c>
+      <x:c r="D299" t="str">
+        <x:v>Gu_supportive</x:v>
+      </x:c>
+      <x:c r="E299" t="str">
+        <x:v>Gu_routine</x:v>
+      </x:c>
+      <x:c r="F299" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G299"/>
+      <x:c r="H299" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I299" t="str">
+        <x:v>timed_insulin</x:v>
+      </x:c>
+      <x:c r="J299" t="str">
+        <x:v>Postdinner insulin concentration</x:v>
+      </x:c>
+      <x:c r="K299"/>
+      <x:c r="L299"/>
+      <x:c r="M299" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="N299" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O299" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P299" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="Q299" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R299" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S299"/>
+      <x:c r="T299"/>
+      <x:c r="U299" t="str">
+        <x:v>&lt;0.05</x:v>
+      </x:c>
+      <x:c r="V299" t="str">
+        <x:v>µU/mL</x:v>
+      </x:c>
+      <x:c r="W299"/>
+      <x:c r="X299"/>
+      <x:c r="Y299" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z299" t="str">
+        <x:v>Gu_2020_primary; PDF p8; Figure 3D</x:v>
+      </x:c>
+      <x:c r="AA299" t="str">
+        <x:v>Approximate means and SEM read from clear plotted markers/error bars; rounded to 1 µU/mL.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="300">
+      <x:c r="A300" t="str">
+        <x:v>O0323</x:v>
+      </x:c>
+      <x:c r="B300" t="str">
+        <x:v>Gu_2020</x:v>
+      </x:c>
+      <x:c r="C300" t="str">
+        <x:v>Gu_2020_all</x:v>
+      </x:c>
+      <x:c r="D300" t="str">
+        <x:v>Gu_supportive</x:v>
+      </x:c>
+      <x:c r="E300" t="str">
+        <x:v>Gu_late</x:v>
+      </x:c>
+      <x:c r="F300" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G300"/>
+      <x:c r="H300" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I300" t="str">
+        <x:v>timed_insulin</x:v>
+      </x:c>
+      <x:c r="J300" t="str">
+        <x:v>Postdinner insulin concentration</x:v>
+      </x:c>
+      <x:c r="K300"/>
+      <x:c r="L300"/>
+      <x:c r="M300" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="N300" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O300" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P300" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="Q300" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R300" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="S300"/>
+      <x:c r="T300"/>
+      <x:c r="U300" t="str">
+        <x:v>&lt;0.05</x:v>
+      </x:c>
+      <x:c r="V300" t="str">
+        <x:v>µU/mL</x:v>
+      </x:c>
+      <x:c r="W300"/>
+      <x:c r="X300"/>
+      <x:c r="Y300" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z300" t="str">
+        <x:v>Gu_2020_primary; PDF p8; Figure 3D</x:v>
+      </x:c>
+      <x:c r="AA300" t="str">
+        <x:v>Approximate means and SEM read from clear plotted markers/error bars; rounded to 1 µU/mL.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301">
+      <x:c r="A301" t="str">
+        <x:v>O0324</x:v>
+      </x:c>
+      <x:c r="B301" t="str">
+        <x:v>Service_1983</x:v>
+      </x:c>
+      <x:c r="C301" t="str">
+        <x:v>Service_1983_all</x:v>
+      </x:c>
+      <x:c r="D301" t="str">
+        <x:v>Service_supportive</x:v>
+      </x:c>
+      <x:c r="E301" t="str">
+        <x:v>Service_large_08</x:v>
+      </x:c>
+      <x:c r="F301" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G301" t="str">
+        <x:v>large</x:v>
+      </x:c>
+      <x:c r="H301" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I301" t="str">
+        <x:v>timed_insulin</x:v>
+      </x:c>
+      <x:c r="J301" t="str">
+        <x:v>Large-meal integrated insulin response</x:v>
+      </x:c>
+      <x:c r="K301" t="str">
+        <x:v>integrated response</x:v>
+      </x:c>
+      <x:c r="L301" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="M301"/>
+      <x:c r="N301" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O301" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="P301" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="Q301" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R301" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="S301"/>
+      <x:c r="T301"/>
+      <x:c r="U301" t="str">
+        <x:v>NS</x:v>
+      </x:c>
+      <x:c r="V301" t="str">
+        <x:v>mU·L⁻¹·300 min⁻¹ (as printed)</x:v>
+      </x:c>
+      <x:c r="W301"/>
+      <x:c r="X301"/>
+      <x:c r="Y301" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z301" t="str">
+        <x:v>Service_1983_primary; PDF pp2–3; Results and Figure 4</x:v>
+      </x:c>
+      <x:c r="AA301" t="str">
+        <x:v>Figure 4 series; no significant time-of-day effect. Printed integrated unit retained.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302">
+      <x:c r="A302" t="str">
+        <x:v>O0325</x:v>
+      </x:c>
+      <x:c r="B302" t="str">
+        <x:v>Service_1983</x:v>
+      </x:c>
+      <x:c r="C302" t="str">
+        <x:v>Service_1983_all</x:v>
+      </x:c>
+      <x:c r="D302" t="str">
+        <x:v>Service_supportive</x:v>
+      </x:c>
+      <x:c r="E302" t="str">
+        <x:v>Service_large_13</x:v>
+      </x:c>
+      <x:c r="F302" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G302" t="str">
+        <x:v>large</x:v>
+      </x:c>
+      <x:c r="H302" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I302" t="str">
+        <x:v>timed_insulin</x:v>
+      </x:c>
+      <x:c r="J302" t="str">
+        <x:v>Large-meal integrated insulin response</x:v>
+      </x:c>
+      <x:c r="K302" t="str">
+        <x:v>integrated response</x:v>
+      </x:c>
+      <x:c r="L302" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="M302"/>
+      <x:c r="N302" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O302" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="P302" t="n">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="Q302" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R302" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="S302"/>
+      <x:c r="T302"/>
+      <x:c r="U302" t="str">
+        <x:v>NS</x:v>
+      </x:c>
+      <x:c r="V302" t="str">
+        <x:v>mU·L⁻¹·300 min⁻¹ (as printed)</x:v>
+      </x:c>
+      <x:c r="W302"/>
+      <x:c r="X302"/>
+      <x:c r="Y302" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z302" t="str">
+        <x:v>Service_1983_primary; PDF pp2–3; Results and Figure 4</x:v>
+      </x:c>
+      <x:c r="AA302" t="str">
+        <x:v>Figure 4 series; no significant time-of-day effect. Printed integrated unit retained.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303">
+      <x:c r="A303" t="str">
+        <x:v>O0326</x:v>
+      </x:c>
+      <x:c r="B303" t="str">
+        <x:v>Service_1983</x:v>
+      </x:c>
+      <x:c r="C303" t="str">
+        <x:v>Service_1983_all</x:v>
+      </x:c>
+      <x:c r="D303" t="str">
+        <x:v>Service_supportive</x:v>
+      </x:c>
+      <x:c r="E303" t="str">
+        <x:v>Service_large_18</x:v>
+      </x:c>
+      <x:c r="F303" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G303" t="str">
+        <x:v>large</x:v>
+      </x:c>
+      <x:c r="H303" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I303" t="str">
+        <x:v>timed_insulin</x:v>
+      </x:c>
+      <x:c r="J303" t="str">
+        <x:v>Large-meal integrated insulin response</x:v>
+      </x:c>
+      <x:c r="K303" t="str">
+        <x:v>integrated response</x:v>
+      </x:c>
+      <x:c r="L303" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="M303"/>
+      <x:c r="N303" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O303" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="P303" t="n">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="Q303" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R303" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="S303"/>
+      <x:c r="T303"/>
+      <x:c r="U303" t="str">
+        <x:v>NS</x:v>
+      </x:c>
+      <x:c r="V303" t="str">
+        <x:v>mU·L⁻¹·300 min⁻¹ (as printed)</x:v>
+      </x:c>
+      <x:c r="W303"/>
+      <x:c r="X303"/>
+      <x:c r="Y303" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z303" t="str">
+        <x:v>Service_1983_primary; PDF pp2–3; Results and Figure 4</x:v>
+      </x:c>
+      <x:c r="AA303" t="str">
+        <x:v>Figure 4 series; no significant time-of-day effect. Printed integrated unit retained.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304">
+      <x:c r="A304" t="str">
+        <x:v>O0327</x:v>
+      </x:c>
+      <x:c r="B304" t="str">
+        <x:v>Service_1983</x:v>
+      </x:c>
+      <x:c r="C304" t="str">
+        <x:v>Service_1983_all</x:v>
+      </x:c>
+      <x:c r="D304" t="str">
+        <x:v>Service_supportive</x:v>
+      </x:c>
+      <x:c r="E304" t="str">
+        <x:v>Service_large_08</x:v>
+      </x:c>
+      <x:c r="F304" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G304" t="str">
+        <x:v>large</x:v>
+      </x:c>
+      <x:c r="H304" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I304" t="str">
+        <x:v>insulin_secretion</x:v>
+      </x:c>
+      <x:c r="J304" t="str">
+        <x:v>Large-meal insulin secretion from C-peptide</x:v>
+      </x:c>
+      <x:c r="K304"/>
+      <x:c r="L304" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="M304"/>
+      <x:c r="N304" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O304" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="P304" t="n">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="Q304" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R304" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S304"/>
+      <x:c r="T304"/>
+      <x:c r="U304" t="str">
+        <x:v>NS</x:v>
+      </x:c>
+      <x:c r="V304" t="str">
+        <x:v>units</x:v>
+      </x:c>
+      <x:c r="W304"/>
+      <x:c r="X304"/>
+      <x:c r="Y304" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z304" t="str">
+        <x:v>Service_1983_primary; PDF pp2–3; Results and Figure 4</x:v>
+      </x:c>
+      <x:c r="AA304" t="str">
+        <x:v>C-peptide model-derived secretion as reported; no significant time-of-day effect.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="305">
+      <x:c r="A305" t="str">
+        <x:v>O0328</x:v>
+      </x:c>
+      <x:c r="B305" t="str">
+        <x:v>Service_1983</x:v>
+      </x:c>
+      <x:c r="C305" t="str">
+        <x:v>Service_1983_all</x:v>
+      </x:c>
+      <x:c r="D305" t="str">
+        <x:v>Service_supportive</x:v>
+      </x:c>
+      <x:c r="E305" t="str">
+        <x:v>Service_large_13</x:v>
+      </x:c>
+      <x:c r="F305" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G305" t="str">
+        <x:v>large</x:v>
+      </x:c>
+      <x:c r="H305" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I305" t="str">
+        <x:v>insulin_secretion</x:v>
+      </x:c>
+      <x:c r="J305" t="str">
+        <x:v>Large-meal insulin secretion from C-peptide</x:v>
+      </x:c>
+      <x:c r="K305"/>
+      <x:c r="L305" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="M305"/>
+      <x:c r="N305" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O305" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="P305" t="n">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="Q305" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R305" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="S305"/>
+      <x:c r="T305"/>
+      <x:c r="U305" t="str">
+        <x:v>NS</x:v>
+      </x:c>
+      <x:c r="V305" t="str">
+        <x:v>units</x:v>
+      </x:c>
+      <x:c r="W305"/>
+      <x:c r="X305"/>
+      <x:c r="Y305" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z305" t="str">
+        <x:v>Service_1983_primary; PDF pp2–3; Results and Figure 4</x:v>
+      </x:c>
+      <x:c r="AA305" t="str">
+        <x:v>C-peptide model-derived secretion as reported; no significant time-of-day effect.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="306">
+      <x:c r="A306" t="str">
+        <x:v>O0329</x:v>
+      </x:c>
+      <x:c r="B306" t="str">
+        <x:v>Service_1983</x:v>
+      </x:c>
+      <x:c r="C306" t="str">
+        <x:v>Service_1983_all</x:v>
+      </x:c>
+      <x:c r="D306" t="str">
+        <x:v>Service_supportive</x:v>
+      </x:c>
+      <x:c r="E306" t="str">
+        <x:v>Service_large_18</x:v>
+      </x:c>
+      <x:c r="F306" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G306" t="str">
+        <x:v>large</x:v>
+      </x:c>
+      <x:c r="H306" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I306" t="str">
+        <x:v>insulin_secretion</x:v>
+      </x:c>
+      <x:c r="J306" t="str">
+        <x:v>Large-meal insulin secretion from C-peptide</x:v>
+      </x:c>
+      <x:c r="K306"/>
+      <x:c r="L306" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="M306"/>
+      <x:c r="N306" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O306" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="P306" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="Q306" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R306" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="S306"/>
+      <x:c r="T306"/>
+      <x:c r="U306" t="str">
+        <x:v>NS</x:v>
+      </x:c>
+      <x:c r="V306" t="str">
+        <x:v>units</x:v>
+      </x:c>
+      <x:c r="W306"/>
+      <x:c r="X306"/>
+      <x:c r="Y306" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z306" t="str">
+        <x:v>Service_1983_primary; PDF pp2–3; Results and Figure 4</x:v>
+      </x:c>
+      <x:c r="AA306" t="str">
+        <x:v>C-peptide model-derived secretion as reported; no significant time-of-day effect.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="307">
+      <x:c r="A307" t="str">
+        <x:v>O0330</x:v>
+      </x:c>
+      <x:c r="B307" t="str">
+        <x:v>Service_1983</x:v>
+      </x:c>
+      <x:c r="C307" t="str">
+        <x:v>Service_1983_all</x:v>
+      </x:c>
+      <x:c r="D307" t="str">
+        <x:v>Service_supportive</x:v>
+      </x:c>
+      <x:c r="E307"/>
+      <x:c r="F307"/>
+      <x:c r="G307"/>
+      <x:c r="H307" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I307" t="str">
+        <x:v>timed_insulin</x:v>
+      </x:c>
+      <x:c r="J307" t="str">
+        <x:v>Insulin response across all meal sizes</x:v>
+      </x:c>
+      <x:c r="K307"/>
+      <x:c r="L307" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="M307"/>
+      <x:c r="N307" t="str">
+        <x:v>narrative_only</x:v>
+      </x:c>
+      <x:c r="O307" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="P307"/>
+      <x:c r="Q307"/>
+      <x:c r="R307"/>
+      <x:c r="S307"/>
+      <x:c r="T307"/>
+      <x:c r="U307" t="str">
+        <x:v>NS</x:v>
+      </x:c>
+      <x:c r="V307"/>
+      <x:c r="W307" t="str">
+        <x:v>no significant difference</x:v>
+      </x:c>
+      <x:c r="X307"/>
+      <x:c r="Y307" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z307" t="str">
+        <x:v>Service_1983_primary; PDF pp2–3; Results and Figures 1,3</x:v>
+      </x:c>
+      <x:c r="AA307" t="str">
+        <x:v>Time of day did not significantly affect plasma insulin for small, medium or large meals. Large-meal numerical series extracted separately.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="308">
+      <x:c r="A308" t="str">
+        <x:v>O0331</x:v>
+      </x:c>
+      <x:c r="B308" t="str">
+        <x:v>Haldar_2020</x:v>
+      </x:c>
+      <x:c r="C308" t="str">
+        <x:v>Haldar_2020_all</x:v>
+      </x:c>
+      <x:c r="D308" t="str">
+        <x:v>Haldar_supportive</x:v>
+      </x:c>
+      <x:c r="E308" t="str">
+        <x:v>Haldar_high_breakfast</x:v>
+      </x:c>
+      <x:c r="F308" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G308" t="str">
+        <x:v>high GI</x:v>
+      </x:c>
+      <x:c r="H308" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I308" t="str">
+        <x:v>glucose_auc</x:v>
+      </x:c>
+      <x:c r="J308" t="str">
+        <x:v>Subsequent-meal glucose iAUC</x:v>
+      </x:c>
+      <x:c r="K308" t="str">
+        <x:v>incremental</x:v>
+      </x:c>
+      <x:c r="L308" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="M308"/>
+      <x:c r="N308" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O308" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P308" t="n">
+        <x:v>140.7</x:v>
+      </x:c>
+      <x:c r="Q308" t="str">
+        <x:v>SD</x:v>
+      </x:c>
+      <x:c r="R308" t="n">
+        <x:v>155.36</x:v>
+      </x:c>
+      <x:c r="S308"/>
+      <x:c r="T308"/>
+      <x:c r="U308"/>
+      <x:c r="V308" t="str">
+        <x:v>not explicitly printed</x:v>
+      </x:c>
+      <x:c r="W308"/>
+      <x:c r="X308"/>
+      <x:c r="Y308" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z308" t="str">
+        <x:v>Haldar_2020_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA308" t="str">
+        <x:v>Subsequent lunch after breakfast test meal versus next-breakfast after dinner test meal; contextual, not the index-meal contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="309">
+      <x:c r="A309" t="str">
+        <x:v>O0332</x:v>
+      </x:c>
+      <x:c r="B309" t="str">
+        <x:v>Haldar_2020</x:v>
+      </x:c>
+      <x:c r="C309" t="str">
+        <x:v>Haldar_2020_all</x:v>
+      </x:c>
+      <x:c r="D309" t="str">
+        <x:v>Haldar_supportive</x:v>
+      </x:c>
+      <x:c r="E309" t="str">
+        <x:v>Haldar_high_dinner</x:v>
+      </x:c>
+      <x:c r="F309" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G309" t="str">
+        <x:v>high GI</x:v>
+      </x:c>
+      <x:c r="H309" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I309" t="str">
+        <x:v>glucose_auc</x:v>
+      </x:c>
+      <x:c r="J309" t="str">
+        <x:v>Subsequent-meal glucose iAUC</x:v>
+      </x:c>
+      <x:c r="K309" t="str">
+        <x:v>incremental</x:v>
+      </x:c>
+      <x:c r="L309" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="M309"/>
+      <x:c r="N309" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O309" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P309" t="n">
+        <x:v>320.57</x:v>
+      </x:c>
+      <x:c r="Q309" t="str">
+        <x:v>SD</x:v>
+      </x:c>
+      <x:c r="R309" t="n">
+        <x:v>151.72</x:v>
+      </x:c>
+      <x:c r="S309"/>
+      <x:c r="T309"/>
+      <x:c r="U309"/>
+      <x:c r="V309" t="str">
+        <x:v>not explicitly printed</x:v>
+      </x:c>
+      <x:c r="W309"/>
+      <x:c r="X309"/>
+      <x:c r="Y309" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z309" t="str">
+        <x:v>Haldar_2020_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA309" t="str">
+        <x:v>Subsequent lunch after breakfast test meal versus next-breakfast after dinner test meal; contextual, not the index-meal contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="310">
+      <x:c r="A310" t="str">
+        <x:v>O0333</x:v>
+      </x:c>
+      <x:c r="B310" t="str">
+        <x:v>Haldar_2020</x:v>
+      </x:c>
+      <x:c r="C310" t="str">
+        <x:v>Haldar_2020_all</x:v>
+      </x:c>
+      <x:c r="D310" t="str">
+        <x:v>Haldar_supportive</x:v>
+      </x:c>
+      <x:c r="E310" t="str">
+        <x:v>Haldar_low_breakfast</x:v>
+      </x:c>
+      <x:c r="F310" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G310" t="str">
+        <x:v>low GI</x:v>
+      </x:c>
+      <x:c r="H310" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I310" t="str">
+        <x:v>glucose_auc</x:v>
+      </x:c>
+      <x:c r="J310" t="str">
+        <x:v>Subsequent-meal glucose iAUC</x:v>
+      </x:c>
+      <x:c r="K310" t="str">
+        <x:v>incremental</x:v>
+      </x:c>
+      <x:c r="L310" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="M310"/>
+      <x:c r="N310" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O310" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P310" t="n">
+        <x:v>93.83</x:v>
+      </x:c>
+      <x:c r="Q310" t="str">
+        <x:v>SD</x:v>
+      </x:c>
+      <x:c r="R310" t="n">
+        <x:v>156.48</x:v>
+      </x:c>
+      <x:c r="S310"/>
+      <x:c r="T310"/>
+      <x:c r="U310"/>
+      <x:c r="V310" t="str">
+        <x:v>not explicitly printed</x:v>
+      </x:c>
+      <x:c r="W310"/>
+      <x:c r="X310"/>
+      <x:c r="Y310" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z310" t="str">
+        <x:v>Haldar_2020_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA310" t="str">
+        <x:v>Subsequent lunch after breakfast test meal versus next-breakfast after dinner test meal; contextual, not the index-meal contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="311">
+      <x:c r="A311" t="str">
+        <x:v>O0334</x:v>
+      </x:c>
+      <x:c r="B311" t="str">
+        <x:v>Haldar_2020</x:v>
+      </x:c>
+      <x:c r="C311" t="str">
+        <x:v>Haldar_2020_all</x:v>
+      </x:c>
+      <x:c r="D311" t="str">
+        <x:v>Haldar_supportive</x:v>
+      </x:c>
+      <x:c r="E311" t="str">
+        <x:v>Haldar_low_dinner</x:v>
+      </x:c>
+      <x:c r="F311" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G311" t="str">
+        <x:v>low GI</x:v>
+      </x:c>
+      <x:c r="H311" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I311" t="str">
+        <x:v>glucose_auc</x:v>
+      </x:c>
+      <x:c r="J311" t="str">
+        <x:v>Subsequent-meal glucose iAUC</x:v>
+      </x:c>
+      <x:c r="K311" t="str">
+        <x:v>incremental</x:v>
+      </x:c>
+      <x:c r="L311" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="M311"/>
+      <x:c r="N311" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O311" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P311" t="n">
+        <x:v>225.52</x:v>
+      </x:c>
+      <x:c r="Q311" t="str">
+        <x:v>SD</x:v>
+      </x:c>
+      <x:c r="R311" t="n">
+        <x:v>108.36</x:v>
+      </x:c>
+      <x:c r="S311"/>
+      <x:c r="T311"/>
+      <x:c r="U311"/>
+      <x:c r="V311" t="str">
+        <x:v>not explicitly printed</x:v>
+      </x:c>
+      <x:c r="W311"/>
+      <x:c r="X311"/>
+      <x:c r="Y311" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z311" t="str">
+        <x:v>Haldar_2020_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA311" t="str">
+        <x:v>Subsequent lunch after breakfast test meal versus next-breakfast after dinner test meal; contextual, not the index-meal contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="312">
+      <x:c r="A312" t="str">
+        <x:v>O0335</x:v>
+      </x:c>
+      <x:c r="B312" t="str">
+        <x:v>Haldar_2020</x:v>
+      </x:c>
+      <x:c r="C312" t="str">
+        <x:v>Haldar_2020_all</x:v>
+      </x:c>
+      <x:c r="D312" t="str">
+        <x:v>Haldar_supportive</x:v>
+      </x:c>
+      <x:c r="E312" t="str">
+        <x:v>Haldar_high_breakfast</x:v>
+      </x:c>
+      <x:c r="F312" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G312" t="str">
+        <x:v>high GI</x:v>
+      </x:c>
+      <x:c r="H312" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I312" t="str">
+        <x:v>insulin_auc</x:v>
+      </x:c>
+      <x:c r="J312" t="str">
+        <x:v>Subsequent-meal insulin iAUC</x:v>
+      </x:c>
+      <x:c r="K312" t="str">
+        <x:v>incremental</x:v>
+      </x:c>
+      <x:c r="L312" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="M312"/>
+      <x:c r="N312" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O312" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P312" t="n">
+        <x:v>2447.71</x:v>
+      </x:c>
+      <x:c r="Q312" t="str">
+        <x:v>SD</x:v>
+      </x:c>
+      <x:c r="R312" t="n">
+        <x:v>1651.66</x:v>
+      </x:c>
+      <x:c r="S312"/>
+      <x:c r="T312"/>
+      <x:c r="U312"/>
+      <x:c r="V312" t="str">
+        <x:v>not explicitly printed</x:v>
+      </x:c>
+      <x:c r="W312"/>
+      <x:c r="X312"/>
+      <x:c r="Y312" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z312" t="str">
+        <x:v>Haldar_2020_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA312" t="str">
+        <x:v>Subsequent lunch after breakfast test meal versus next-breakfast after dinner test meal; contextual, not the index-meal contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="313">
+      <x:c r="A313" t="str">
+        <x:v>O0336</x:v>
+      </x:c>
+      <x:c r="B313" t="str">
+        <x:v>Haldar_2020</x:v>
+      </x:c>
+      <x:c r="C313" t="str">
+        <x:v>Haldar_2020_all</x:v>
+      </x:c>
+      <x:c r="D313" t="str">
+        <x:v>Haldar_supportive</x:v>
+      </x:c>
+      <x:c r="E313" t="str">
+        <x:v>Haldar_high_dinner</x:v>
+      </x:c>
+      <x:c r="F313" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G313" t="str">
+        <x:v>high GI</x:v>
+      </x:c>
+      <x:c r="H313" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I313" t="str">
+        <x:v>insulin_auc</x:v>
+      </x:c>
+      <x:c r="J313" t="str">
+        <x:v>Subsequent-meal insulin iAUC</x:v>
+      </x:c>
+      <x:c r="K313" t="str">
+        <x:v>incremental</x:v>
+      </x:c>
+      <x:c r="L313" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="M313"/>
+      <x:c r="N313" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O313" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P313" t="n">
+        <x:v>5684.67</x:v>
+      </x:c>
+      <x:c r="Q313" t="str">
+        <x:v>SD</x:v>
+      </x:c>
+      <x:c r="R313" t="n">
+        <x:v>3420.26</x:v>
+      </x:c>
+      <x:c r="S313"/>
+      <x:c r="T313"/>
+      <x:c r="U313"/>
+      <x:c r="V313" t="str">
+        <x:v>not explicitly printed</x:v>
+      </x:c>
+      <x:c r="W313"/>
+      <x:c r="X313"/>
+      <x:c r="Y313" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z313" t="str">
+        <x:v>Haldar_2020_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA313" t="str">
+        <x:v>Subsequent lunch after breakfast test meal versus next-breakfast after dinner test meal; contextual, not the index-meal contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="314">
+      <x:c r="A314" t="str">
+        <x:v>O0337</x:v>
+      </x:c>
+      <x:c r="B314" t="str">
+        <x:v>Haldar_2020</x:v>
+      </x:c>
+      <x:c r="C314" t="str">
+        <x:v>Haldar_2020_all</x:v>
+      </x:c>
+      <x:c r="D314" t="str">
+        <x:v>Haldar_supportive</x:v>
+      </x:c>
+      <x:c r="E314" t="str">
+        <x:v>Haldar_low_breakfast</x:v>
+      </x:c>
+      <x:c r="F314" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G314" t="str">
+        <x:v>low GI</x:v>
+      </x:c>
+      <x:c r="H314" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I314" t="str">
+        <x:v>insulin_auc</x:v>
+      </x:c>
+      <x:c r="J314" t="str">
+        <x:v>Subsequent-meal insulin iAUC</x:v>
+      </x:c>
+      <x:c r="K314" t="str">
+        <x:v>incremental</x:v>
+      </x:c>
+      <x:c r="L314" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="M314"/>
+      <x:c r="N314" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O314" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P314" t="n">
+        <x:v>3454.72</x:v>
+      </x:c>
+      <x:c r="Q314" t="str">
+        <x:v>SD</x:v>
+      </x:c>
+      <x:c r="R314" t="n">
+        <x:v>2338.81</x:v>
+      </x:c>
+      <x:c r="S314"/>
+      <x:c r="T314"/>
+      <x:c r="U314"/>
+      <x:c r="V314" t="str">
+        <x:v>not explicitly printed</x:v>
+      </x:c>
+      <x:c r="W314"/>
+      <x:c r="X314"/>
+      <x:c r="Y314" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z314" t="str">
+        <x:v>Haldar_2020_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA314" t="str">
+        <x:v>Subsequent lunch after breakfast test meal versus next-breakfast after dinner test meal; contextual, not the index-meal contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="315">
+      <x:c r="A315" t="str">
+        <x:v>O0338</x:v>
+      </x:c>
+      <x:c r="B315" t="str">
+        <x:v>Haldar_2020</x:v>
+      </x:c>
+      <x:c r="C315" t="str">
+        <x:v>Haldar_2020_all</x:v>
+      </x:c>
+      <x:c r="D315" t="str">
+        <x:v>Haldar_supportive</x:v>
+      </x:c>
+      <x:c r="E315" t="str">
+        <x:v>Haldar_low_dinner</x:v>
+      </x:c>
+      <x:c r="F315" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G315" t="str">
+        <x:v>low GI</x:v>
+      </x:c>
+      <x:c r="H315" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I315" t="str">
+        <x:v>insulin_auc</x:v>
+      </x:c>
+      <x:c r="J315" t="str">
+        <x:v>Subsequent-meal insulin iAUC</x:v>
+      </x:c>
+      <x:c r="K315" t="str">
+        <x:v>incremental</x:v>
+      </x:c>
+      <x:c r="L315" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="M315"/>
+      <x:c r="N315" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O315" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P315" t="n">
+        <x:v>5141.35</x:v>
+      </x:c>
+      <x:c r="Q315" t="str">
+        <x:v>SD</x:v>
+      </x:c>
+      <x:c r="R315" t="n">
+        <x:v>2288.56</x:v>
+      </x:c>
+      <x:c r="S315"/>
+      <x:c r="T315"/>
+      <x:c r="U315"/>
+      <x:c r="V315" t="str">
+        <x:v>not explicitly printed</x:v>
+      </x:c>
+      <x:c r="W315"/>
+      <x:c r="X315"/>
+      <x:c r="Y315" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z315" t="str">
+        <x:v>Haldar_2020_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA315" t="str">
+        <x:v>Subsequent lunch after breakfast test meal versus next-breakfast after dinner test meal; contextual, not the index-meal contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="316">
+      <x:c r="A316" t="str">
+        <x:v>O0339</x:v>
+      </x:c>
+      <x:c r="B316" t="str">
+        <x:v>Haldar_2020</x:v>
+      </x:c>
+      <x:c r="C316" t="str">
+        <x:v>Haldar_2020_all</x:v>
+      </x:c>
+      <x:c r="D316" t="str">
+        <x:v>Haldar_overall_daypart</x:v>
+      </x:c>
+      <x:c r="E316"/>
+      <x:c r="F316"/>
+      <x:c r="G316"/>
+      <x:c r="H316" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I316" t="str">
+        <x:v>timed_insulin</x:v>
+      </x:c>
+      <x:c r="J316" t="str">
+        <x:v>Overall test-meal insulin timing contrast</x:v>
+      </x:c>
+      <x:c r="K316" t="str">
+        <x:v>incremental</x:v>
+      </x:c>
+      <x:c r="L316" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="M316"/>
+      <x:c r="N316" t="str">
+        <x:v>model_contrast</x:v>
+      </x:c>
+      <x:c r="O316" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P316" t="n">
+        <x:v>865.96</x:v>
+      </x:c>
+      <x:c r="Q316"/>
+      <x:c r="R316"/>
+      <x:c r="S316"/>
+      <x:c r="T316"/>
+      <x:c r="U316" t="str">
+        <x:v>&lt;0.05</x:v>
+      </x:c>
+      <x:c r="V316" t="str">
+        <x:v>not explicitly printed</x:v>
+      </x:c>
+      <x:c r="W316" t="str">
+        <x:v>dinner minus breakfast</x:v>
+      </x:c>
+      <x:c r="X316"/>
+      <x:c r="Y316" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z316" t="str">
+        <x:v>Haldar_2020_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA316"/>
+    </x:row>
+    <x:row r="317">
+      <x:c r="A317" t="str">
+        <x:v>O0340</x:v>
+      </x:c>
+      <x:c r="B317" t="str">
+        <x:v>Haldar_2020</x:v>
+      </x:c>
+      <x:c r="C317" t="str">
+        <x:v>Haldar_2020_all</x:v>
+      </x:c>
+      <x:c r="D317" t="str">
+        <x:v>Haldar_supportive</x:v>
+      </x:c>
+      <x:c r="E317"/>
+      <x:c r="F317"/>
+      <x:c r="G317"/>
+      <x:c r="H317" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I317" t="str">
+        <x:v>glucose_auc</x:v>
+      </x:c>
+      <x:c r="J317" t="str">
+        <x:v>Overall subsequent-meal timing contrast</x:v>
+      </x:c>
+      <x:c r="K317" t="str">
+        <x:v>incremental</x:v>
+      </x:c>
+      <x:c r="L317" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="M317"/>
+      <x:c r="N317" t="str">
+        <x:v>model_contrast</x:v>
+      </x:c>
+      <x:c r="O317" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P317" t="n">
+        <x:v>155.78</x:v>
+      </x:c>
+      <x:c r="Q317"/>
+      <x:c r="R317"/>
+      <x:c r="S317"/>
+      <x:c r="T317"/>
+      <x:c r="U317" t="str">
+        <x:v>&lt;0.0001</x:v>
+      </x:c>
+      <x:c r="V317" t="str">
+        <x:v>not explicitly printed</x:v>
+      </x:c>
+      <x:c r="W317" t="str">
+        <x:v>after dinner minus after breakfast test meal</x:v>
+      </x:c>
+      <x:c r="X317"/>
+      <x:c r="Y317" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z317" t="str">
+        <x:v>Haldar_2020_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA317" t="str">
+        <x:v>Different subsequent meal occasions; contextual result.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="318">
+      <x:c r="A318" t="str">
+        <x:v>O0341</x:v>
+      </x:c>
+      <x:c r="B318" t="str">
+        <x:v>Haldar_2020</x:v>
+      </x:c>
+      <x:c r="C318" t="str">
+        <x:v>Haldar_2020_all</x:v>
+      </x:c>
+      <x:c r="D318" t="str">
+        <x:v>Haldar_supportive</x:v>
+      </x:c>
+      <x:c r="E318"/>
+      <x:c r="F318"/>
+      <x:c r="G318"/>
+      <x:c r="H318" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I318" t="str">
+        <x:v>insulin_auc</x:v>
+      </x:c>
+      <x:c r="J318" t="str">
+        <x:v>Overall subsequent-meal timing contrast</x:v>
+      </x:c>
+      <x:c r="K318" t="str">
+        <x:v>incremental</x:v>
+      </x:c>
+      <x:c r="L318" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="M318"/>
+      <x:c r="N318" t="str">
+        <x:v>model_contrast</x:v>
+      </x:c>
+      <x:c r="O318" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P318" t="n">
+        <x:v>2462.41</x:v>
+      </x:c>
+      <x:c r="Q318"/>
+      <x:c r="R318"/>
+      <x:c r="S318"/>
+      <x:c r="T318"/>
+      <x:c r="U318" t="str">
+        <x:v>&lt;0.0001</x:v>
+      </x:c>
+      <x:c r="V318" t="str">
+        <x:v>not explicitly printed</x:v>
+      </x:c>
+      <x:c r="W318" t="str">
+        <x:v>after dinner minus after breakfast test meal</x:v>
+      </x:c>
+      <x:c r="X318"/>
+      <x:c r="Y318" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z318" t="str">
+        <x:v>Haldar_2020_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA318" t="str">
+        <x:v>Different subsequent meal occasions; contextual result.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="319">
+      <x:c r="A319" t="str">
+        <x:v>O0342</x:v>
+      </x:c>
+      <x:c r="B319" t="str">
+        <x:v>Garaulet_2022</x:v>
+      </x:c>
+      <x:c r="C319" t="str">
+        <x:v>Garaulet_2022_all</x:v>
+      </x:c>
+      <x:c r="D319" t="str">
+        <x:v>Garaulet_OGTT_all</x:v>
+      </x:c>
+      <x:c r="E319"/>
+      <x:c r="F319"/>
+      <x:c r="G319" t="str">
+        <x:v>MTNR1B all</x:v>
+      </x:c>
+      <x:c r="H319" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I319" t="str">
+        <x:v>glucose_auc</x:v>
+      </x:c>
+      <x:c r="J319" t="str">
+        <x:v>glucose AUC paired difference</x:v>
+      </x:c>
+      <x:c r="K319" t="str">
+        <x:v>incremental</x:v>
+      </x:c>
+      <x:c r="L319" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="M319"/>
+      <x:c r="N319" t="str">
+        <x:v>within_person_contrast</x:v>
+      </x:c>
+      <x:c r="O319" t="n">
+        <x:v>845</x:v>
+      </x:c>
+      <x:c r="P319" t="n">
+        <x:v>22.92</x:v>
+      </x:c>
+      <x:c r="Q319" t="str">
+        <x:v>SD (paired difference)</x:v>
+      </x:c>
+      <x:c r="R319" t="n">
+        <x:v>43.96</x:v>
+      </x:c>
+      <x:c r="S319"/>
+      <x:c r="T319"/>
+      <x:c r="U319"/>
+      <x:c r="V319" t="str">
+        <x:v>mg×h/dL</x:v>
+      </x:c>
+      <x:c r="W319" t="str">
+        <x:v>late minus early</x:v>
+      </x:c>
+      <x:c r="X319"/>
+      <x:c r="Y319" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z319" t="str">
+        <x:v>Garaulet_2022_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA319" t="str">
+        <x:v>Table P values compare genotypes, not the within-person timing effect; not assigned to this contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="320">
+      <x:c r="A320" t="str">
+        <x:v>O0343</x:v>
+      </x:c>
+      <x:c r="B320" t="str">
+        <x:v>Garaulet_2022</x:v>
+      </x:c>
+      <x:c r="C320" t="str">
+        <x:v>Garaulet_2022_all</x:v>
+      </x:c>
+      <x:c r="D320" t="str">
+        <x:v>Garaulet_OGTT_CC</x:v>
+      </x:c>
+      <x:c r="E320"/>
+      <x:c r="F320"/>
+      <x:c r="G320" t="str">
+        <x:v>MTNR1B CC</x:v>
+      </x:c>
+      <x:c r="H320" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I320" t="str">
+        <x:v>glucose_auc</x:v>
+      </x:c>
+      <x:c r="J320" t="str">
+        <x:v>glucose AUC paired difference</x:v>
+      </x:c>
+      <x:c r="K320" t="str">
+        <x:v>incremental</x:v>
+      </x:c>
+      <x:c r="L320" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="M320"/>
+      <x:c r="N320" t="str">
+        <x:v>within_person_contrast</x:v>
+      </x:c>
+      <x:c r="O320" t="n">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="P320" t="n">
+        <x:v>15.48</x:v>
+      </x:c>
+      <x:c r="Q320" t="str">
+        <x:v>SD (paired difference)</x:v>
+      </x:c>
+      <x:c r="R320" t="n">
+        <x:v>39.28</x:v>
+      </x:c>
+      <x:c r="S320"/>
+      <x:c r="T320"/>
+      <x:c r="U320"/>
+      <x:c r="V320" t="str">
+        <x:v>mg×h/dL</x:v>
+      </x:c>
+      <x:c r="W320" t="str">
+        <x:v>late minus early</x:v>
+      </x:c>
+      <x:c r="X320"/>
+      <x:c r="Y320" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z320" t="str">
+        <x:v>Garaulet_2022_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA320" t="str">
+        <x:v>Table P values compare genotypes, not the within-person timing effect; not assigned to this contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="321">
+      <x:c r="A321" t="str">
+        <x:v>O0344</x:v>
+      </x:c>
+      <x:c r="B321" t="str">
+        <x:v>Garaulet_2022</x:v>
+      </x:c>
+      <x:c r="C321" t="str">
+        <x:v>Garaulet_2022_all</x:v>
+      </x:c>
+      <x:c r="D321" t="str">
+        <x:v>Garaulet_OGTT_CG</x:v>
+      </x:c>
+      <x:c r="E321"/>
+      <x:c r="F321"/>
+      <x:c r="G321" t="str">
+        <x:v>MTNR1B CG</x:v>
+      </x:c>
+      <x:c r="H321" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I321" t="str">
+        <x:v>glucose_auc</x:v>
+      </x:c>
+      <x:c r="J321" t="str">
+        <x:v>glucose AUC paired difference</x:v>
+      </x:c>
+      <x:c r="K321" t="str">
+        <x:v>incremental</x:v>
+      </x:c>
+      <x:c r="L321" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="M321"/>
+      <x:c r="N321" t="str">
+        <x:v>within_person_contrast</x:v>
+      </x:c>
+      <x:c r="O321" t="n">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="P321" t="n">
+        <x:v>28.36</x:v>
+      </x:c>
+      <x:c r="Q321" t="str">
+        <x:v>SD (paired difference)</x:v>
+      </x:c>
+      <x:c r="R321" t="n">
+        <x:v>47.89</x:v>
+      </x:c>
+      <x:c r="S321"/>
+      <x:c r="T321"/>
+      <x:c r="U321"/>
+      <x:c r="V321" t="str">
+        <x:v>mg×h/dL</x:v>
+      </x:c>
+      <x:c r="W321" t="str">
+        <x:v>late minus early</x:v>
+      </x:c>
+      <x:c r="X321"/>
+      <x:c r="Y321" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z321" t="str">
+        <x:v>Garaulet_2022_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA321" t="str">
+        <x:v>Table P values compare genotypes, not the within-person timing effect; not assigned to this contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="322">
+      <x:c r="A322" t="str">
+        <x:v>O0345</x:v>
+      </x:c>
+      <x:c r="B322" t="str">
+        <x:v>Garaulet_2022</x:v>
+      </x:c>
+      <x:c r="C322" t="str">
+        <x:v>Garaulet_2022_all</x:v>
+      </x:c>
+      <x:c r="D322" t="str">
+        <x:v>Garaulet_OGTT_GG</x:v>
+      </x:c>
+      <x:c r="E322"/>
+      <x:c r="F322"/>
+      <x:c r="G322" t="str">
+        <x:v>MTNR1B GG</x:v>
+      </x:c>
+      <x:c r="H322" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I322" t="str">
+        <x:v>glucose_auc</x:v>
+      </x:c>
+      <x:c r="J322" t="str">
+        <x:v>glucose AUC paired difference</x:v>
+      </x:c>
+      <x:c r="K322" t="str">
+        <x:v>incremental</x:v>
+      </x:c>
+      <x:c r="L322" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="M322"/>
+      <x:c r="N322" t="str">
+        <x:v>within_person_contrast</x:v>
+      </x:c>
+      <x:c r="O322" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="P322" t="n">
+        <x:v>38.95</x:v>
+      </x:c>
+      <x:c r="Q322" t="str">
+        <x:v>SD (paired difference)</x:v>
+      </x:c>
+      <x:c r="R322" t="n">
+        <x:v>42.66</x:v>
+      </x:c>
+      <x:c r="S322"/>
+      <x:c r="T322"/>
+      <x:c r="U322"/>
+      <x:c r="V322" t="str">
+        <x:v>mg×h/dL</x:v>
+      </x:c>
+      <x:c r="W322" t="str">
+        <x:v>late minus early</x:v>
+      </x:c>
+      <x:c r="X322"/>
+      <x:c r="Y322" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z322" t="str">
+        <x:v>Garaulet_2022_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA322" t="str">
+        <x:v>Table P values compare genotypes, not the within-person timing effect; not assigned to this contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="323">
+      <x:c r="A323" t="str">
+        <x:v>O0346</x:v>
+      </x:c>
+      <x:c r="B323" t="str">
+        <x:v>Garaulet_2022</x:v>
+      </x:c>
+      <x:c r="C323" t="str">
+        <x:v>Garaulet_2022_all</x:v>
+      </x:c>
+      <x:c r="D323" t="str">
+        <x:v>Garaulet_OGTT_all</x:v>
+      </x:c>
+      <x:c r="E323"/>
+      <x:c r="F323"/>
+      <x:c r="G323" t="str">
+        <x:v>MTNR1B all</x:v>
+      </x:c>
+      <x:c r="H323" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I323" t="str">
+        <x:v>insulin_auc</x:v>
+      </x:c>
+      <x:c r="J323" t="str">
+        <x:v>insulin AUC paired difference</x:v>
+      </x:c>
+      <x:c r="K323" t="str">
+        <x:v>incremental</x:v>
+      </x:c>
+      <x:c r="L323" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="M323"/>
+      <x:c r="N323" t="str">
+        <x:v>within_person_contrast</x:v>
+      </x:c>
+      <x:c r="O323" t="n">
+        <x:v>845</x:v>
+      </x:c>
+      <x:c r="P323" t="n">
+        <x:v>-6.58</x:v>
+      </x:c>
+      <x:c r="Q323" t="str">
+        <x:v>SD (paired difference)</x:v>
+      </x:c>
+      <x:c r="R323" t="n">
+        <x:v>53.71</x:v>
+      </x:c>
+      <x:c r="S323"/>
+      <x:c r="T323"/>
+      <x:c r="U323"/>
+      <x:c r="V323" t="str">
+        <x:v>µU×h/mL</x:v>
+      </x:c>
+      <x:c r="W323" t="str">
+        <x:v>late minus early</x:v>
+      </x:c>
+      <x:c r="X323"/>
+      <x:c r="Y323" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z323" t="str">
+        <x:v>Garaulet_2022_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA323" t="str">
+        <x:v>Table P values compare genotypes, not the within-person timing effect; not assigned to this contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="324">
+      <x:c r="A324" t="str">
+        <x:v>O0347</x:v>
+      </x:c>
+      <x:c r="B324" t="str">
+        <x:v>Garaulet_2022</x:v>
+      </x:c>
+      <x:c r="C324" t="str">
+        <x:v>Garaulet_2022_all</x:v>
+      </x:c>
+      <x:c r="D324" t="str">
+        <x:v>Garaulet_OGTT_CC</x:v>
+      </x:c>
+      <x:c r="E324"/>
+      <x:c r="F324"/>
+      <x:c r="G324" t="str">
+        <x:v>MTNR1B CC</x:v>
+      </x:c>
+      <x:c r="H324" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I324" t="str">
+        <x:v>insulin_auc</x:v>
+      </x:c>
+      <x:c r="J324" t="str">
+        <x:v>insulin AUC paired difference</x:v>
+      </x:c>
+      <x:c r="K324" t="str">
+        <x:v>incremental</x:v>
+      </x:c>
+      <x:c r="L324" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="M324"/>
+      <x:c r="N324" t="str">
+        <x:v>within_person_contrast</x:v>
+      </x:c>
+      <x:c r="O324" t="n">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="P324" t="n">
+        <x:v>-0.19</x:v>
+      </x:c>
+      <x:c r="Q324" t="str">
+        <x:v>SD (paired difference)</x:v>
+      </x:c>
+      <x:c r="R324" t="n">
+        <x:v>55.16</x:v>
+      </x:c>
+      <x:c r="S324"/>
+      <x:c r="T324"/>
+      <x:c r="U324"/>
+      <x:c r="V324" t="str">
+        <x:v>µU×h/mL</x:v>
+      </x:c>
+      <x:c r="W324" t="str">
+        <x:v>late minus early</x:v>
+      </x:c>
+      <x:c r="X324"/>
+      <x:c r="Y324" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z324" t="str">
+        <x:v>Garaulet_2022_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA324" t="str">
+        <x:v>Table P values compare genotypes, not the within-person timing effect; not assigned to this contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="325">
+      <x:c r="A325" t="str">
+        <x:v>O0348</x:v>
+      </x:c>
+      <x:c r="B325" t="str">
+        <x:v>Garaulet_2022</x:v>
+      </x:c>
+      <x:c r="C325" t="str">
+        <x:v>Garaulet_2022_all</x:v>
+      </x:c>
+      <x:c r="D325" t="str">
+        <x:v>Garaulet_OGTT_CG</x:v>
+      </x:c>
+      <x:c r="E325"/>
+      <x:c r="F325"/>
+      <x:c r="G325" t="str">
+        <x:v>MTNR1B CG</x:v>
+      </x:c>
+      <x:c r="H325" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I325" t="str">
+        <x:v>insulin_auc</x:v>
+      </x:c>
+      <x:c r="J325" t="str">
+        <x:v>insulin AUC paired difference</x:v>
+      </x:c>
+      <x:c r="K325" t="str">
+        <x:v>incremental</x:v>
+      </x:c>
+      <x:c r="L325" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="M325"/>
+      <x:c r="N325" t="str">
+        <x:v>within_person_contrast</x:v>
+      </x:c>
+      <x:c r="O325" t="n">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="P325" t="n">
+        <x:v>-12.67</x:v>
+      </x:c>
+      <x:c r="Q325" t="str">
+        <x:v>SD (paired difference)</x:v>
+      </x:c>
+      <x:c r="R325" t="n">
+        <x:v>52.36</x:v>
+      </x:c>
+      <x:c r="S325"/>
+      <x:c r="T325"/>
+      <x:c r="U325"/>
+      <x:c r="V325" t="str">
+        <x:v>µU×h/mL</x:v>
+      </x:c>
+      <x:c r="W325" t="str">
+        <x:v>late minus early</x:v>
+      </x:c>
+      <x:c r="X325"/>
+      <x:c r="Y325" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z325" t="str">
+        <x:v>Garaulet_2022_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA325" t="str">
+        <x:v>Table P values compare genotypes, not the within-person timing effect; not assigned to this contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="326">
+      <x:c r="A326" t="str">
+        <x:v>O0349</x:v>
+      </x:c>
+      <x:c r="B326" t="str">
+        <x:v>Garaulet_2022</x:v>
+      </x:c>
+      <x:c r="C326" t="str">
+        <x:v>Garaulet_2022_all</x:v>
+      </x:c>
+      <x:c r="D326" t="str">
+        <x:v>Garaulet_OGTT_GG</x:v>
+      </x:c>
+      <x:c r="E326"/>
+      <x:c r="F326"/>
+      <x:c r="G326" t="str">
+        <x:v>MTNR1B GG</x:v>
+      </x:c>
+      <x:c r="H326" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I326" t="str">
+        <x:v>insulin_auc</x:v>
+      </x:c>
+      <x:c r="J326" t="str">
+        <x:v>insulin AUC paired difference</x:v>
+      </x:c>
+      <x:c r="K326" t="str">
+        <x:v>incremental</x:v>
+      </x:c>
+      <x:c r="L326" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="M326"/>
+      <x:c r="N326" t="str">
+        <x:v>within_person_contrast</x:v>
+      </x:c>
+      <x:c r="O326" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="P326" t="n">
+        <x:v>-14.31</x:v>
+      </x:c>
+      <x:c r="Q326" t="str">
+        <x:v>SD (paired difference)</x:v>
+      </x:c>
+      <x:c r="R326" t="n">
+        <x:v>47.81</x:v>
+      </x:c>
+      <x:c r="S326"/>
+      <x:c r="T326"/>
+      <x:c r="U326"/>
+      <x:c r="V326" t="str">
+        <x:v>µU×h/mL</x:v>
+      </x:c>
+      <x:c r="W326" t="str">
+        <x:v>late minus early</x:v>
+      </x:c>
+      <x:c r="X326"/>
+      <x:c r="Y326" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z326" t="str">
+        <x:v>Garaulet_2022_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA326" t="str">
+        <x:v>Table P values compare genotypes, not the within-person timing effect; not assigned to this contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="327">
+      <x:c r="A327" t="str">
+        <x:v>O0350</x:v>
+      </x:c>
+      <x:c r="B327" t="str">
+        <x:v>Garaulet_2022</x:v>
+      </x:c>
+      <x:c r="C327" t="str">
+        <x:v>Garaulet_2022_all</x:v>
+      </x:c>
+      <x:c r="D327" t="str">
+        <x:v>Garaulet_OGTT_all</x:v>
+      </x:c>
+      <x:c r="E327"/>
+      <x:c r="F327"/>
+      <x:c r="G327" t="str">
+        <x:v>MTNR1B all</x:v>
+      </x:c>
+      <x:c r="H327" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I327" t="str">
+        <x:v>timed_glucose</x:v>
+      </x:c>
+      <x:c r="J327" t="str">
+        <x:v>Postprandial glucose paired difference</x:v>
+      </x:c>
+      <x:c r="K327"/>
+      <x:c r="L327"/>
+      <x:c r="M327" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N327" t="str">
+        <x:v>within_person_contrast</x:v>
+      </x:c>
+      <x:c r="O327" t="n">
+        <x:v>845</x:v>
+      </x:c>
+      <x:c r="P327" t="n">
+        <x:v>3.84</x:v>
+      </x:c>
+      <x:c r="Q327" t="str">
+        <x:v>SD (paired difference)</x:v>
+      </x:c>
+      <x:c r="R327" t="n">
+        <x:v>26.37</x:v>
+      </x:c>
+      <x:c r="S327"/>
+      <x:c r="T327"/>
+      <x:c r="U327"/>
+      <x:c r="V327" t="str">
+        <x:v>mg/dL</x:v>
+      </x:c>
+      <x:c r="W327" t="str">
+        <x:v>late minus early</x:v>
+      </x:c>
+      <x:c r="X327"/>
+      <x:c r="Y327" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z327" t="str">
+        <x:v>Garaulet_2022_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA327" t="str">
+        <x:v>Table P values compare genotypes, not the within-person timing effect; not assigned to this contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="328">
+      <x:c r="A328" t="str">
+        <x:v>O0351</x:v>
+      </x:c>
+      <x:c r="B328" t="str">
+        <x:v>Garaulet_2022</x:v>
+      </x:c>
+      <x:c r="C328" t="str">
+        <x:v>Garaulet_2022_all</x:v>
+      </x:c>
+      <x:c r="D328" t="str">
+        <x:v>Garaulet_OGTT_CC</x:v>
+      </x:c>
+      <x:c r="E328"/>
+      <x:c r="F328"/>
+      <x:c r="G328" t="str">
+        <x:v>MTNR1B CC</x:v>
+      </x:c>
+      <x:c r="H328" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I328" t="str">
+        <x:v>timed_glucose</x:v>
+      </x:c>
+      <x:c r="J328" t="str">
+        <x:v>Postprandial glucose paired difference</x:v>
+      </x:c>
+      <x:c r="K328"/>
+      <x:c r="L328"/>
+      <x:c r="M328" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N328" t="str">
+        <x:v>within_person_contrast</x:v>
+      </x:c>
+      <x:c r="O328" t="n">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="P328" t="n">
+        <x:v>1.64</x:v>
+      </x:c>
+      <x:c r="Q328" t="str">
+        <x:v>SD (paired difference)</x:v>
+      </x:c>
+      <x:c r="R328" t="n">
+        <x:v>25.24</x:v>
+      </x:c>
+      <x:c r="S328"/>
+      <x:c r="T328"/>
+      <x:c r="U328"/>
+      <x:c r="V328" t="str">
+        <x:v>mg/dL</x:v>
+      </x:c>
+      <x:c r="W328" t="str">
+        <x:v>late minus early</x:v>
+      </x:c>
+      <x:c r="X328"/>
+      <x:c r="Y328" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z328" t="str">
+        <x:v>Garaulet_2022_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA328" t="str">
+        <x:v>Table P values compare genotypes, not the within-person timing effect; not assigned to this contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="329">
+      <x:c r="A329" t="str">
+        <x:v>O0352</x:v>
+      </x:c>
+      <x:c r="B329" t="str">
+        <x:v>Garaulet_2022</x:v>
+      </x:c>
+      <x:c r="C329" t="str">
+        <x:v>Garaulet_2022_all</x:v>
+      </x:c>
+      <x:c r="D329" t="str">
+        <x:v>Garaulet_OGTT_CG</x:v>
+      </x:c>
+      <x:c r="E329"/>
+      <x:c r="F329"/>
+      <x:c r="G329" t="str">
+        <x:v>MTNR1B CG</x:v>
+      </x:c>
+      <x:c r="H329" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I329" t="str">
+        <x:v>timed_glucose</x:v>
+      </x:c>
+      <x:c r="J329" t="str">
+        <x:v>Postprandial glucose paired difference</x:v>
+      </x:c>
+      <x:c r="K329"/>
+      <x:c r="L329"/>
+      <x:c r="M329" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N329" t="str">
+        <x:v>within_person_contrast</x:v>
+      </x:c>
+      <x:c r="O329" t="n">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="P329" t="n">
+        <x:v>4.59</x:v>
+      </x:c>
+      <x:c r="Q329" t="str">
+        <x:v>SD (paired difference)</x:v>
+      </x:c>
+      <x:c r="R329" t="n">
+        <x:v>26.65</x:v>
+      </x:c>
+      <x:c r="S329"/>
+      <x:c r="T329"/>
+      <x:c r="U329"/>
+      <x:c r="V329" t="str">
+        <x:v>mg/dL</x:v>
+      </x:c>
+      <x:c r="W329" t="str">
+        <x:v>late minus early</x:v>
+      </x:c>
+      <x:c r="X329"/>
+      <x:c r="Y329" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z329" t="str">
+        <x:v>Garaulet_2022_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA329" t="str">
+        <x:v>Table P values compare genotypes, not the within-person timing effect; not assigned to this contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="330">
+      <x:c r="A330" t="str">
+        <x:v>O0353</x:v>
+      </x:c>
+      <x:c r="B330" t="str">
+        <x:v>Garaulet_2022</x:v>
+      </x:c>
+      <x:c r="C330" t="str">
+        <x:v>Garaulet_2022_all</x:v>
+      </x:c>
+      <x:c r="D330" t="str">
+        <x:v>Garaulet_OGTT_GG</x:v>
+      </x:c>
+      <x:c r="E330"/>
+      <x:c r="F330"/>
+      <x:c r="G330" t="str">
+        <x:v>MTNR1B GG</x:v>
+      </x:c>
+      <x:c r="H330" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I330" t="str">
+        <x:v>timed_glucose</x:v>
+      </x:c>
+      <x:c r="J330" t="str">
+        <x:v>Postprandial glucose paired difference</x:v>
+      </x:c>
+      <x:c r="K330"/>
+      <x:c r="L330"/>
+      <x:c r="M330" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N330" t="str">
+        <x:v>within_person_contrast</x:v>
+      </x:c>
+      <x:c r="O330" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="P330" t="n">
+        <x:v>12.24</x:v>
+      </x:c>
+      <x:c r="Q330" t="str">
+        <x:v>SD (paired difference)</x:v>
+      </x:c>
+      <x:c r="R330" t="n">
+        <x:v>29.35</x:v>
+      </x:c>
+      <x:c r="S330"/>
+      <x:c r="T330"/>
+      <x:c r="U330"/>
+      <x:c r="V330" t="str">
+        <x:v>mg/dL</x:v>
+      </x:c>
+      <x:c r="W330" t="str">
+        <x:v>late minus early</x:v>
+      </x:c>
+      <x:c r="X330"/>
+      <x:c r="Y330" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z330" t="str">
+        <x:v>Garaulet_2022_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA330" t="str">
+        <x:v>Table P values compare genotypes, not the within-person timing effect; not assigned to this contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="331">
+      <x:c r="A331" t="str">
+        <x:v>O0354</x:v>
+      </x:c>
+      <x:c r="B331" t="str">
+        <x:v>Garaulet_2022</x:v>
+      </x:c>
+      <x:c r="C331" t="str">
+        <x:v>Garaulet_2022_all</x:v>
+      </x:c>
+      <x:c r="D331" t="str">
+        <x:v>Garaulet_OGTT_all</x:v>
+      </x:c>
+      <x:c r="E331"/>
+      <x:c r="F331"/>
+      <x:c r="G331" t="str">
+        <x:v>MTNR1B all</x:v>
+      </x:c>
+      <x:c r="H331" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I331" t="str">
+        <x:v>timed_glucose</x:v>
+      </x:c>
+      <x:c r="J331" t="str">
+        <x:v>Postprandial glucose paired difference</x:v>
+      </x:c>
+      <x:c r="K331"/>
+      <x:c r="L331"/>
+      <x:c r="M331" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="N331" t="str">
+        <x:v>within_person_contrast</x:v>
+      </x:c>
+      <x:c r="O331" t="n">
+        <x:v>845</x:v>
+      </x:c>
+      <x:c r="P331" t="n">
+        <x:v>20.36</x:v>
+      </x:c>
+      <x:c r="Q331" t="str">
+        <x:v>SD (paired difference)</x:v>
+      </x:c>
+      <x:c r="R331" t="n">
+        <x:v>53.54</x:v>
+      </x:c>
+      <x:c r="S331"/>
+      <x:c r="T331"/>
+      <x:c r="U331"/>
+      <x:c r="V331" t="str">
+        <x:v>mg/dL</x:v>
+      </x:c>
+      <x:c r="W331" t="str">
+        <x:v>late minus early</x:v>
+      </x:c>
+      <x:c r="X331"/>
+      <x:c r="Y331" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z331" t="str">
+        <x:v>Garaulet_2022_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA331" t="str">
+        <x:v>Table P values compare genotypes, not the within-person timing effect; not assigned to this contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="332">
+      <x:c r="A332" t="str">
+        <x:v>O0355</x:v>
+      </x:c>
+      <x:c r="B332" t="str">
+        <x:v>Garaulet_2022</x:v>
+      </x:c>
+      <x:c r="C332" t="str">
+        <x:v>Garaulet_2022_all</x:v>
+      </x:c>
+      <x:c r="D332" t="str">
+        <x:v>Garaulet_OGTT_CC</x:v>
+      </x:c>
+      <x:c r="E332"/>
+      <x:c r="F332"/>
+      <x:c r="G332" t="str">
+        <x:v>MTNR1B CC</x:v>
+      </x:c>
+      <x:c r="H332" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I332" t="str">
+        <x:v>timed_glucose</x:v>
+      </x:c>
+      <x:c r="J332" t="str">
+        <x:v>Postprandial glucose paired difference</x:v>
+      </x:c>
+      <x:c r="K332"/>
+      <x:c r="L332"/>
+      <x:c r="M332" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="N332" t="str">
+        <x:v>within_person_contrast</x:v>
+      </x:c>
+      <x:c r="O332" t="n">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="P332" t="n">
+        <x:v>15.04</x:v>
+      </x:c>
+      <x:c r="Q332" t="str">
+        <x:v>SD (paired difference)</x:v>
+      </x:c>
+      <x:c r="R332" t="n">
+        <x:v>32.08</x:v>
+      </x:c>
+      <x:c r="S332"/>
+      <x:c r="T332"/>
+      <x:c r="U332"/>
+      <x:c r="V332" t="str">
+        <x:v>mg/dL</x:v>
+      </x:c>
+      <x:c r="W332" t="str">
+        <x:v>late minus early</x:v>
+      </x:c>
+      <x:c r="X332"/>
+      <x:c r="Y332" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z332" t="str">
+        <x:v>Garaulet_2022_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA332" t="str">
+        <x:v>Table P values compare genotypes, not the within-person timing effect; not assigned to this contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="333">
+      <x:c r="A333" t="str">
+        <x:v>O0356</x:v>
+      </x:c>
+      <x:c r="B333" t="str">
+        <x:v>Garaulet_2022</x:v>
+      </x:c>
+      <x:c r="C333" t="str">
+        <x:v>Garaulet_2022_all</x:v>
+      </x:c>
+      <x:c r="D333" t="str">
+        <x:v>Garaulet_OGTT_CG</x:v>
+      </x:c>
+      <x:c r="E333"/>
+      <x:c r="F333"/>
+      <x:c r="G333" t="str">
+        <x:v>MTNR1B CG</x:v>
+      </x:c>
+      <x:c r="H333" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I333" t="str">
+        <x:v>timed_glucose</x:v>
+      </x:c>
+      <x:c r="J333" t="str">
+        <x:v>Postprandial glucose paired difference</x:v>
+      </x:c>
+      <x:c r="K333"/>
+      <x:c r="L333"/>
+      <x:c r="M333" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="N333" t="str">
+        <x:v>within_person_contrast</x:v>
+      </x:c>
+      <x:c r="O333" t="n">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="P333" t="n">
+        <x:v>23.67</x:v>
+      </x:c>
+      <x:c r="Q333" t="str">
+        <x:v>SD (paired difference)</x:v>
+      </x:c>
+      <x:c r="R333" t="n">
+        <x:v>36.79</x:v>
+      </x:c>
+      <x:c r="S333"/>
+      <x:c r="T333"/>
+      <x:c r="U333"/>
+      <x:c r="V333" t="str">
+        <x:v>mg/dL</x:v>
+      </x:c>
+      <x:c r="W333" t="str">
+        <x:v>late minus early</x:v>
+      </x:c>
+      <x:c r="X333"/>
+      <x:c r="Y333" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z333" t="str">
+        <x:v>Garaulet_2022_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA333" t="str">
+        <x:v>Table P values compare genotypes, not the within-person timing effect; not assigned to this contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="334">
+      <x:c r="A334" t="str">
+        <x:v>O0357</x:v>
+      </x:c>
+      <x:c r="B334" t="str">
+        <x:v>Garaulet_2022</x:v>
+      </x:c>
+      <x:c r="C334" t="str">
+        <x:v>Garaulet_2022_all</x:v>
+      </x:c>
+      <x:c r="D334" t="str">
+        <x:v>Garaulet_OGTT_GG</x:v>
+      </x:c>
+      <x:c r="E334"/>
+      <x:c r="F334"/>
+      <x:c r="G334" t="str">
+        <x:v>MTNR1B GG</x:v>
+      </x:c>
+      <x:c r="H334" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I334" t="str">
+        <x:v>timed_glucose</x:v>
+      </x:c>
+      <x:c r="J334" t="str">
+        <x:v>Postprandial glucose paired difference</x:v>
+      </x:c>
+      <x:c r="K334"/>
+      <x:c r="L334"/>
+      <x:c r="M334" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="N334" t="str">
+        <x:v>within_person_contrast</x:v>
+      </x:c>
+      <x:c r="O334" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="P334" t="n">
+        <x:v>34.35</x:v>
+      </x:c>
+      <x:c r="Q334" t="str">
+        <x:v>SD (paired difference)</x:v>
+      </x:c>
+      <x:c r="R334" t="n">
+        <x:v>41.94</x:v>
+      </x:c>
+      <x:c r="S334"/>
+      <x:c r="T334"/>
+      <x:c r="U334"/>
+      <x:c r="V334" t="str">
+        <x:v>mg/dL</x:v>
+      </x:c>
+      <x:c r="W334" t="str">
+        <x:v>late minus early</x:v>
+      </x:c>
+      <x:c r="X334"/>
+      <x:c r="Y334" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z334" t="str">
+        <x:v>Garaulet_2022_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA334" t="str">
+        <x:v>Table P values compare genotypes, not the within-person timing effect; not assigned to this contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="335">
+      <x:c r="A335" t="str">
+        <x:v>O0358</x:v>
+      </x:c>
+      <x:c r="B335" t="str">
+        <x:v>Garaulet_2022</x:v>
+      </x:c>
+      <x:c r="C335" t="str">
+        <x:v>Garaulet_2022_all</x:v>
+      </x:c>
+      <x:c r="D335" t="str">
+        <x:v>Garaulet_OGTT_all</x:v>
+      </x:c>
+      <x:c r="E335"/>
+      <x:c r="F335"/>
+      <x:c r="G335" t="str">
+        <x:v>MTNR1B all</x:v>
+      </x:c>
+      <x:c r="H335" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I335" t="str">
+        <x:v>timed_insulin</x:v>
+      </x:c>
+      <x:c r="J335" t="str">
+        <x:v>Postprandial insulin paired difference</x:v>
+      </x:c>
+      <x:c r="K335"/>
+      <x:c r="L335"/>
+      <x:c r="M335" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N335" t="str">
+        <x:v>within_person_contrast</x:v>
+      </x:c>
+      <x:c r="O335" t="n">
+        <x:v>845</x:v>
+      </x:c>
+      <x:c r="P335" t="n">
+        <x:v>-4.73</x:v>
+      </x:c>
+      <x:c r="Q335" t="str">
+        <x:v>SD (paired difference)</x:v>
+      </x:c>
+      <x:c r="R335" t="n">
+        <x:v>28.78</x:v>
+      </x:c>
+      <x:c r="S335"/>
+      <x:c r="T335"/>
+      <x:c r="U335"/>
+      <x:c r="V335" t="str">
+        <x:v>µU/mL</x:v>
+      </x:c>
+      <x:c r="W335" t="str">
+        <x:v>late minus early</x:v>
+      </x:c>
+      <x:c r="X335"/>
+      <x:c r="Y335" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z335" t="str">
+        <x:v>Garaulet_2022_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA335" t="str">
+        <x:v>Table P values compare genotypes, not the within-person timing effect; not assigned to this contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="336">
+      <x:c r="A336" t="str">
+        <x:v>O0359</x:v>
+      </x:c>
+      <x:c r="B336" t="str">
+        <x:v>Garaulet_2022</x:v>
+      </x:c>
+      <x:c r="C336" t="str">
+        <x:v>Garaulet_2022_all</x:v>
+      </x:c>
+      <x:c r="D336" t="str">
+        <x:v>Garaulet_OGTT_CC</x:v>
+      </x:c>
+      <x:c r="E336"/>
+      <x:c r="F336"/>
+      <x:c r="G336" t="str">
+        <x:v>MTNR1B CC</x:v>
+      </x:c>
+      <x:c r="H336" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I336" t="str">
+        <x:v>timed_insulin</x:v>
+      </x:c>
+      <x:c r="J336" t="str">
+        <x:v>Postprandial insulin paired difference</x:v>
+      </x:c>
+      <x:c r="K336"/>
+      <x:c r="L336"/>
+      <x:c r="M336" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N336" t="str">
+        <x:v>within_person_contrast</x:v>
+      </x:c>
+      <x:c r="O336" t="n">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="P336" t="n">
+        <x:v>-2.96</x:v>
+      </x:c>
+      <x:c r="Q336" t="str">
+        <x:v>SD (paired difference)</x:v>
+      </x:c>
+      <x:c r="R336" t="n">
+        <x:v>29.64</x:v>
+      </x:c>
+      <x:c r="S336"/>
+      <x:c r="T336"/>
+      <x:c r="U336"/>
+      <x:c r="V336" t="str">
+        <x:v>µU/mL</x:v>
+      </x:c>
+      <x:c r="W336" t="str">
+        <x:v>late minus early</x:v>
+      </x:c>
+      <x:c r="X336"/>
+      <x:c r="Y336" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z336" t="str">
+        <x:v>Garaulet_2022_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA336" t="str">
+        <x:v>Table P values compare genotypes, not the within-person timing effect; not assigned to this contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="337">
+      <x:c r="A337" t="str">
+        <x:v>O0360</x:v>
+      </x:c>
+      <x:c r="B337" t="str">
+        <x:v>Garaulet_2022</x:v>
+      </x:c>
+      <x:c r="C337" t="str">
+        <x:v>Garaulet_2022_all</x:v>
+      </x:c>
+      <x:c r="D337" t="str">
+        <x:v>Garaulet_OGTT_CG</x:v>
+      </x:c>
+      <x:c r="E337"/>
+      <x:c r="F337"/>
+      <x:c r="G337" t="str">
+        <x:v>MTNR1B CG</x:v>
+      </x:c>
+      <x:c r="H337" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I337" t="str">
+        <x:v>timed_insulin</x:v>
+      </x:c>
+      <x:c r="J337" t="str">
+        <x:v>Postprandial insulin paired difference</x:v>
+      </x:c>
+      <x:c r="K337"/>
+      <x:c r="L337"/>
+      <x:c r="M337" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N337" t="str">
+        <x:v>within_person_contrast</x:v>
+      </x:c>
+      <x:c r="O337" t="n">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="P337" t="n">
+        <x:v>-7.1</x:v>
+      </x:c>
+      <x:c r="Q337" t="str">
+        <x:v>SD (paired difference)</x:v>
+      </x:c>
+      <x:c r="R337" t="n">
+        <x:v>28.23</x:v>
+      </x:c>
+      <x:c r="S337"/>
+      <x:c r="T337"/>
+      <x:c r="U337"/>
+      <x:c r="V337" t="str">
+        <x:v>µU/mL</x:v>
+      </x:c>
+      <x:c r="W337" t="str">
+        <x:v>late minus early</x:v>
+      </x:c>
+      <x:c r="X337"/>
+      <x:c r="Y337" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z337" t="str">
+        <x:v>Garaulet_2022_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA337" t="str">
+        <x:v>Table P values compare genotypes, not the within-person timing effect; not assigned to this contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="338">
+      <x:c r="A338" t="str">
+        <x:v>O0361</x:v>
+      </x:c>
+      <x:c r="B338" t="str">
+        <x:v>Garaulet_2022</x:v>
+      </x:c>
+      <x:c r="C338" t="str">
+        <x:v>Garaulet_2022_all</x:v>
+      </x:c>
+      <x:c r="D338" t="str">
+        <x:v>Garaulet_OGTT_GG</x:v>
+      </x:c>
+      <x:c r="E338"/>
+      <x:c r="F338"/>
+      <x:c r="G338" t="str">
+        <x:v>MTNR1B GG</x:v>
+      </x:c>
+      <x:c r="H338" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I338" t="str">
+        <x:v>timed_insulin</x:v>
+      </x:c>
+      <x:c r="J338" t="str">
+        <x:v>Postprandial insulin paired difference</x:v>
+      </x:c>
+      <x:c r="K338"/>
+      <x:c r="L338"/>
+      <x:c r="M338" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N338" t="str">
+        <x:v>within_person_contrast</x:v>
+      </x:c>
+      <x:c r="O338" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="P338" t="n">
+        <x:v>-3.98</x:v>
+      </x:c>
+      <x:c r="Q338" t="str">
+        <x:v>SD (paired difference)</x:v>
+      </x:c>
+      <x:c r="R338" t="n">
+        <x:v>26.94</x:v>
+      </x:c>
+      <x:c r="S338"/>
+      <x:c r="T338"/>
+      <x:c r="U338"/>
+      <x:c r="V338" t="str">
+        <x:v>µU/mL</x:v>
+      </x:c>
+      <x:c r="W338" t="str">
+        <x:v>late minus early</x:v>
+      </x:c>
+      <x:c r="X338"/>
+      <x:c r="Y338" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z338" t="str">
+        <x:v>Garaulet_2022_primary; PDF p6; Table 2</x:v>
+      </x:c>
+      <x:c r="AA338" t="str">
+        <x:v>Table P values compare genotypes, not the within-person timing effect; not assigned to this contrast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="339">
+      <x:c r="A339" t="str">
+        <x:v>O0362</x:v>
+      </x:c>
+      <x:c r="B339" t="str">
+        <x:v>Lu_2022</x:v>
+      </x:c>
+      <x:c r="C339" t="str">
+        <x:v>Lu_2022_all</x:v>
+      </x:c>
+      <x:c r="D339" t="str">
+        <x:v>Lu_supportive</x:v>
+      </x:c>
+      <x:c r="E339" t="str">
+        <x:v>Lu_12S</x:v>
+      </x:c>
+      <x:c r="F339" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G339" t="str">
+        <x:v>no preload</x:v>
+      </x:c>
+      <x:c r="H339" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I339" t="str">
+        <x:v>glucose_auc</x:v>
+      </x:c>
+      <x:c r="J339" t="str">
+        <x:v>Capillary glucose iAUC</x:v>
+      </x:c>
+      <x:c r="K339"/>
+      <x:c r="L339" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="M339"/>
+      <x:c r="N339" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O339" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P339" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="Q339" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R339" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="S339"/>
+      <x:c r="T339"/>
+      <x:c r="U339" t="str">
+        <x:v>&lt;0.05</x:v>
+      </x:c>
+      <x:c r="V339" t="str">
+        <x:v>mmol/L×min</x:v>
+      </x:c>
+      <x:c r="W339"/>
+      <x:c r="X339"/>
+      <x:c r="Y339" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z339" t="str">
+        <x:v>Lu_2022_primary; PDF p8; Figure 3B</x:v>
+      </x:c>
+      <x:c r="AA339" t="str">
+        <x:v>Approximate bar/SEM digitization, rounded to graph resolution. Figure AUC labels 0–120 min conflict with −30 to +90 min meal-relative sampling; peak-time origin retained as plotted. No paired precision inferred.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="340">
+      <x:c r="A340" t="str">
+        <x:v>O0363</x:v>
+      </x:c>
+      <x:c r="B340" t="str">
+        <x:v>Lu_2022</x:v>
+      </x:c>
+      <x:c r="C340" t="str">
+        <x:v>Lu_2022_all</x:v>
+      </x:c>
+      <x:c r="D340" t="str">
+        <x:v>Lu_supportive</x:v>
+      </x:c>
+      <x:c r="E340" t="str">
+        <x:v>Lu_14S</x:v>
+      </x:c>
+      <x:c r="F340" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G340" t="str">
+        <x:v>no preload</x:v>
+      </x:c>
+      <x:c r="H340" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I340" t="str">
+        <x:v>glucose_auc</x:v>
+      </x:c>
+      <x:c r="J340" t="str">
+        <x:v>Capillary glucose iAUC</x:v>
+      </x:c>
+      <x:c r="K340"/>
+      <x:c r="L340" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="M340"/>
+      <x:c r="N340" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O340" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P340" t="n">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="Q340" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R340" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="S340"/>
+      <x:c r="T340"/>
+      <x:c r="U340" t="str">
+        <x:v>&lt;0.05</x:v>
+      </x:c>
+      <x:c r="V340" t="str">
+        <x:v>mmol/L×min</x:v>
+      </x:c>
+      <x:c r="W340"/>
+      <x:c r="X340"/>
+      <x:c r="Y340" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z340" t="str">
+        <x:v>Lu_2022_primary; PDF p8; Figure 3B</x:v>
+      </x:c>
+      <x:c r="AA340" t="str">
+        <x:v>Approximate bar/SEM digitization, rounded to graph resolution. Figure AUC labels 0–120 min conflict with −30 to +90 min meal-relative sampling; peak-time origin retained as plotted. No paired precision inferred.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="341">
+      <x:c r="A341" t="str">
+        <x:v>O0364</x:v>
+      </x:c>
+      <x:c r="B341" t="str">
+        <x:v>Lu_2022</x:v>
+      </x:c>
+      <x:c r="C341" t="str">
+        <x:v>Lu_2022_all</x:v>
+      </x:c>
+      <x:c r="D341" t="str">
+        <x:v>Lu_supportive</x:v>
+      </x:c>
+      <x:c r="E341" t="str">
+        <x:v>Lu_12S</x:v>
+      </x:c>
+      <x:c r="F341" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G341" t="str">
+        <x:v>no preload</x:v>
+      </x:c>
+      <x:c r="H341" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I341" t="str">
+        <x:v>peak_glucose</x:v>
+      </x:c>
+      <x:c r="J341" t="str">
+        <x:v>Capillary incremental glucose peak</x:v>
+      </x:c>
+      <x:c r="K341"/>
+      <x:c r="L341" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="M341"/>
+      <x:c r="N341" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O341" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P341" t="n">
+        <x:v>3.9</x:v>
+      </x:c>
+      <x:c r="Q341" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R341" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="S341"/>
+      <x:c r="T341"/>
+      <x:c r="U341" t="str">
+        <x:v>&lt;0.05</x:v>
+      </x:c>
+      <x:c r="V341" t="str">
+        <x:v>mmol/L</x:v>
+      </x:c>
+      <x:c r="W341"/>
+      <x:c r="X341"/>
+      <x:c r="Y341" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z341" t="str">
+        <x:v>Lu_2022_primary; PDF p8; Figure 3C</x:v>
+      </x:c>
+      <x:c r="AA341" t="str">
+        <x:v>Approximate bar/SEM digitization, rounded to graph resolution. Figure AUC labels 0–120 min conflict with −30 to +90 min meal-relative sampling; peak-time origin retained as plotted. No paired precision inferred.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="342">
+      <x:c r="A342" t="str">
+        <x:v>O0365</x:v>
+      </x:c>
+      <x:c r="B342" t="str">
+        <x:v>Lu_2022</x:v>
+      </x:c>
+      <x:c r="C342" t="str">
+        <x:v>Lu_2022_all</x:v>
+      </x:c>
+      <x:c r="D342" t="str">
+        <x:v>Lu_supportive</x:v>
+      </x:c>
+      <x:c r="E342" t="str">
+        <x:v>Lu_14S</x:v>
+      </x:c>
+      <x:c r="F342" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G342" t="str">
+        <x:v>no preload</x:v>
+      </x:c>
+      <x:c r="H342" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I342" t="str">
+        <x:v>peak_glucose</x:v>
+      </x:c>
+      <x:c r="J342" t="str">
+        <x:v>Capillary incremental glucose peak</x:v>
+      </x:c>
+      <x:c r="K342"/>
+      <x:c r="L342" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="M342"/>
+      <x:c r="N342" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O342" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P342" t="n">
+        <x:v>4.9</x:v>
+      </x:c>
+      <x:c r="Q342" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R342" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="S342"/>
+      <x:c r="T342"/>
+      <x:c r="U342" t="str">
+        <x:v>&lt;0.05</x:v>
+      </x:c>
+      <x:c r="V342" t="str">
+        <x:v>mmol/L</x:v>
+      </x:c>
+      <x:c r="W342"/>
+      <x:c r="X342"/>
+      <x:c r="Y342" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z342" t="str">
+        <x:v>Lu_2022_primary; PDF p8; Figure 3C</x:v>
+      </x:c>
+      <x:c r="AA342" t="str">
+        <x:v>Approximate bar/SEM digitization, rounded to graph resolution. Figure AUC labels 0–120 min conflict with −30 to +90 min meal-relative sampling; peak-time origin retained as plotted. No paired precision inferred.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="343">
+      <x:c r="A343" t="str">
+        <x:v>O0366</x:v>
+      </x:c>
+      <x:c r="B343" t="str">
+        <x:v>Lu_2022</x:v>
+      </x:c>
+      <x:c r="C343" t="str">
+        <x:v>Lu_2022_all</x:v>
+      </x:c>
+      <x:c r="D343" t="str">
+        <x:v>Lu_supportive</x:v>
+      </x:c>
+      <x:c r="E343" t="str">
+        <x:v>Lu_12S</x:v>
+      </x:c>
+      <x:c r="F343" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G343" t="str">
+        <x:v>no preload</x:v>
+      </x:c>
+      <x:c r="H343" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I343" t="str">
+        <x:v>insulin_auc</x:v>
+      </x:c>
+      <x:c r="J343" t="str">
+        <x:v>Insulin percent-change iAUC</x:v>
+      </x:c>
+      <x:c r="K343"/>
+      <x:c r="L343" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="M343"/>
+      <x:c r="N343" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O343" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P343" t="n">
+        <x:v>60000</x:v>
+      </x:c>
+      <x:c r="Q343" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R343" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="S343"/>
+      <x:c r="T343"/>
+      <x:c r="U343" t="str">
+        <x:v>&lt;0.05</x:v>
+      </x:c>
+      <x:c r="V343" t="str">
+        <x:v>%×min</x:v>
+      </x:c>
+      <x:c r="W343"/>
+      <x:c r="X343"/>
+      <x:c r="Y343" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z343" t="str">
+        <x:v>Lu_2022_primary; PDF p8; Figure 3E</x:v>
+      </x:c>
+      <x:c r="AA343" t="str">
+        <x:v>Approximate bar/SEM digitization, rounded to graph resolution. Figure AUC labels 0–120 min conflict with −30 to +90 min meal-relative sampling; peak-time origin retained as plotted. No paired precision inferred.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="344">
+      <x:c r="A344" t="str">
+        <x:v>O0367</x:v>
+      </x:c>
+      <x:c r="B344" t="str">
+        <x:v>Lu_2022</x:v>
+      </x:c>
+      <x:c r="C344" t="str">
+        <x:v>Lu_2022_all</x:v>
+      </x:c>
+      <x:c r="D344" t="str">
+        <x:v>Lu_supportive</x:v>
+      </x:c>
+      <x:c r="E344" t="str">
+        <x:v>Lu_14S</x:v>
+      </x:c>
+      <x:c r="F344" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G344" t="str">
+        <x:v>no preload</x:v>
+      </x:c>
+      <x:c r="H344" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I344" t="str">
+        <x:v>insulin_auc</x:v>
+      </x:c>
+      <x:c r="J344" t="str">
+        <x:v>Insulin percent-change iAUC</x:v>
+      </x:c>
+      <x:c r="K344"/>
+      <x:c r="L344" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="M344"/>
+      <x:c r="N344" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O344" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P344" t="n">
+        <x:v>130000</x:v>
+      </x:c>
+      <x:c r="Q344" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R344" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="S344"/>
+      <x:c r="T344"/>
+      <x:c r="U344" t="str">
+        <x:v>&lt;0.05</x:v>
+      </x:c>
+      <x:c r="V344" t="str">
+        <x:v>%×min</x:v>
+      </x:c>
+      <x:c r="W344"/>
+      <x:c r="X344"/>
+      <x:c r="Y344" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z344" t="str">
+        <x:v>Lu_2022_primary; PDF p8; Figure 3E</x:v>
+      </x:c>
+      <x:c r="AA344" t="str">
+        <x:v>Approximate bar/SEM digitization, rounded to graph resolution. Figure AUC labels 0–120 min conflict with −30 to +90 min meal-relative sampling; peak-time origin retained as plotted. No paired precision inferred.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="345">
+      <x:c r="A345" t="str">
+        <x:v>O0368</x:v>
+      </x:c>
+      <x:c r="B345" t="str">
+        <x:v>Lu_2022</x:v>
+      </x:c>
+      <x:c r="C345" t="str">
+        <x:v>Lu_2022_all</x:v>
+      </x:c>
+      <x:c r="D345" t="str">
+        <x:v>Lu_supportive</x:v>
+      </x:c>
+      <x:c r="E345" t="str">
+        <x:v>Lu_12S</x:v>
+      </x:c>
+      <x:c r="F345" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G345" t="str">
+        <x:v>no preload</x:v>
+      </x:c>
+      <x:c r="H345" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I345" t="str">
+        <x:v>peak_insulin</x:v>
+      </x:c>
+      <x:c r="J345" t="str">
+        <x:v>Insulin percent-change peak</x:v>
+      </x:c>
+      <x:c r="K345"/>
+      <x:c r="L345" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="M345"/>
+      <x:c r="N345" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O345" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P345" t="n">
+        <x:v>1300</x:v>
+      </x:c>
+      <x:c r="Q345" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R345" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="S345"/>
+      <x:c r="T345"/>
+      <x:c r="U345" t="str">
+        <x:v>&lt;0.05</x:v>
+      </x:c>
+      <x:c r="V345" t="str">
+        <x:v>%</x:v>
+      </x:c>
+      <x:c r="W345"/>
+      <x:c r="X345"/>
+      <x:c r="Y345" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z345" t="str">
+        <x:v>Lu_2022_primary; PDF p8; Figure 3F</x:v>
+      </x:c>
+      <x:c r="AA345" t="str">
+        <x:v>Approximate bar/SEM digitization, rounded to graph resolution. Figure AUC labels 0–120 min conflict with −30 to +90 min meal-relative sampling; peak-time origin retained as plotted. No paired precision inferred.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="346">
+      <x:c r="A346" t="str">
+        <x:v>O0369</x:v>
+      </x:c>
+      <x:c r="B346" t="str">
+        <x:v>Lu_2022</x:v>
+      </x:c>
+      <x:c r="C346" t="str">
+        <x:v>Lu_2022_all</x:v>
+      </x:c>
+      <x:c r="D346" t="str">
+        <x:v>Lu_supportive</x:v>
+      </x:c>
+      <x:c r="E346" t="str">
+        <x:v>Lu_14S</x:v>
+      </x:c>
+      <x:c r="F346" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G346" t="str">
+        <x:v>no preload</x:v>
+      </x:c>
+      <x:c r="H346" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I346" t="str">
+        <x:v>peak_insulin</x:v>
+      </x:c>
+      <x:c r="J346" t="str">
+        <x:v>Insulin percent-change peak</x:v>
+      </x:c>
+      <x:c r="K346"/>
+      <x:c r="L346" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="M346"/>
+      <x:c r="N346" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O346" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P346" t="n">
+        <x:v>2200</x:v>
+      </x:c>
+      <x:c r="Q346" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R346" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="S346"/>
+      <x:c r="T346"/>
+      <x:c r="U346" t="str">
+        <x:v>&lt;0.05</x:v>
+      </x:c>
+      <x:c r="V346" t="str">
+        <x:v>%</x:v>
+      </x:c>
+      <x:c r="W346"/>
+      <x:c r="X346"/>
+      <x:c r="Y346" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z346" t="str">
+        <x:v>Lu_2022_primary; PDF p8; Figure 3F</x:v>
+      </x:c>
+      <x:c r="AA346" t="str">
+        <x:v>Approximate bar/SEM digitization, rounded to graph resolution. Figure AUC labels 0–120 min conflict with −30 to +90 min meal-relative sampling; peak-time origin retained as plotted. No paired precision inferred.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="347">
+      <x:c r="A347" t="str">
+        <x:v>O0370</x:v>
+      </x:c>
+      <x:c r="B347" t="str">
+        <x:v>Lu_2022</x:v>
+      </x:c>
+      <x:c r="C347" t="str">
+        <x:v>Lu_2022_all</x:v>
+      </x:c>
+      <x:c r="D347" t="str">
+        <x:v>Lu_supportive</x:v>
+      </x:c>
+      <x:c r="E347" t="str">
+        <x:v>Lu_12S</x:v>
+      </x:c>
+      <x:c r="F347" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G347" t="str">
+        <x:v>no preload</x:v>
+      </x:c>
+      <x:c r="H347" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I347" t="str">
+        <x:v>peak_time</x:v>
+      </x:c>
+      <x:c r="J347" t="str">
+        <x:v>Glucose peak time</x:v>
+      </x:c>
+      <x:c r="K347"/>
+      <x:c r="L347"/>
+      <x:c r="M347"/>
+      <x:c r="N347" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O347" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P347" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="Q347" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R347" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="S347"/>
+      <x:c r="T347"/>
+      <x:c r="U347" t="str">
+        <x:v>NS</x:v>
+      </x:c>
+      <x:c r="V347" t="str">
+        <x:v>min</x:v>
+      </x:c>
+      <x:c r="W347"/>
+      <x:c r="X347"/>
+      <x:c r="Y347" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z347" t="str">
+        <x:v>Lu_2022_primary; PDF p8; Figure 4A</x:v>
+      </x:c>
+      <x:c r="AA347" t="str">
+        <x:v>Approximate bar/SEM digitization, rounded to graph resolution. Figure AUC labels 0–120 min conflict with −30 to +90 min meal-relative sampling; peak-time origin retained as plotted. No paired precision inferred.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="348">
+      <x:c r="A348" t="str">
+        <x:v>O0371</x:v>
+      </x:c>
+      <x:c r="B348" t="str">
+        <x:v>Lu_2022</x:v>
+      </x:c>
+      <x:c r="C348" t="str">
+        <x:v>Lu_2022_all</x:v>
+      </x:c>
+      <x:c r="D348" t="str">
+        <x:v>Lu_supportive</x:v>
+      </x:c>
+      <x:c r="E348" t="str">
+        <x:v>Lu_14S</x:v>
+      </x:c>
+      <x:c r="F348" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G348" t="str">
+        <x:v>no preload</x:v>
+      </x:c>
+      <x:c r="H348" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I348" t="str">
+        <x:v>peak_time</x:v>
+      </x:c>
+      <x:c r="J348" t="str">
+        <x:v>Glucose peak time</x:v>
+      </x:c>
+      <x:c r="K348"/>
+      <x:c r="L348"/>
+      <x:c r="M348"/>
+      <x:c r="N348" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O348" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P348" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="Q348" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R348" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="S348"/>
+      <x:c r="T348"/>
+      <x:c r="U348" t="str">
+        <x:v>NS</x:v>
+      </x:c>
+      <x:c r="V348" t="str">
+        <x:v>min</x:v>
+      </x:c>
+      <x:c r="W348"/>
+      <x:c r="X348"/>
+      <x:c r="Y348" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z348" t="str">
+        <x:v>Lu_2022_primary; PDF p8; Figure 4A</x:v>
+      </x:c>
+      <x:c r="AA348" t="str">
+        <x:v>Approximate bar/SEM digitization, rounded to graph resolution. Figure AUC labels 0–120 min conflict with −30 to +90 min meal-relative sampling; peak-time origin retained as plotted. No paired precision inferred.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="349">
+      <x:c r="A349" t="str">
+        <x:v>O0372</x:v>
+      </x:c>
+      <x:c r="B349" t="str">
+        <x:v>Lu_2022</x:v>
+      </x:c>
+      <x:c r="C349" t="str">
+        <x:v>Lu_2022_all</x:v>
+      </x:c>
+      <x:c r="D349" t="str">
+        <x:v>Lu_supportive</x:v>
+      </x:c>
+      <x:c r="E349" t="str">
+        <x:v>Lu_12S</x:v>
+      </x:c>
+      <x:c r="F349" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G349" t="str">
+        <x:v>no preload</x:v>
+      </x:c>
+      <x:c r="H349" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I349" t="str">
+        <x:v>peak_time</x:v>
+      </x:c>
+      <x:c r="J349" t="str">
+        <x:v>Insulin peak time</x:v>
+      </x:c>
+      <x:c r="K349"/>
+      <x:c r="L349"/>
+      <x:c r="M349"/>
+      <x:c r="N349" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O349" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P349" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="Q349" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R349" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="S349"/>
+      <x:c r="T349"/>
+      <x:c r="U349" t="str">
+        <x:v>&lt;0.05</x:v>
+      </x:c>
+      <x:c r="V349" t="str">
+        <x:v>min</x:v>
+      </x:c>
+      <x:c r="W349"/>
+      <x:c r="X349"/>
+      <x:c r="Y349" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z349" t="str">
+        <x:v>Lu_2022_primary; PDF p8; Figure 4B</x:v>
+      </x:c>
+      <x:c r="AA349" t="str">
+        <x:v>Approximate bar/SEM digitization, rounded to graph resolution. Figure AUC labels 0–120 min conflict with −30 to +90 min meal-relative sampling; peak-time origin retained as plotted. No paired precision inferred.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="350">
+      <x:c r="A350" t="str">
+        <x:v>O0373</x:v>
+      </x:c>
+      <x:c r="B350" t="str">
+        <x:v>Lu_2022</x:v>
+      </x:c>
+      <x:c r="C350" t="str">
+        <x:v>Lu_2022_all</x:v>
+      </x:c>
+      <x:c r="D350" t="str">
+        <x:v>Lu_supportive</x:v>
+      </x:c>
+      <x:c r="E350" t="str">
+        <x:v>Lu_14S</x:v>
+      </x:c>
+      <x:c r="F350" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G350" t="str">
+        <x:v>no preload</x:v>
+      </x:c>
+      <x:c r="H350" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I350" t="str">
+        <x:v>peak_time</x:v>
+      </x:c>
+      <x:c r="J350" t="str">
+        <x:v>Insulin peak time</x:v>
+      </x:c>
+      <x:c r="K350"/>
+      <x:c r="L350"/>
+      <x:c r="M350"/>
+      <x:c r="N350" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O350" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P350" t="n">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="Q350" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R350" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="S350"/>
+      <x:c r="T350"/>
+      <x:c r="U350" t="str">
+        <x:v>&lt;0.05</x:v>
+      </x:c>
+      <x:c r="V350" t="str">
+        <x:v>min</x:v>
+      </x:c>
+      <x:c r="W350"/>
+      <x:c r="X350"/>
+      <x:c r="Y350" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z350" t="str">
+        <x:v>Lu_2022_primary; PDF p8; Figure 4B</x:v>
+      </x:c>
+      <x:c r="AA350" t="str">
+        <x:v>Approximate bar/SEM digitization, rounded to graph resolution. Figure AUC labels 0–120 min conflict with −30 to +90 min meal-relative sampling; peak-time origin retained as plotted. No paired precision inferred.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="351">
+      <x:c r="A351" t="str">
+        <x:v>O0374</x:v>
+      </x:c>
+      <x:c r="B351" t="str">
+        <x:v>Lu_2022</x:v>
+      </x:c>
+      <x:c r="C351" t="str">
+        <x:v>Lu_2022_all</x:v>
+      </x:c>
+      <x:c r="D351" t="str">
+        <x:v>Lu_supportive</x:v>
+      </x:c>
+      <x:c r="E351" t="str">
+        <x:v>Lu_12S</x:v>
+      </x:c>
+      <x:c r="F351" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G351" t="str">
+        <x:v>no preload</x:v>
+      </x:c>
+      <x:c r="H351" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I351" t="str">
+        <x:v>insulin_sensitivity</x:v>
+      </x:c>
+      <x:c r="J351" t="str">
+        <x:v>Insulin sensitivity index</x:v>
+      </x:c>
+      <x:c r="K351"/>
+      <x:c r="L351"/>
+      <x:c r="M351"/>
+      <x:c r="N351" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O351" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P351" t="n">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="Q351" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R351" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="S351"/>
+      <x:c r="T351"/>
+      <x:c r="U351" t="str">
+        <x:v>&lt;0.05</x:v>
+      </x:c>
+      <x:c r="V351" t="str">
+        <x:v>index</x:v>
+      </x:c>
+      <x:c r="W351"/>
+      <x:c r="X351"/>
+      <x:c r="Y351" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z351" t="str">
+        <x:v>Lu_2022_primary; PDF p8; Figure 4C</x:v>
+      </x:c>
+      <x:c r="AA351" t="str">
+        <x:v>Approximate bar/SEM digitization, rounded to graph resolution. Figure AUC labels 0–120 min conflict with −30 to +90 min meal-relative sampling; peak-time origin retained as plotted. No paired precision inferred.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="352">
+      <x:c r="A352" t="str">
+        <x:v>O0375</x:v>
+      </x:c>
+      <x:c r="B352" t="str">
+        <x:v>Lu_2022</x:v>
+      </x:c>
+      <x:c r="C352" t="str">
+        <x:v>Lu_2022_all</x:v>
+      </x:c>
+      <x:c r="D352" t="str">
+        <x:v>Lu_supportive</x:v>
+      </x:c>
+      <x:c r="E352" t="str">
+        <x:v>Lu_14S</x:v>
+      </x:c>
+      <x:c r="F352" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G352" t="str">
+        <x:v>no preload</x:v>
+      </x:c>
+      <x:c r="H352" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I352" t="str">
+        <x:v>insulin_sensitivity</x:v>
+      </x:c>
+      <x:c r="J352" t="str">
+        <x:v>Insulin sensitivity index</x:v>
+      </x:c>
+      <x:c r="K352"/>
+      <x:c r="L352"/>
+      <x:c r="M352"/>
+      <x:c r="N352" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O352" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P352" t="n">
+        <x:v>5.2</x:v>
+      </x:c>
+      <x:c r="Q352" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R352" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="S352"/>
+      <x:c r="T352"/>
+      <x:c r="U352" t="str">
+        <x:v>&lt;0.05</x:v>
+      </x:c>
+      <x:c r="V352" t="str">
+        <x:v>index</x:v>
+      </x:c>
+      <x:c r="W352"/>
+      <x:c r="X352"/>
+      <x:c r="Y352" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z352" t="str">
+        <x:v>Lu_2022_primary; PDF p8; Figure 4C</x:v>
+      </x:c>
+      <x:c r="AA352" t="str">
+        <x:v>Approximate bar/SEM digitization, rounded to graph resolution. Figure AUC labels 0–120 min conflict with −30 to +90 min meal-relative sampling; peak-time origin retained as plotted. No paired precision inferred.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="353">
+      <x:c r="A353" t="str">
+        <x:v>O0376</x:v>
+      </x:c>
+      <x:c r="B353" t="str">
+        <x:v>Lu_2022</x:v>
+      </x:c>
+      <x:c r="C353" t="str">
+        <x:v>Lu_2022_all</x:v>
+      </x:c>
+      <x:c r="D353" t="str">
+        <x:v>Lu_supportive</x:v>
+      </x:c>
+      <x:c r="E353" t="str">
+        <x:v>Lu_12S</x:v>
+      </x:c>
+      <x:c r="F353" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G353" t="str">
+        <x:v>no preload</x:v>
+      </x:c>
+      <x:c r="H353" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I353" t="str">
+        <x:v>insulin_sensitivity</x:v>
+      </x:c>
+      <x:c r="J353" t="str">
+        <x:v>HOMA-PP</x:v>
+      </x:c>
+      <x:c r="K353"/>
+      <x:c r="L353"/>
+      <x:c r="M353"/>
+      <x:c r="N353" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O353" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P353" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="Q353" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R353" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="S353"/>
+      <x:c r="T353"/>
+      <x:c r="U353" t="str">
+        <x:v>&lt;0.05</x:v>
+      </x:c>
+      <x:c r="V353" t="str">
+        <x:v>index</x:v>
+      </x:c>
+      <x:c r="W353"/>
+      <x:c r="X353"/>
+      <x:c r="Y353" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z353" t="str">
+        <x:v>Lu_2022_primary; PDF p8; Figure 4D</x:v>
+      </x:c>
+      <x:c r="AA353" t="str">
+        <x:v>Approximate bar/SEM digitization, rounded to graph resolution. Figure AUC labels 0–120 min conflict with −30 to +90 min meal-relative sampling; peak-time origin retained as plotted. No paired precision inferred.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="354">
+      <x:c r="A354" t="str">
+        <x:v>O0377</x:v>
+      </x:c>
+      <x:c r="B354" t="str">
+        <x:v>Lu_2022</x:v>
+      </x:c>
+      <x:c r="C354" t="str">
+        <x:v>Lu_2022_all</x:v>
+      </x:c>
+      <x:c r="D354" t="str">
+        <x:v>Lu_supportive</x:v>
+      </x:c>
+      <x:c r="E354" t="str">
+        <x:v>Lu_14S</x:v>
+      </x:c>
+      <x:c r="F354" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G354" t="str">
+        <x:v>no preload</x:v>
+      </x:c>
+      <x:c r="H354" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I354" t="str">
+        <x:v>insulin_sensitivity</x:v>
+      </x:c>
+      <x:c r="J354" t="str">
+        <x:v>HOMA-PP</x:v>
+      </x:c>
+      <x:c r="K354"/>
+      <x:c r="L354"/>
+      <x:c r="M354"/>
+      <x:c r="N354" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O354" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P354" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="Q354" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R354" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="S354"/>
+      <x:c r="T354"/>
+      <x:c r="U354" t="str">
+        <x:v>&lt;0.05</x:v>
+      </x:c>
+      <x:c r="V354" t="str">
+        <x:v>index</x:v>
+      </x:c>
+      <x:c r="W354"/>
+      <x:c r="X354"/>
+      <x:c r="Y354" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="Z354" t="str">
+        <x:v>Lu_2022_primary; PDF p8; Figure 4D</x:v>
+      </x:c>
+      <x:c r="AA354" t="str">
+        <x:v>Approximate bar/SEM digitization, rounded to graph resolution. Figure AUC labels 0–120 min conflict with −30 to +90 min meal-relative sampling; peak-time origin retained as plotted. No paired precision inferred.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="355">
+      <x:c r="A355" t="str">
+        <x:v>O0378</x:v>
+      </x:c>
+      <x:c r="B355" t="str">
+        <x:v>Sato_2011</x:v>
+      </x:c>
+      <x:c r="C355" t="str">
+        <x:v>Sato_2011_all</x:v>
+      </x:c>
+      <x:c r="D355" t="str">
+        <x:v>Sato_supportive</x:v>
+      </x:c>
+      <x:c r="E355" t="str">
+        <x:v>Sato_normal</x:v>
+      </x:c>
+      <x:c r="F355" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G355"/>
+      <x:c r="H355" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I355" t="str">
+        <x:v>timed_glucose</x:v>
+      </x:c>
+      <x:c r="J355" t="str">
+        <x:v>Next-morning fasting glucose</x:v>
+      </x:c>
+      <x:c r="K355"/>
+      <x:c r="L355"/>
+      <x:c r="M355" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N355" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O355" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P355" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="Q355" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R355" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S355"/>
+      <x:c r="T355"/>
+      <x:c r="U355" t="n">
+        <x:v>0.231</x:v>
+      </x:c>
+      <x:c r="V355" t="str">
+        <x:v>mg/dL</x:v>
+      </x:c>
+      <x:c r="W355"/>
+      <x:c r="X355"/>
+      <x:c r="Y355" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z355" t="str">
+        <x:v>Sato_2011_primary; PDF p5; Results</x:v>
+      </x:c>
+      <x:c r="AA355"/>
+    </x:row>
+    <x:row r="356">
+      <x:c r="A356" t="str">
+        <x:v>O0379</x:v>
+      </x:c>
+      <x:c r="B356" t="str">
+        <x:v>Sato_2011</x:v>
+      </x:c>
+      <x:c r="C356" t="str">
+        <x:v>Sato_2011_all</x:v>
+      </x:c>
+      <x:c r="D356" t="str">
+        <x:v>Sato_supportive</x:v>
+      </x:c>
+      <x:c r="E356" t="str">
+        <x:v>Sato_late</x:v>
+      </x:c>
+      <x:c r="F356" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G356"/>
+      <x:c r="H356" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I356" t="str">
+        <x:v>timed_glucose</x:v>
+      </x:c>
+      <x:c r="J356" t="str">
+        <x:v>Next-morning fasting glucose</x:v>
+      </x:c>
+      <x:c r="K356"/>
+      <x:c r="L356"/>
+      <x:c r="M356" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N356" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O356" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P356" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="Q356" t="str">
+        <x:v>SEM</x:v>
+      </x:c>
+      <x:c r="R356" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S356"/>
+      <x:c r="T356"/>
+      <x:c r="U356" t="n">
+        <x:v>0.231</x:v>
+      </x:c>
+      <x:c r="V356" t="str">
+        <x:v>mg/dL</x:v>
+      </x:c>
+      <x:c r="W356"/>
+      <x:c r="X356"/>
+      <x:c r="Y356" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z356" t="str">
+        <x:v>Sato_2011_primary; PDF p5; Results</x:v>
+      </x:c>
+      <x:c r="AA356"/>
+    </x:row>
+    <x:row r="357">
+      <x:c r="A357" t="str">
+        <x:v>O0380</x:v>
+      </x:c>
+      <x:c r="B357" t="str">
+        <x:v>Pizinger_2018</x:v>
+      </x:c>
+      <x:c r="C357" t="str">
+        <x:v>Pizinger_2018_all</x:v>
+      </x:c>
+      <x:c r="D357" t="str">
+        <x:v>Pizinger_supportive</x:v>
+      </x:c>
+      <x:c r="E357" t="str">
+        <x:v>Piz_NsNm</x:v>
+      </x:c>
+      <x:c r="F357" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G357" t="str">
+        <x:v>sleep timing: normal</x:v>
+      </x:c>
+      <x:c r="H357" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I357" t="str">
+        <x:v>insulin_sensitivity</x:v>
+      </x:c>
+      <x:c r="J357" t="str">
+        <x:v>MTT Matsuda index</x:v>
+      </x:c>
+      <x:c r="K357"/>
+      <x:c r="L357"/>
+      <x:c r="M357"/>
+      <x:c r="N357" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O357" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="P357" t="n">
+        <x:v>5.67</x:v>
+      </x:c>
+      <x:c r="Q357" t="str">
+        <x:v>SD</x:v>
+      </x:c>
+      <x:c r="R357" t="n">
+        <x:v>2.65</x:v>
+      </x:c>
+      <x:c r="S357"/>
+      <x:c r="T357"/>
+      <x:c r="U357" t="str">
+        <x:v>0.18 (meal main effect)</x:v>
+      </x:c>
+      <x:c r="V357" t="str">
+        <x:v>index</x:v>
+      </x:c>
+      <x:c r="W357"/>
+      <x:c r="X357"/>
+      <x:c r="Y357" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z357" t="str">
+        <x:v>Pizinger_2018_primary; PDF p3; Results</x:v>
+      </x:c>
+      <x:c r="AA357" t="str">
+        <x:v>n=5 for late sleep/late meal; otherwise n=6; log2-transformed analysis.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="358">
+      <x:c r="A358" t="str">
+        <x:v>O0381</x:v>
+      </x:c>
+      <x:c r="B358" t="str">
+        <x:v>Pizinger_2018</x:v>
+      </x:c>
+      <x:c r="C358" t="str">
+        <x:v>Pizinger_2018_all</x:v>
+      </x:c>
+      <x:c r="D358" t="str">
+        <x:v>Pizinger_supportive</x:v>
+      </x:c>
+      <x:c r="E358" t="str">
+        <x:v>Piz_LsNm</x:v>
+      </x:c>
+      <x:c r="F358" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G358" t="str">
+        <x:v>sleep timing: late</x:v>
+      </x:c>
+      <x:c r="H358" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I358" t="str">
+        <x:v>insulin_sensitivity</x:v>
+      </x:c>
+      <x:c r="J358" t="str">
+        <x:v>MTT Matsuda index</x:v>
+      </x:c>
+      <x:c r="K358"/>
+      <x:c r="L358"/>
+      <x:c r="M358"/>
+      <x:c r="N358" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O358" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="P358" t="n">
+        <x:v>4.72</x:v>
+      </x:c>
+      <x:c r="Q358" t="str">
+        <x:v>SD</x:v>
+      </x:c>
+      <x:c r="R358" t="n">
+        <x:v>0.86</x:v>
+      </x:c>
+      <x:c r="S358"/>
+      <x:c r="T358"/>
+      <x:c r="U358" t="str">
+        <x:v>0.18 (meal main effect)</x:v>
+      </x:c>
+      <x:c r="V358" t="str">
+        <x:v>index</x:v>
+      </x:c>
+      <x:c r="W358"/>
+      <x:c r="X358"/>
+      <x:c r="Y358" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z358" t="str">
+        <x:v>Pizinger_2018_primary; PDF p3; Results</x:v>
+      </x:c>
+      <x:c r="AA358" t="str">
+        <x:v>n=5 for late sleep/late meal; otherwise n=6; log2-transformed analysis.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="359">
+      <x:c r="A359" t="str">
+        <x:v>O0382</x:v>
+      </x:c>
+      <x:c r="B359" t="str">
+        <x:v>Pizinger_2018</x:v>
+      </x:c>
+      <x:c r="C359" t="str">
+        <x:v>Pizinger_2018_all</x:v>
+      </x:c>
+      <x:c r="D359" t="str">
+        <x:v>Pizinger_supportive</x:v>
+      </x:c>
+      <x:c r="E359" t="str">
+        <x:v>Piz_NsLm</x:v>
+      </x:c>
+      <x:c r="F359" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G359" t="str">
+        <x:v>sleep timing: normal</x:v>
+      </x:c>
+      <x:c r="H359" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I359" t="str">
+        <x:v>insulin_sensitivity</x:v>
+      </x:c>
+      <x:c r="J359" t="str">
+        <x:v>MTT Matsuda index</x:v>
+      </x:c>
+      <x:c r="K359"/>
+      <x:c r="L359"/>
+      <x:c r="M359"/>
+      <x:c r="N359" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O359" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="P359" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="Q359" t="str">
+        <x:v>SD</x:v>
+      </x:c>
+      <x:c r="R359" t="n">
+        <x:v>2.69</x:v>
+      </x:c>
+      <x:c r="S359"/>
+      <x:c r="T359"/>
+      <x:c r="U359" t="str">
+        <x:v>0.18 (meal main effect)</x:v>
+      </x:c>
+      <x:c r="V359" t="str">
+        <x:v>index</x:v>
+      </x:c>
+      <x:c r="W359"/>
+      <x:c r="X359"/>
+      <x:c r="Y359" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z359" t="str">
+        <x:v>Pizinger_2018_primary; PDF p3; Results</x:v>
+      </x:c>
+      <x:c r="AA359" t="str">
+        <x:v>n=5 for late sleep/late meal; otherwise n=6; log2-transformed analysis.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="360">
+      <x:c r="A360" t="str">
+        <x:v>O0383</x:v>
+      </x:c>
+      <x:c r="B360" t="str">
+        <x:v>Pizinger_2018</x:v>
+      </x:c>
+      <x:c r="C360" t="str">
+        <x:v>Pizinger_2018_all</x:v>
+      </x:c>
+      <x:c r="D360" t="str">
+        <x:v>Pizinger_supportive</x:v>
+      </x:c>
+      <x:c r="E360" t="str">
+        <x:v>Piz_LsLm</x:v>
+      </x:c>
+      <x:c r="F360" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G360" t="str">
+        <x:v>sleep timing: late</x:v>
+      </x:c>
+      <x:c r="H360" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I360" t="str">
+        <x:v>insulin_sensitivity</x:v>
+      </x:c>
+      <x:c r="J360" t="str">
+        <x:v>MTT Matsuda index</x:v>
+      </x:c>
+      <x:c r="K360"/>
+      <x:c r="L360"/>
+      <x:c r="M360"/>
+      <x:c r="N360" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O360" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="P360" t="n">
+        <x:v>3.87</x:v>
+      </x:c>
+      <x:c r="Q360" t="str">
+        <x:v>SD</x:v>
+      </x:c>
+      <x:c r="R360" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="S360"/>
+      <x:c r="T360"/>
+      <x:c r="U360" t="str">
+        <x:v>0.18 (meal main effect)</x:v>
+      </x:c>
+      <x:c r="V360" t="str">
+        <x:v>index</x:v>
+      </x:c>
+      <x:c r="W360"/>
+      <x:c r="X360"/>
+      <x:c r="Y360" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z360" t="str">
+        <x:v>Pizinger_2018_primary; PDF p3; Results</x:v>
+      </x:c>
+      <x:c r="AA360" t="str">
+        <x:v>n=5 for late sleep/late meal; otherwise n=6; log2-transformed analysis.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="361">
+      <x:c r="A361" t="str">
+        <x:v>O0384</x:v>
+      </x:c>
+      <x:c r="B361" t="str">
+        <x:v>Enomoto_2026</x:v>
+      </x:c>
+      <x:c r="C361" t="str">
+        <x:v>Enomoto_2026_all</x:v>
+      </x:c>
+      <x:c r="D361" t="str">
+        <x:v>Enomoto_supportive</x:v>
+      </x:c>
+      <x:c r="E361" t="str">
+        <x:v>Enomoto_5h</x:v>
+      </x:c>
+      <x:c r="F361" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G361"/>
+      <x:c r="H361" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I361" t="str">
+        <x:v>insulin_sensitivity</x:v>
+      </x:c>
+      <x:c r="J361" t="str">
+        <x:v>Next-day HOMA-IR</x:v>
+      </x:c>
+      <x:c r="K361"/>
+      <x:c r="L361"/>
+      <x:c r="M361"/>
+      <x:c r="N361" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O361" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="P361" t="n">
+        <x:v>1.48</x:v>
+      </x:c>
+      <x:c r="Q361" t="str">
+        <x:v>SD</x:v>
+      </x:c>
+      <x:c r="R361" t="n">
+        <x:v>0.72</x:v>
+      </x:c>
+      <x:c r="S361"/>
+      <x:c r="T361"/>
+      <x:c r="U361" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="V361" t="str">
+        <x:v>index</x:v>
+      </x:c>
+      <x:c r="W361"/>
+      <x:c r="X361"/>
+      <x:c r="Y361" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z361" t="str">
+        <x:v>Enomoto_2026_primary; PDF p7; Table 4</x:v>
+      </x:c>
+      <x:c r="AA361" t="str">
+        <x:v>Supportive next-day OGTT/fasting index, not index-dinner insulin AUC.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="362">
+      <x:c r="A362" t="str">
+        <x:v>O0385</x:v>
+      </x:c>
+      <x:c r="B362" t="str">
+        <x:v>Enomoto_2026</x:v>
+      </x:c>
+      <x:c r="C362" t="str">
+        <x:v>Enomoto_2026_all</x:v>
+      </x:c>
+      <x:c r="D362" t="str">
+        <x:v>Enomoto_supportive</x:v>
+      </x:c>
+      <x:c r="E362" t="str">
+        <x:v>Enomoto_1h</x:v>
+      </x:c>
+      <x:c r="F362" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G362"/>
+      <x:c r="H362" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I362" t="str">
+        <x:v>insulin_sensitivity</x:v>
+      </x:c>
+      <x:c r="J362" t="str">
+        <x:v>Next-day HOMA-IR</x:v>
+      </x:c>
+      <x:c r="K362"/>
+      <x:c r="L362"/>
+      <x:c r="M362"/>
+      <x:c r="N362" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O362" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="P362" t="n">
+        <x:v>1.77</x:v>
+      </x:c>
+      <x:c r="Q362" t="str">
+        <x:v>SD</x:v>
+      </x:c>
+      <x:c r="R362" t="n">
+        <x:v>0.61</x:v>
+      </x:c>
+      <x:c r="S362"/>
+      <x:c r="T362"/>
+      <x:c r="U362" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="V362" t="str">
+        <x:v>index</x:v>
+      </x:c>
+      <x:c r="W362"/>
+      <x:c r="X362"/>
+      <x:c r="Y362" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z362" t="str">
+        <x:v>Enomoto_2026_primary; PDF p7; Table 4</x:v>
+      </x:c>
+      <x:c r="AA362" t="str">
+        <x:v>Supportive next-day OGTT/fasting index, not index-dinner insulin AUC.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="363">
+      <x:c r="A363" t="str">
+        <x:v>O0386</x:v>
+      </x:c>
+      <x:c r="B363" t="str">
+        <x:v>Enomoto_2026</x:v>
+      </x:c>
+      <x:c r="C363" t="str">
+        <x:v>Enomoto_2026_all</x:v>
+      </x:c>
+      <x:c r="D363" t="str">
+        <x:v>Enomoto_supportive</x:v>
+      </x:c>
+      <x:c r="E363" t="str">
+        <x:v>Enomoto_5h</x:v>
+      </x:c>
+      <x:c r="F363" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G363"/>
+      <x:c r="H363" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I363" t="str">
+        <x:v>insulin_secretion</x:v>
+      </x:c>
+      <x:c r="J363" t="str">
+        <x:v>Next-day HOMA-beta</x:v>
+      </x:c>
+      <x:c r="K363"/>
+      <x:c r="L363"/>
+      <x:c r="M363"/>
+      <x:c r="N363" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O363" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="P363" t="n">
+        <x:v>111.08</x:v>
+      </x:c>
+      <x:c r="Q363" t="str">
+        <x:v>SD</x:v>
+      </x:c>
+      <x:c r="R363" t="n">
+        <x:v>48.35</x:v>
+      </x:c>
+      <x:c r="S363"/>
+      <x:c r="T363"/>
+      <x:c r="U363" t="n">
+        <x:v>0.563</x:v>
+      </x:c>
+      <x:c r="V363" t="str">
+        <x:v>%</x:v>
+      </x:c>
+      <x:c r="W363"/>
+      <x:c r="X363"/>
+      <x:c r="Y363" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z363" t="str">
+        <x:v>Enomoto_2026_primary; PDF p7; Table 4</x:v>
+      </x:c>
+      <x:c r="AA363" t="str">
+        <x:v>Supportive next-day OGTT/fasting index, not index-dinner insulin AUC.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="364">
+      <x:c r="A364" t="str">
+        <x:v>O0387</x:v>
+      </x:c>
+      <x:c r="B364" t="str">
+        <x:v>Enomoto_2026</x:v>
+      </x:c>
+      <x:c r="C364" t="str">
+        <x:v>Enomoto_2026_all</x:v>
+      </x:c>
+      <x:c r="D364" t="str">
+        <x:v>Enomoto_supportive</x:v>
+      </x:c>
+      <x:c r="E364" t="str">
+        <x:v>Enomoto_1h</x:v>
+      </x:c>
+      <x:c r="F364" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G364"/>
+      <x:c r="H364" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I364" t="str">
+        <x:v>insulin_secretion</x:v>
+      </x:c>
+      <x:c r="J364" t="str">
+        <x:v>Next-day HOMA-beta</x:v>
+      </x:c>
+      <x:c r="K364"/>
+      <x:c r="L364"/>
+      <x:c r="M364"/>
+      <x:c r="N364" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O364" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="P364" t="n">
+        <x:v>118.81</x:v>
+      </x:c>
+      <x:c r="Q364" t="str">
+        <x:v>SD</x:v>
+      </x:c>
+      <x:c r="R364" t="n">
+        <x:v>40.41</x:v>
+      </x:c>
+      <x:c r="S364"/>
+      <x:c r="T364"/>
+      <x:c r="U364" t="n">
+        <x:v>0.563</x:v>
+      </x:c>
+      <x:c r="V364" t="str">
+        <x:v>%</x:v>
+      </x:c>
+      <x:c r="W364"/>
+      <x:c r="X364"/>
+      <x:c r="Y364" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z364" t="str">
+        <x:v>Enomoto_2026_primary; PDF p7; Table 4</x:v>
+      </x:c>
+      <x:c r="AA364" t="str">
+        <x:v>Supportive next-day OGTT/fasting index, not index-dinner insulin AUC.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="365">
+      <x:c r="A365" t="str">
+        <x:v>O0388</x:v>
+      </x:c>
+      <x:c r="B365" t="str">
+        <x:v>Enomoto_2026</x:v>
+      </x:c>
+      <x:c r="C365" t="str">
+        <x:v>Enomoto_2026_all</x:v>
+      </x:c>
+      <x:c r="D365" t="str">
+        <x:v>Enomoto_supportive</x:v>
+      </x:c>
+      <x:c r="E365" t="str">
+        <x:v>Enomoto_5h</x:v>
+      </x:c>
+      <x:c r="F365" t="str">
+        <x:v>earlier</x:v>
+      </x:c>
+      <x:c r="G365"/>
+      <x:c r="H365" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I365" t="str">
+        <x:v>insulin_secretion</x:v>
+      </x:c>
+      <x:c r="J365" t="str">
+        <x:v>Next-day Insulinogenic index</x:v>
+      </x:c>
+      <x:c r="K365"/>
+      <x:c r="L365"/>
+      <x:c r="M365"/>
+      <x:c r="N365" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O365" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="P365" t="n">
+        <x:v>1.28</x:v>
+      </x:c>
+      <x:c r="Q365" t="str">
+        <x:v>SD</x:v>
+      </x:c>
+      <x:c r="R365" t="n">
+        <x:v>0.71</x:v>
+      </x:c>
+      <x:c r="S365"/>
+      <x:c r="T365"/>
+      <x:c r="U365" t="n">
+        <x:v>0.648</x:v>
+      </x:c>
+      <x:c r="V365" t="str">
+        <x:v>index</x:v>
+      </x:c>
+      <x:c r="W365"/>
+      <x:c r="X365"/>
+      <x:c r="Y365" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z365" t="str">
+        <x:v>Enomoto_2026_primary; PDF p7; Table 4</x:v>
+      </x:c>
+      <x:c r="AA365" t="str">
+        <x:v>Supportive next-day OGTT/fasting index, not index-dinner insulin AUC.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="366">
+      <x:c r="A366" t="str">
+        <x:v>O0389</x:v>
+      </x:c>
+      <x:c r="B366" t="str">
+        <x:v>Enomoto_2026</x:v>
+      </x:c>
+      <x:c r="C366" t="str">
+        <x:v>Enomoto_2026_all</x:v>
+      </x:c>
+      <x:c r="D366" t="str">
+        <x:v>Enomoto_supportive</x:v>
+      </x:c>
+      <x:c r="E366" t="str">
+        <x:v>Enomoto_1h</x:v>
+      </x:c>
+      <x:c r="F366" t="str">
+        <x:v>later</x:v>
+      </x:c>
+      <x:c r="G366"/>
+      <x:c r="H366" t="str">
+        <x:v>insulin</x:v>
+      </x:c>
+      <x:c r="I366" t="str">
+        <x:v>insulin_secretion</x:v>
+      </x:c>
+      <x:c r="J366" t="str">
+        <x:v>Next-day Insulinogenic index</x:v>
+      </x:c>
+      <x:c r="K366"/>
+      <x:c r="L366"/>
+      <x:c r="M366"/>
+      <x:c r="N366" t="str">
+        <x:v>condition_summary</x:v>
+      </x:c>
+      <x:c r="O366" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="P366" t="n">
+        <x:v>1.22</x:v>
+      </x:c>
+      <x:c r="Q366" t="str">
+        <x:v>SD</x:v>
+      </x:c>
+      <x:c r="R366" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="S366"/>
+      <x:c r="T366"/>
+      <x:c r="U366" t="n">
+        <x:v>0.648</x:v>
+      </x:c>
+      <x:c r="V366" t="str">
+        <x:v>index</x:v>
+      </x:c>
+      <x:c r="W366"/>
+      <x:c r="X366"/>
+      <x:c r="Y366" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z366" t="str">
+        <x:v>Enomoto_2026_primary; PDF p7; Table 4</x:v>
+      </x:c>
+      <x:c r="AA366" t="str">
+        <x:v>Supportive next-day OGTT/fasting index, not index-dinner insulin AUC.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="367">
+      <x:c r="A367" t="str">
+        <x:v>O0390</x:v>
+      </x:c>
+      <x:c r="B367" t="str">
+        <x:v>Bravo_Garcia_2024</x:v>
+      </x:c>
+      <x:c r="C367" t="str">
+        <x:v>Bravo_Garcia_2024_T2D</x:v>
+      </x:c>
+      <x:c r="D367" t="str">
+        <x:v>Bravo_Garcia_supportive</x:v>
+      </x:c>
+      <x:c r="E367"/>
+      <x:c r="F367"/>
+      <x:c r="G367"/>
+      <x:c r="H367" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I367" t="str">
+        <x:v>cgm_postprandial</x:v>
+      </x:c>
+      <x:c r="J367" t="str">
+        <x:v>24-h glucose iAUC</x:v>
+      </x:c>
+      <x:c r="K367"/>
+      <x:c r="L367" t="n">
+        <x:v>1440</x:v>
+      </x:c>
+      <x:c r="M367"/>
+      <x:c r="N367" t="str">
+        <x:v>narrative_only</x:v>
+      </x:c>
+      <x:c r="O367" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="P367"/>
+      <x:c r="Q367"/>
+      <x:c r="R367"/>
+      <x:c r="S367"/>
+      <x:c r="T367"/>
+      <x:c r="U367" t="str">
+        <x:v>NS</x:v>
+      </x:c>
+      <x:c r="V367"/>
+      <x:c r="W367" t="str">
+        <x:v>no significant difference</x:v>
+      </x:c>
+      <x:c r="X367"/>
+      <x:c r="Y367" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z367" t="str">
+        <x:v>Bravo_Garcia_2024_primary; PDF pp4–5; Results and Figure 3</x:v>
+      </x:c>
+      <x:c r="AA367" t="str">
+        <x:v>No significant difference among early, mid and delayed breakfast without exercise; condition summaries presented graphically.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="368">
+      <x:c r="A368" t="str">
+        <x:v>O0391</x:v>
+      </x:c>
+      <x:c r="B368" t="str">
+        <x:v>Bravo_Garcia_2024</x:v>
+      </x:c>
+      <x:c r="C368" t="str">
+        <x:v>Bravo_Garcia_2024_T2D</x:v>
+      </x:c>
+      <x:c r="D368" t="str">
+        <x:v>Bravo_Garcia_supportive</x:v>
+      </x:c>
+      <x:c r="E368"/>
+      <x:c r="F368"/>
+      <x:c r="G368"/>
+      <x:c r="H368" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I368" t="str">
+        <x:v>cgm_postprandial</x:v>
+      </x:c>
+      <x:c r="J368" t="str">
+        <x:v>Fasting glucose at 06:00</x:v>
+      </x:c>
+      <x:c r="K368"/>
+      <x:c r="L368"/>
+      <x:c r="M368"/>
+      <x:c r="N368" t="str">
+        <x:v>narrative_only</x:v>
+      </x:c>
+      <x:c r="O368" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="P368"/>
+      <x:c r="Q368"/>
+      <x:c r="R368"/>
+      <x:c r="S368"/>
+      <x:c r="T368"/>
+      <x:c r="U368" t="str">
+        <x:v>NS</x:v>
+      </x:c>
+      <x:c r="V368"/>
+      <x:c r="W368" t="str">
+        <x:v>no significant difference</x:v>
+      </x:c>
+      <x:c r="X368"/>
+      <x:c r="Y368" t="str">
+        <x:v>reported_text</x:v>
+      </x:c>
+      <x:c r="Z368" t="str">
+        <x:v>Bravo_Garcia_2024_primary; PDF pp4–5; Results and Figure 3</x:v>
+      </x:c>
+      <x:c r="AA368" t="str">
+        <x:v>No significant difference among early, mid and delayed breakfast without exercise; condition summaries presented graphically.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="369">
+      <x:c r="A369" t="str">
+        <x:v>O0392</x:v>
+      </x:c>
+      <x:c r="B369" t="str">
+        <x:v>Sulaimani_2025</x:v>
+      </x:c>
+      <x:c r="C369" t="str">
+        <x:v>Sulaimani_2025_all</x:v>
+      </x:c>
+      <x:c r="D369" t="str">
+        <x:v>Sulaimani_overall</x:v>
+      </x:c>
+      <x:c r="E369"/>
+      <x:c r="F369"/>
+      <x:c r="G369" t="str">
+        <x:v>overall</x:v>
+      </x:c>
+      <x:c r="H369" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I369" t="str">
+        <x:v>glucose_auc</x:v>
+      </x:c>
+      <x:c r="J369" t="str">
+        <x:v>glucose iAUC paired difference</x:v>
+      </x:c>
+      <x:c r="K369" t="str">
+        <x:v>incremental</x:v>
+      </x:c>
+      <x:c r="L369" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="M369"/>
+      <x:c r="N369" t="str">
+        <x:v>within_person_contrast</x:v>
+      </x:c>
+      <x:c r="O369" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="P369" t="n">
+        <x:v>182.978214285714</x:v>
+      </x:c>
+      <x:c r="Q369" t="str">
+        <x:v>SD (paired difference)</x:v>
+      </x:c>
+      <x:c r="R369" t="n">
+        <x:v>138.498935189008</x:v>
+      </x:c>
+      <x:c r="S369" t="n">
+        <x:v>103.011309888361</x:v>
+      </x:c>
+      <x:c r="T369" t="n">
+        <x:v>262.945118683068</x:v>
+      </x:c>
+      <x:c r="U369"/>
+      <x:c r="V369" t="str">
+        <x:v>mmol/L x min (source-inferred)</x:v>
+      </x:c>
+      <x:c r="W369" t="str">
+        <x:v>evening minus morning</x:v>
+      </x:c>
+      <x:c r="X369"/>
+      <x:c r="Y369" t="str">
+        <x:v>derived</x:v>
+      </x:c>
+      <x:c r="Z369" t="str">
+        <x:v>Sulaimani_2025; author-provided iAUC-glucose worksheet; PDF p6, Figure 3B</x:v>
+      </x:c>
+      <x:c r="AA369" t="str">
+        <x:v>Mean participant-level paired difference; SE=SD_difference/sqrt(14); 95% CI uses t(13). Overall averages both rice conditions within each participant. Raw participant data not redistributed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="370">
+      <x:c r="A370" t="str">
+        <x:v>O0393</x:v>
+      </x:c>
+      <x:c r="B370" t="str">
+        <x:v>Sulaimani_2025</x:v>
+      </x:c>
+      <x:c r="C370" t="str">
+        <x:v>Sulaimani_2025_all</x:v>
+      </x:c>
+      <x:c r="D370" t="str">
+        <x:v>Sulaimani_control</x:v>
+      </x:c>
+      <x:c r="E370"/>
+      <x:c r="F370"/>
+      <x:c r="G370" t="str">
+        <x:v>control</x:v>
+      </x:c>
+      <x:c r="H370" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I370" t="str">
+        <x:v>glucose_auc</x:v>
+      </x:c>
+      <x:c r="J370" t="str">
+        <x:v>glucose iAUC paired difference</x:v>
+      </x:c>
+      <x:c r="K370" t="str">
+        <x:v>incremental</x:v>
+      </x:c>
+      <x:c r="L370" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="M370"/>
+      <x:c r="N370" t="str">
+        <x:v>within_person_contrast</x:v>
+      </x:c>
+      <x:c r="O370" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="P370" t="n">
+        <x:v>163.607857142857</x:v>
+      </x:c>
+      <x:c r="Q370" t="str">
+        <x:v>SD (paired difference)</x:v>
+      </x:c>
+      <x:c r="R370" t="n">
+        <x:v>159.962543845478</x:v>
+      </x:c>
+      <x:c r="S370" t="n">
+        <x:v>71.2482340642237</x:v>
+      </x:c>
+      <x:c r="T370" t="n">
+        <x:v>255.967480221491</x:v>
+      </x:c>
+      <x:c r="U370"/>
+      <x:c r="V370" t="str">
+        <x:v>mmol/L x min (source-inferred)</x:v>
+      </x:c>
+      <x:c r="W370" t="str">
+        <x:v>evening minus morning</x:v>
+      </x:c>
+      <x:c r="X370"/>
+      <x:c r="Y370" t="str">
+        <x:v>derived</x:v>
+      </x:c>
+      <x:c r="Z370" t="str">
+        <x:v>Sulaimani_2025; author-provided iAUC-glucose worksheet; PDF p6, Figure 3B</x:v>
+      </x:c>
+      <x:c r="AA370" t="str">
+        <x:v>Mean participant-level paired difference; SE=SD_difference/sqrt(14); 95% CI uses t(13). Overall averages both rice conditions within each participant. Raw participant data not redistributed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="371">
+      <x:c r="A371" t="str">
+        <x:v>O0394</x:v>
+      </x:c>
+      <x:c r="B371" t="str">
+        <x:v>Sulaimani_2025</x:v>
+      </x:c>
+      <x:c r="C371" t="str">
+        <x:v>Sulaimani_2025_all</x:v>
+      </x:c>
+      <x:c r="D371" t="str">
+        <x:v>Sulaimani_GTE</x:v>
+      </x:c>
+      <x:c r="E371"/>
+      <x:c r="F371"/>
+      <x:c r="G371" t="str">
+        <x:v>GTE</x:v>
+      </x:c>
+      <x:c r="H371" t="str">
+        <x:v>glucose</x:v>
+      </x:c>
+      <x:c r="I371" t="str">
+        <x:v>glucose_auc</x:v>
+      </x:c>
+      <x:c r="J371" t="str">
+        <x:v>glucose iAUC paired difference</x:v>
+      </x:c>
+      <x:c r="K371" t="str">
+        <x:v>incremental</x:v>
+      </x:c>
+      <x:c r="L371" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="M371"/>
+      <x:c r="N371" t="str">
+        <x:v>within_person_contrast</x:v>
+      </x:c>
+      <x:c r="O371" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="P371" t="n">
+        <x:v>202.348571428571</x:v>
+      </x:c>
+      <x:c r="Q371" t="str">
+        <x:v>SD (paired difference)</x:v>
+      </x:c>
+      <x:c r="R371" t="n">
+        <x:v>155.720594451292</x:v>
+      </x:c>
+      <x:c r="S371" t="n">
+        <x:v>112.438177011518</x:v>
+      </x:c>
+      <x:c r="T371" t="n">
+        <x:v>292.258965845624</x:v>
+      </x:c>
+      <x:c r="U371"/>
+      <x:c r="V371" t="str">
+        <x:v>mmol/L x min (source-inferred)</x:v>
+      </x:c>
+      <x:c r="W371" t="str">
+        <x:v>evening minus morning</x:v>
+      </x:c>
+      <x:c r="X371"/>
+      <x:c r="Y371" t="str">
+        <x:v>derived</x:v>
+      </x:c>
+      <x:c r="Z371" t="str">
+        <x:v>Sulaimani_2025; author-provided iAUC-glucose worksheet; PDF p6, Figure 3B</x:v>
+      </x:c>
+      <x:c r="AA371" t="str">
+        <x:v>Mean participant-level paired difference; SE=SD_difference/sqrt(14); 95% CI uses t(13). Overall averages both rice conditions within each participant. Raw participant data not redistributed.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -23858,7 +30163,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84230c2802c0431e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11e2c374ef874738"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23880,347 +30185,347 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="2" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" s="2" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D1" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G1" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H1" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I1" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J1" s="2" t="s">
-        <x:v>9</x:v>
+      <x:c r="A1" s="2" t="str">
+        <x:v>derivation_id</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="str">
+        <x:v>study_id</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="str">
+        <x:v>outcome_id</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="str">
+        <x:v>derivation_type</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="str">
+        <x:v>inputs</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="str">
+        <x:v>formula_or_method</x:v>
+      </x:c>
+      <x:c r="G1" s="2" t="str">
+        <x:v>assumptions</x:v>
+      </x:c>
+      <x:c r="H1" s="2" t="str">
+        <x:v>result</x:v>
+      </x:c>
+      <x:c r="I1" s="2" t="str">
+        <x:v>data_status</x:v>
+      </x:c>
+      <x:c r="J1" s="2" t="str">
+        <x:v>notes</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
-      <x:c r="A2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I2" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="J2" s="1" t="s">
-        <x:v>19</x:v>
+      <x:c r="A2" s="1" t="str">
+        <x:v>D001</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="str">
+        <x:v>Bandin_2015</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="str">
+        <x:v>O0003</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="str">
+        <x:v>paired SE from exact paired t-test</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="str">
+        <x:v>condition means 102.6 and 70.0; n=10; two-sided p=0.002</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="str">
+        <x:v>SE = |MD| / |t_(1-p/2, n-1)|</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="str">
+        <x:v>Exact p corresponds to unadjusted paired t-test for displayed means</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="str">
+        <x:v>SE=7.5870; SDdifference=23.9923</x:v>
+      </x:c>
+      <x:c r="I2" s="1" t="str">
+        <x:v>derived</x:v>
+      </x:c>
+      <x:c r="J2" s="1" t="str">
+        <x:v>Do not use if the reported p was from a different model/test.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B3" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G3" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H3" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="I3" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="J3" s="1" t="s">
-        <x:v>28</x:v>
+      <x:c r="A3" s="1" t="str">
+        <x:v>D002</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="str">
+        <x:v>Bo_2015</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="str">
+        <x:v>O0004</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="str">
+        <x:v>SE from 95% CI</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="str">
+        <x:v>CI [-2564.1, -1036.0]</x:v>
+      </x:c>
+      <x:c r="F3" s="1" t="str">
+        <x:v>SE = (upper-lower)/(2×1.96)</x:v>
+      </x:c>
+      <x:c r="G3" s="1" t="str">
+        <x:v>Normal approximation</x:v>
+      </x:c>
+      <x:c r="H3" s="1" t="str">
+        <x:v>SE=389.8286</x:v>
+      </x:c>
+      <x:c r="I3" s="1" t="str">
+        <x:v>derived</x:v>
+      </x:c>
+      <x:c r="J3" s="1" t="str">
+        <x:v>Reported model contrast itself remains primary.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B4" s="1" t="s">
-        <x:v>30</x:v>
+      <x:c r="A4" s="1" t="str">
+        <x:v>D003</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="str">
+        <x:v>Gu_2020</x:v>
       </x:c>
       <x:c r="C4" s="1"/>
-      <x:c r="D4" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F4" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G4" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H4" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="I4" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="J4" s="1" t="s">
-        <x:v>28</x:v>
+      <x:c r="D4" s="1" t="str">
+        <x:v>SE from 95% CI</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="str">
+        <x:v>CI [70.3, 107.3]</x:v>
+      </x:c>
+      <x:c r="F4" s="1" t="str">
+        <x:v>SE = (upper-lower)/(2×1.96)</x:v>
+      </x:c>
+      <x:c r="G4" s="1" t="str">
+        <x:v>Normal approximation</x:v>
+      </x:c>
+      <x:c r="H4" s="1" t="str">
+        <x:v>SE=9.4390</x:v>
+      </x:c>
+      <x:c r="I4" s="1" t="str">
+        <x:v>derived</x:v>
+      </x:c>
+      <x:c r="J4" s="1" t="str">
+        <x:v>Reported model contrast itself remains primary.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B5" s="1" t="s">
-        <x:v>34</x:v>
+      <x:c r="A5" s="1" t="str">
+        <x:v>D004</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="str">
+        <x:v>Lopez_Minguez_2018</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
-      <x:c r="D5" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F5" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G5" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H5" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I5" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="J5" s="1" t="s">
-        <x:v>38</x:v>
+      <x:c r="D5" s="1" t="str">
+        <x:v>paired SE from exact paired t-test</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="str">
+        <x:v>late 284.74; early 269.61; n=40; p=0.004</x:v>
+      </x:c>
+      <x:c r="F5" s="1" t="str">
+        <x:v>SE = |MD| / |t_(1-p/2, n-1)|</x:v>
+      </x:c>
+      <x:c r="G5" s="1" t="str">
+        <x:v>Exact p corresponds to unadjusted paired t-test for displayed total-sample means</x:v>
+      </x:c>
+      <x:c r="H5" s="1" t="str">
+        <x:v>MD=15.13; SE=4.9456; SDdifference=31.2787</x:v>
+      </x:c>
+      <x:c r="I5" s="1" t="str">
+        <x:v>derived</x:v>
+      </x:c>
+      <x:c r="J5" s="1" t="str">
+        <x:v>Do not transfer covariance to genotype subgroups.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B6" s="1" t="s">
-        <x:v>40</x:v>
+      <x:c r="A6" s="1" t="str">
+        <x:v>D005</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="str">
+        <x:v>Stutz_2024</x:v>
       </x:c>
       <x:c r="C6" s="1"/>
-      <x:c r="D6" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F6" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G6" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H6" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="I6" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="J6" s="1" t="s">
-        <x:v>43</x:v>
+      <x:c r="D6" s="1" t="str">
+        <x:v>SE from 95% CI</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="str">
+        <x:v>early chronotype 2-h iAUC contrast CI [2,77]</x:v>
+      </x:c>
+      <x:c r="F6" s="1" t="str">
+        <x:v>SE = (upper-lower)/(2×1.96)</x:v>
+      </x:c>
+      <x:c r="G6" s="1" t="str">
+        <x:v>Normal approximation</x:v>
+      </x:c>
+      <x:c r="H6" s="1" t="str">
+        <x:v>SE=19.1330</x:v>
+      </x:c>
+      <x:c r="I6" s="1" t="str">
+        <x:v>derived</x:v>
+      </x:c>
+      <x:c r="J6" s="1" t="str">
+        <x:v>Use reported multilevel-model contrast.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B7" s="1" t="s">
-        <x:v>40</x:v>
+      <x:c r="A7" s="1" t="str">
+        <x:v>D006</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="str">
+        <x:v>Stutz_2024</x:v>
       </x:c>
       <x:c r="C7" s="1"/>
-      <x:c r="D7" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F7" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G7" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H7" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="I7" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="J7" s="1" t="s">
-        <x:v>43</x:v>
+      <x:c r="D7" s="1" t="str">
+        <x:v>SE from 95% CI</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="str">
+        <x:v>late chronotype 2-h iAUC contrast CI [-55,48]</x:v>
+      </x:c>
+      <x:c r="F7" s="1" t="str">
+        <x:v>SE = (upper-lower)/(2×1.96)</x:v>
+      </x:c>
+      <x:c r="G7" s="1" t="str">
+        <x:v>Normal approximation</x:v>
+      </x:c>
+      <x:c r="H7" s="1" t="str">
+        <x:v>SE=26.2760</x:v>
+      </x:c>
+      <x:c r="I7" s="1" t="str">
+        <x:v>derived</x:v>
+      </x:c>
+      <x:c r="J7" s="1" t="str">
+        <x:v>Use reported multilevel-model contrast.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B8" s="1" t="s">
-        <x:v>48</x:v>
+      <x:c r="A8" s="1" t="str">
+        <x:v>D007</x:v>
+      </x:c>
+      <x:c r="B8" s="1" t="str">
+        <x:v>Garaulet_2022</x:v>
       </x:c>
       <x:c r="C8" s="1"/>
-      <x:c r="D8" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F8" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G8" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H8" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="I8" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="J8" s="1" t="s">
-        <x:v>55</x:v>
+      <x:c r="D8" s="1" t="str">
+        <x:v>manual graph digitization</x:v>
+      </x:c>
+      <x:c r="E8" s="1" t="str">
+        <x:v>Figure 1B/D bars and SEM caps</x:v>
+      </x:c>
+      <x:c r="F8" s="1" t="str">
+        <x:v>Axis-calibrated visual read; rounded to graph resolution</x:v>
+      </x:c>
+      <x:c r="G8" s="1" t="str">
+        <x:v>No subpixel precision claimed</x:v>
+      </x:c>
+      <x:c r="H8" s="1" t="str">
+        <x:v>glucose ~276 vs 299; insulin ~98 vs 91.5</x:v>
+      </x:c>
+      <x:c r="I8" s="1" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="J8" s="1" t="str">
+        <x:v>Approximate condition means retained; exact paired AUC differences and SDs extracted from PDF p6, Table 2.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="B9" s="1" t="s">
-        <x:v>57</x:v>
+      <x:c r="A9" s="1" t="str">
+        <x:v>D008</x:v>
+      </x:c>
+      <x:c r="B9" s="1" t="str">
+        <x:v>Nakamura_2021</x:v>
       </x:c>
       <x:c r="C9" s="1"/>
-      <x:c r="D9" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F9" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G9" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H9" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I9" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="J9" s="1" t="s">
-        <x:v>61</x:v>
+      <x:c r="D9" s="1" t="str">
+        <x:v>manual graph digitization</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="str">
+        <x:v>Figure 3A/B bars and SD caps</x:v>
+      </x:c>
+      <x:c r="F9" s="1" t="str">
+        <x:v>Axis-calibrated visual read; rounded to graph resolution</x:v>
+      </x:c>
+      <x:c r="G9" s="1" t="str">
+        <x:v>Figure states mean±SD</x:v>
+      </x:c>
+      <x:c r="H9" s="1" t="str">
+        <x:v>meal-specific iAUC and period mean values</x:v>
+      </x:c>
+      <x:c r="I9" s="1" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="J9" s="1" t="str">
+        <x:v>Dinner contrast direction robust; exact values approximate.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B10" s="1" t="s">
-        <x:v>63</x:v>
+      <x:c r="A10" s="1" t="str">
+        <x:v>D009</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="str">
+        <x:v>Sulaimani_2025</x:v>
       </x:c>
       <x:c r="C10" s="1"/>
-      <x:c r="D10" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F10" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G10" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="H10" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="I10" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="J10" s="1" t="s">
-        <x:v>67</x:v>
+      <x:c r="D10" s="1" t="str">
+        <x:v>manual graph digitization</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="str">
+        <x:v>Figures 3C and 4B/C bars and SD caps</x:v>
+      </x:c>
+      <x:c r="F10" s="1" t="str">
+        <x:v>Axis-calibrated visual read; rounded to graph resolution</x:v>
+      </x:c>
+      <x:c r="G10" s="1" t="str">
+        <x:v>Figures state mean±SD</x:v>
+      </x:c>
+      <x:c r="H10" s="1" t="str">
+        <x:v>glucose peak; insulin iAUC and peaks except reported morning GTE peak</x:v>
+      </x:c>
+      <x:c r="I10" s="1" t="str">
+        <x:v>graph_digitized</x:v>
+      </x:c>
+      <x:c r="J10" s="1" t="str">
+        <x:v>Glucose iAUC uses author-provided participant data. Morning GTE insulin peak uses the reported Abstract value.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="1" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="B11" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>70</x:v>
+      <x:c r="A11" s="1" t="str">
+        <x:v>D010</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="str">
+        <x:v>Enomoto_2026</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="str">
+        <x:v>O0261</x:v>
       </x:c>
       <x:c r="D11" s="1" t="str">
         <x:v>unit conversion for delayed-dinner synthesis</x:v>
       </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="F11" s="1" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G11" s="1" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H11" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="I11" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="J11" s="1" t="s">
-        <x:v>75</x:v>
+      <x:c r="E11" s="1" t="str">
+        <x:v>Author-provided Day-2 MD=598.84615 and SE=738.32932 mg/dL×min</x:v>
+      </x:c>
+      <x:c r="F11" s="1" t="str">
+        <x:v>Divide glucose concentration-time values by 18</x:v>
+      </x:c>
+      <x:c r="G11" s="1" t="str">
+        <x:v>1 mmol/L glucose = 18 mg/dL; time unit unchanged</x:v>
+      </x:c>
+      <x:c r="H11" s="1" t="str">
+        <x:v>MD=33.2692; SE=41.0183 mmol/L×min</x:v>
+      </x:c>
+      <x:c r="I11" s="1" t="str">
+        <x:v>derived</x:v>
+      </x:c>
+      <x:c r="J11" s="1" t="str">
+        <x:v>Original author-provided units and values remain unchanged in Outcomes.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R001a2997e0ef4e7f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0bdf524795649bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24276,10 +30581,10 @@
         <x:v>Most crossover studies omit within-person contrast SD/SE.</x:v>
       </x:c>
       <x:c r="F2" s="1" t="str">
-        <x:v>Condition summaries require paired/model precision. Correlation sensitivity calculations describe uncertainty and are not primary variance imputations.</x:v>
+        <x:v>Do not treat conditions as independent; request paired/model precision or obtain approval for a correlation sensitivity analysis.</x:v>
       </x:c>
       <x:c r="G2" s="1" t="str">
-        <x:v>Outcomes and Derivations; meta_analysis/outputs/evidence_assessment/</x:v>
+        <x:v>codebook; feasibility pilot</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -24302,7 +30607,7 @@
         <x:v>Verify against journal version/supplement or author data before synthesis.</x:v>
       </x:c>
       <x:c r="G3" s="1" t="str">
-        <x:v>Bandin_2015; PDF p4</x:v>
+        <x:v>Bandin_2015; PDF p13; Results</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
@@ -24316,13 +30621,13 @@
         <x:v>missing condition values</x:v>
       </x:c>
       <x:c r="D4" s="1" t="str">
-        <x:v>open</x:v>
+        <x:v>resolved</x:v>
       </x:c>
       <x:c r="E4" s="1" t="str">
-        <x:v>Primary AUC condition means are figure-only; adjusted contrast is directly reported.</x:v>
+        <x:v>Condition AUC means and SDs are printed in the companion report.</x:v>
       </x:c>
       <x:c r="F4" s="1" t="str">
-        <x:v>Use reported adjusted contrast; digitize only if condition summaries become necessary.</x:v>
+        <x:v>Extracted from Bo 2017, PDF p4; retain primary adjusted contrast.</x:v>
       </x:c>
       <x:c r="G4" s="1" t="str">
         <x:v>Bo_2015_primary; Figure/Table 2</x:v>
@@ -24345,7 +30650,7 @@
         <x:v>Primary glucose iAUC contrasts have p values but no usable SE/CI; condition summaries are individual plots.</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
-        <x:v>Pairwise model contrasts with SEs or confidence intervals are needed to estimate precision.</x:v>
+        <x:v>Request model contrasts/SE or participant-level summaries.</x:v>
       </x:c>
       <x:c r="G5" s="1" t="str">
         <x:v>Bravo_Garcia_2024; Results/Figure 3</x:v>
@@ -24368,7 +30673,7 @@
         <x:v>Four intervention days show changing condition differences; interaction p is 0.046 in table and 0.042 in abstract.</x:v>
       </x:c>
       <x:c r="F6" s="1" t="str">
-        <x:v>Day 2 is the primary comparison to match Nakamura's Day 2 dinner; Days 1, 3, and 4 are sensitivity analyses. Paired precision supplied on 2026-08-31.</x:v>
+        <x:v>Day 2 prespecified as principal to match Nakamura's Day-2 dinner; Days 1 and 4 retained as adaptation sensitivities. Paired precision supplied by the author on 2026-08-31.</x:v>
       </x:c>
       <x:c r="G6" s="1" t="str">
         <x:v>Enomoto_2026; abstract/Table 3; author correspondence 2026-08-31</x:v>
@@ -24385,16 +30690,16 @@
         <x:v>graph digitization</x:v>
       </x:c>
       <x:c r="D7" s="1" t="str">
-        <x:v>open</x:v>
+        <x:v>partially resolved</x:v>
       </x:c>
       <x:c r="E7" s="1" t="str">
-        <x:v>Absolute AUC means/SEM were read from Figure 1; text reports only relative differences.</x:v>
+        <x:v>Condition AUC means/SEM are figure-derived; exact paired AUC differences and SDs are printed in Table 2.</x:v>
       </x:c>
       <x:c r="F7" s="1" t="str">
-        <x:v>Replace with exact data if supplement/author data become available.</x:v>
+        <x:v>Use reported paired differences and SDs; avoid double-counting overall and genotype strata.</x:v>
       </x:c>
       <x:c r="G7" s="1" t="str">
-        <x:v>Garaulet_2022; Figure 1</x:v>
+        <x:v>Garaulet_2022; PDF p6; Table 2 and Figure 1</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
@@ -24437,7 +30742,7 @@
         <x:v>Dinner and snack times are exchanged, so the eligible dinner timing contrast occurs within a different preceding/following snack schedule.</x:v>
       </x:c>
       <x:c r="F9" s="1" t="str">
-        <x:v>Report separately because dinner timing is accompanied by reciprocal snack timing.</x:v>
+        <x:v>Retain as approved but keep separate/sensitivity-coded in analysis plan.</x:v>
       </x:c>
       <x:c r="G9" s="1" t="str">
         <x:v>Gu_2020; Methods</x:v>
@@ -24572,10 +30877,10 @@
         <x:v>open</x:v>
       </x:c>
       <x:c r="E15" s="1" t="str">
-        <x:v>Integrated glucose unit is malformed in print; small-meal numerical values and insulin/GIP results are figure-based.</x:v>
+        <x:v>Integrated glucose/insulin units are malformed in print; large-meal insulin and secretion summaries are reported in Results; small-meal and other hormone values are figure-based.</x:v>
       </x:c>
       <x:c r="F15" s="1" t="str">
-        <x:v>Verify unit and digitize small-meal/insulin only if needed for a prespecified analysis.</x:v>
+        <x:v>Retain printed units and reported large-meal summaries; do not infer paired precision.</x:v>
       </x:c>
       <x:c r="G15" s="1" t="str">
         <x:v>Service_1983; Results/Figures</x:v>
@@ -24615,13 +30920,13 @@
         <x:v>graph digitization</x:v>
       </x:c>
       <x:c r="D17" s="1" t="str">
-        <x:v>open</x:v>
+        <x:v>partially resolved</x:v>
       </x:c>
       <x:c r="E17" s="1" t="str">
-        <x:v>AUC and peak values are figure-only; time×treatment structure creates dependent eligible contrasts.</x:v>
+        <x:v>Author-provided glucose iAUC values supply condition summaries and paired precision. Other insulin and peak outcomes remain figure-derived, except the reported morning GTE insulin peak.</x:v>
       </x:c>
       <x:c r="F17" s="1" t="str">
-        <x:v>Replace approximate values if exact data are obtained; preserve both control and GTE contrasts.</x:v>
+        <x:v>Use author-derived glucose estimates; no glucose covariance transferred to insulin.</x:v>
       </x:c>
       <x:c r="G17" s="1" t="str">
         <x:v>Sulaimani_2025; Figures 3–4</x:v>
@@ -24644,10 +30949,10 @@
         <x:v>Mixed meals, isolated glucose challenges, daypart, same-meal-occasion, relative-to-sleep, healthy, and T2D studies are not one estimand.</x:v>
       </x:c>
       <x:c r="F18" s="1" t="str">
-        <x:v>Analyze compatible comparisons separately by outcome definition, observation window, meal or challenge, population, and paired precision.</x:v>
+        <x:v>Keep synthesis strata separate under locked PICOS and a later approved analysis plan.</x:v>
       </x:c>
       <x:c r="G18" s="1" t="str">
-        <x:v>meta_analysis/analysis_plan.md</x:v>
+        <x:v>01_protocol/PICOS.md</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="30" customHeight="1">
@@ -24664,7 +30969,7 @@
         <x:v>resolved</x:v>
       </x:c>
       <x:c r="E19" s="1" t="str">
-        <x:v>The CONSORT flow reports 48 randomized, 37 completed, and 34 analyzed per protocol; 40 is not the randomized denominator.</x:v>
+        <x:v>Earlier working extraction treated 40 as randomized; the CONSORT flow reports 48 randomized, 37 completed, and 34 analyzed per protocol.</x:v>
       </x:c>
       <x:c r="F19" s="1" t="str">
         <x:v>Counts corrected from the report flow diagram before ROBUST-RCT assessment.</x:v>
@@ -24687,7 +30992,7 @@
         <x:v>resolved</x:v>
       </x:c>
       <x:c r="E20" s="1" t="str">
-        <x:v>The randomized denominator is 14; the analyzed sample is 12.</x:v>
+        <x:v>Earlier working extraction treated the final n=12 as randomized; 14 were randomized and 12 analyzed.</x:v>
       </x:c>
       <x:c r="F20" s="1" t="str">
         <x:v>Counts corrected from Methods and participant flow before ROBUST-RCT assessment.</x:v>
@@ -24710,7 +31015,7 @@
         <x:v>resolved</x:v>
       </x:c>
       <x:c r="E21" s="1" t="str">
-        <x:v>Randomized and completed counts are not reported by chronotype stratum; analyzed stratum counts cannot substitute for these denominators.</x:v>
+        <x:v>Earlier working extraction copied analyzed chronotype-stratum counts into randomized/completed fields.</x:v>
       </x:c>
       <x:c r="F21" s="1" t="str">
         <x:v>Stratum randomized/completed fields left blank; overall flow retained in notes: 60 randomized, 46 completed, 45 analyzed.</x:v>
@@ -24720,53 +31025,93 @@
       </x:c>
     </x:row>
     <x:row r="22" ht="30" customHeight="1">
-      <x:c r="A22" s="1"/>
+      <x:c r="A22" s="1" t="str">
+        <x:v>I_Lu_1</x:v>
+      </x:c>
       <x:c r="B22" s="1" t="str">
         <x:v>Lu_2022</x:v>
       </x:c>
-      <x:c r="C22" s="1"/>
-      <x:c r="D22" s="1"/>
-      <x:c r="E22" s="1"/>
-      <x:c r="F22" s="1"/>
+      <x:c r="C22" s="1" t="str">
+        <x:v>outcome interpretation</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="str">
+        <x:v>open</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="str">
+        <x:v>Reported CGM 0-270 min extends 30 min beyond scheduled 18:00 dinner in 14S; retain as descriptive context, not clean lunch-only AUC. Paired covariance unavailable.</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="str">
+        <x:v>Retain explicit limitation; do not pool ambiguous or covariance-missing estimates.</x:v>
+      </x:c>
       <x:c r="G22" s="1" t="str">
         <x:v>Lu 2022; pp3-8, Methods/Results and Figures 2-3</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23"/>
+      <x:c r="A23" t="str">
+        <x:v>I_Lu_2</x:v>
+      </x:c>
       <x:c r="B23" t="str">
         <x:v>Lu_2022</x:v>
       </x:c>
-      <x:c r="C23"/>
-      <x:c r="D23"/>
-      <x:c r="E23"/>
-      <x:c r="F23"/>
+      <x:c r="C23" t="str">
+        <x:v>outcome interpretation</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>open</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>Figure 3 AUC/peak labels say 0–120 min, but Methods/time-course axes show −30 to +90 min relative to lunch. Bar means/SEM digitized; paired precision remains unavailable.</x:v>
+      </x:c>
+      <x:c r="F23" t="str">
+        <x:v>Retain explicit limitation; do not pool ambiguous or covariance-missing estimates.</x:v>
+      </x:c>
       <x:c r="G23" t="str">
         <x:v>Lu 2022; pp3-8, Methods/Results and Figures 2-3</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24"/>
+      <x:c r="A24" t="str">
+        <x:v>I_Lu_3</x:v>
+      </x:c>
       <x:c r="B24" t="str">
         <x:v>Lu_2022</x:v>
       </x:c>
-      <x:c r="C24"/>
-      <x:c r="D24"/>
-      <x:c r="E24"/>
-      <x:c r="F24"/>
+      <x:c r="C24" t="str">
+        <x:v>risk of bias</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>open</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>Six of 26 completed participants lack capillary glucose/insulin data (23.1%); CGM available in all 26.</x:v>
+      </x:c>
+      <x:c r="F24" t="str">
+        <x:v>Retain explicit limitation; do not pool ambiguous or covariance-missing estimates.</x:v>
+      </x:c>
       <x:c r="G24" t="str">
         <x:v>Lu 2022; pp3-8, Methods/Results and Figures 2-3</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25"/>
+      <x:c r="A25" t="str">
+        <x:v>I_Lu_4</x:v>
+      </x:c>
       <x:c r="B25" t="str">
         <x:v>Lu_2022</x:v>
       </x:c>
-      <x:c r="C25"/>
-      <x:c r="D25"/>
-      <x:c r="E25"/>
-      <x:c r="F25"/>
+      <x:c r="C25" t="str">
+        <x:v>risk of bias</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>open</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>Registry ChiCTR2200057791 cited; full registry/protocol could not be independently retrieved during this update.</x:v>
+      </x:c>
+      <x:c r="F25" t="str">
+        <x:v>Retain explicit limitation; do not pool ambiguous or covariance-missing estimates.</x:v>
+      </x:c>
       <x:c r="G25" t="str">
         <x:v>Lu 2022; pp3-8, Methods/Results and Figures 2-3</x:v>
       </x:c>
@@ -24782,7 +31127,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbea8a42e211943ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf788c9f499af45f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>